--- a/artfynd/A 45899-2025 artfynd.xlsx
+++ b/artfynd/A 45899-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128952855</v>
+        <v>128952862</v>
       </c>
       <c r="B2" t="n">
         <v>79124</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585226</v>
+        <v>585416</v>
       </c>
       <c r="R2" t="n">
-        <v>7212260</v>
+        <v>7212032</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128952862</v>
+        <v>128952855</v>
       </c>
       <c r="B3" t="n">
         <v>79124</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585416</v>
+        <v>585226</v>
       </c>
       <c r="R3" t="n">
-        <v>7212032</v>
+        <v>7212260</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128952863</v>
+        <v>128952869</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>78527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585437</v>
+        <v>585319</v>
       </c>
       <c r="R11" t="n">
-        <v>7212010</v>
+        <v>7212162</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128952852</v>
+        <v>128952864</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585386</v>
+        <v>585455</v>
       </c>
       <c r="R12" t="n">
-        <v>7212102</v>
+        <v>7211979</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128952864</v>
+        <v>128952863</v>
       </c>
       <c r="B13" t="n">
         <v>79124</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585455</v>
+        <v>585437</v>
       </c>
       <c r="R13" t="n">
-        <v>7211979</v>
+        <v>7212010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128952869</v>
+        <v>128952852</v>
       </c>
       <c r="B14" t="n">
-        <v>78527</v>
+        <v>91526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585319</v>
+        <v>585386</v>
       </c>
       <c r="R14" t="n">
-        <v>7212162</v>
+        <v>7212102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128952861</v>
+        <v>128952834</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585400</v>
+        <v>585327</v>
       </c>
       <c r="R19" t="n">
-        <v>7212047</v>
+        <v>7212199</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128952834</v>
+        <v>128952861</v>
       </c>
       <c r="B20" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585327</v>
+        <v>585400</v>
       </c>
       <c r="R20" t="n">
-        <v>7212199</v>
+        <v>7212047</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128952866</v>
+        <v>128952833</v>
       </c>
       <c r="B24" t="n">
-        <v>75201</v>
+        <v>80258</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585443</v>
+        <v>585389</v>
       </c>
       <c r="R24" t="n">
-        <v>7212014</v>
+        <v>7212111</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128952856</v>
+        <v>128952859</v>
       </c>
       <c r="B25" t="n">
         <v>79124</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585263</v>
+        <v>585319</v>
       </c>
       <c r="R25" t="n">
-        <v>7212285</v>
+        <v>7212183</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3100,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128952833</v>
+        <v>128952856</v>
       </c>
       <c r="B27" t="n">
-        <v>80258</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585389</v>
+        <v>585263</v>
       </c>
       <c r="R27" t="n">
-        <v>7212111</v>
+        <v>7212285</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128952859</v>
+        <v>128952866</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>75201</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585319</v>
+        <v>585443</v>
       </c>
       <c r="R28" t="n">
-        <v>7212183</v>
+        <v>7212014</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128952841</v>
+        <v>128952860</v>
       </c>
       <c r="B29" t="n">
-        <v>80257</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585473</v>
+        <v>585411</v>
       </c>
       <c r="R29" t="n">
-        <v>7211954</v>
+        <v>7212074</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128952860</v>
+        <v>128952841</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>80257</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585411</v>
+        <v>585473</v>
       </c>
       <c r="R30" t="n">
-        <v>7212074</v>
+        <v>7211954</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3876,32 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128970955</v>
+        <v>128971049</v>
       </c>
       <c r="B35" t="n">
-        <v>80264</v>
+        <v>91526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585580</v>
+        <v>585222</v>
       </c>
       <c r="R35" t="n">
-        <v>7212249</v>
+        <v>7212119</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3961,12 +3961,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4063,39 +4063,39 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128971049</v>
+        <v>128970955</v>
       </c>
       <c r="B37" t="n">
-        <v>91526</v>
+        <v>80264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585222</v>
+        <v>585580</v>
       </c>
       <c r="R37" t="n">
-        <v>7212119</v>
+        <v>7212249</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4155,12 +4155,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4264,32 +4264,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128971053</v>
+        <v>128971022</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>97507</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585461</v>
+        <v>585464</v>
       </c>
       <c r="R39" t="n">
-        <v>7211969</v>
+        <v>7211949</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4361,32 +4361,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128971022</v>
+        <v>128971053</v>
       </c>
       <c r="B40" t="n">
-        <v>97507</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585464</v>
+        <v>585461</v>
       </c>
       <c r="R40" t="n">
-        <v>7211949</v>
+        <v>7211969</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4451,17 +4451,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970912</v>
+        <v>128970943</v>
       </c>
       <c r="B41" t="n">
-        <v>80230</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4469,21 +4469,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585753</v>
+        <v>585010</v>
       </c>
       <c r="R41" t="n">
-        <v>7212201</v>
+        <v>7212219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4548,34 +4548,34 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128971071</v>
+        <v>128971060</v>
       </c>
       <c r="B42" t="n">
-        <v>80264</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585174</v>
+        <v>585277</v>
       </c>
       <c r="R42" t="n">
-        <v>7212174</v>
+        <v>7212276</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4645,39 +4645,39 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128970943</v>
+        <v>128971040</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>75192</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585010</v>
+        <v>585331</v>
       </c>
       <c r="R43" t="n">
-        <v>7212219</v>
+        <v>7211998</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4737,22 +4737,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128971060</v>
+        <v>128970954</v>
       </c>
       <c r="B44" t="n">
-        <v>79124</v>
+        <v>88908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4760,21 +4760,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585277</v>
+        <v>585170</v>
       </c>
       <c r="R44" t="n">
-        <v>7212276</v>
+        <v>7212058</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4834,22 +4834,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128970954</v>
+        <v>128970912</v>
       </c>
       <c r="B45" t="n">
-        <v>88908</v>
+        <v>80230</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4857,21 +4857,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585170</v>
+        <v>585753</v>
       </c>
       <c r="R45" t="n">
-        <v>7212058</v>
+        <v>7212201</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4936,17 +4936,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128971040</v>
+        <v>128971071</v>
       </c>
       <c r="B46" t="n">
-        <v>75192</v>
+        <v>80264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4954,21 +4954,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585331</v>
+        <v>585174</v>
       </c>
       <c r="R46" t="n">
-        <v>7211998</v>
+        <v>7212174</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5033,17 +5033,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128971007</v>
+        <v>128971048</v>
       </c>
       <c r="B47" t="n">
-        <v>80230</v>
+        <v>91526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5051,21 +5051,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585162</v>
+        <v>585167</v>
       </c>
       <c r="R47" t="n">
-        <v>7211872</v>
+        <v>7212181</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5105,12 +5105,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5130,39 +5130,39 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128970982</v>
+        <v>128971074</v>
       </c>
       <c r="B48" t="n">
-        <v>75209</v>
+        <v>91918</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>4217</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585424</v>
+        <v>585355</v>
       </c>
       <c r="R48" t="n">
-        <v>7211989</v>
+        <v>7212020</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5329,17 +5329,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128971048</v>
+        <v>128971007</v>
       </c>
       <c r="B50" t="n">
-        <v>91526</v>
+        <v>80230</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585167</v>
+        <v>585162</v>
       </c>
       <c r="R50" t="n">
-        <v>7212181</v>
+        <v>7211872</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5401,12 +5401,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5433,32 +5433,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128971074</v>
+        <v>128970982</v>
       </c>
       <c r="B51" t="n">
-        <v>91918</v>
+        <v>75209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4217</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585355</v>
+        <v>585424</v>
       </c>
       <c r="R51" t="n">
-        <v>7212020</v>
+        <v>7211989</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5523,17 +5523,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128970911</v>
+        <v>128970905</v>
       </c>
       <c r="B52" t="n">
-        <v>80230</v>
+        <v>57717</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585705</v>
+        <v>585261</v>
       </c>
       <c r="R52" t="n">
-        <v>7212154</v>
+        <v>7212445</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5627,32 +5627,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128971072</v>
+        <v>128970952</v>
       </c>
       <c r="B53" t="n">
-        <v>75201</v>
+        <v>91769</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>308</v>
+        <v>65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585126</v>
+        <v>584977</v>
       </c>
       <c r="R53" t="n">
-        <v>7212238</v>
+        <v>7212268</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5712,44 +5712,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128970952</v>
+        <v>128970983</v>
       </c>
       <c r="B54" t="n">
-        <v>91769</v>
+        <v>96882</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584977</v>
+        <v>585336</v>
       </c>
       <c r="R54" t="n">
-        <v>7212268</v>
+        <v>7212194</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5809,44 +5809,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128970905</v>
+        <v>128970953</v>
       </c>
       <c r="B55" t="n">
-        <v>57717</v>
+        <v>91769</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>65</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585261</v>
+        <v>585429</v>
       </c>
       <c r="R55" t="n">
-        <v>7212445</v>
+        <v>7212208</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5911,17 +5911,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128970983</v>
+        <v>128970893</v>
       </c>
       <c r="B56" t="n">
-        <v>96882</v>
+        <v>57880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585336</v>
+        <v>584907</v>
       </c>
       <c r="R56" t="n">
-        <v>7212194</v>
+        <v>7212296</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6003,44 +6003,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128970953</v>
+        <v>128970911</v>
       </c>
       <c r="B57" t="n">
-        <v>91769</v>
+        <v>80230</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>65</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>585429</v>
+        <v>585705</v>
       </c>
       <c r="R57" t="n">
-        <v>7212208</v>
+        <v>7212154</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6105,17 +6105,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128970893</v>
+        <v>128971072</v>
       </c>
       <c r="B58" t="n">
-        <v>57880</v>
+        <v>75201</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6123,21 +6123,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584907</v>
+        <v>585126</v>
       </c>
       <c r="R58" t="n">
-        <v>7212296</v>
+        <v>7212238</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6177,12 +6177,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6197,22 +6197,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128971062</v>
+        <v>128971009</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>80230</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6220,21 +6220,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>585119</v>
+        <v>585602</v>
       </c>
       <c r="R59" t="n">
-        <v>7212230</v>
+        <v>7212039</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6306,27 +6306,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128971069</v>
+        <v>128971062</v>
       </c>
       <c r="B60" t="n">
-        <v>80264</v>
+        <v>79124</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>585209</v>
+        <v>585119</v>
       </c>
       <c r="R60" t="n">
-        <v>7212303</v>
+        <v>7212230</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6396,39 +6396,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128971009</v>
+        <v>128971069</v>
       </c>
       <c r="B61" t="n">
-        <v>80230</v>
+        <v>80264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6438,10 +6438,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585602</v>
+        <v>585209</v>
       </c>
       <c r="R61" t="n">
-        <v>7212039</v>
+        <v>7212303</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6597,32 +6597,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128970984</v>
+        <v>128971033</v>
       </c>
       <c r="B63" t="n">
-        <v>91508</v>
+        <v>80265</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>585162</v>
+        <v>585316</v>
       </c>
       <c r="R63" t="n">
-        <v>7211879</v>
+        <v>7212062</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6687,39 +6687,39 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128971033</v>
+        <v>128971020</v>
       </c>
       <c r="B64" t="n">
-        <v>80265</v>
+        <v>57720</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6729,10 +6729,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>585316</v>
+        <v>585163</v>
       </c>
       <c r="R64" t="n">
-        <v>7212062</v>
+        <v>7211880</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6759,12 +6759,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6791,10 +6796,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128971020</v>
+        <v>128970984</v>
       </c>
       <c r="B65" t="n">
-        <v>57720</v>
+        <v>91508</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6802,21 +6807,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6826,10 +6831,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>585163</v>
+        <v>585162</v>
       </c>
       <c r="R65" t="n">
-        <v>7211880</v>
+        <v>7211879</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6864,11 +6869,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -6983,17 +6983,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128971036</v>
+        <v>128971061</v>
       </c>
       <c r="B67" t="n">
-        <v>91504</v>
+        <v>79124</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7001,21 +7001,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>584592</v>
+        <v>585189</v>
       </c>
       <c r="R67" t="n">
-        <v>7211936</v>
+        <v>7212297</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7055,12 +7055,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7080,39 +7080,39 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128970997</v>
+        <v>128970978</v>
       </c>
       <c r="B68" t="n">
-        <v>80258</v>
+        <v>75209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>585430</v>
+        <v>585096</v>
       </c>
       <c r="R68" t="n">
-        <v>7211964</v>
+        <v>7212243</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7177,17 +7177,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128971019</v>
+        <v>128970944</v>
       </c>
       <c r="B69" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7195,21 +7195,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>585141</v>
+        <v>584886</v>
       </c>
       <c r="R69" t="n">
-        <v>7211874</v>
+        <v>7212247</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7257,11 +7257,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7274,44 +7269,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128971061</v>
+        <v>128970997</v>
       </c>
       <c r="B70" t="n">
-        <v>79124</v>
+        <v>80258</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7321,10 +7316,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>585189</v>
+        <v>585430</v>
       </c>
       <c r="R70" t="n">
-        <v>7212297</v>
+        <v>7211964</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7376,7 +7371,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7480,10 +7475,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128970978</v>
+        <v>128971036</v>
       </c>
       <c r="B72" t="n">
-        <v>75209</v>
+        <v>91504</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7491,21 +7486,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7515,10 +7510,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>585096</v>
+        <v>584592</v>
       </c>
       <c r="R72" t="n">
-        <v>7212243</v>
+        <v>7211936</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7545,12 +7540,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7570,17 +7565,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128970944</v>
+        <v>128971019</v>
       </c>
       <c r="B73" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7588,21 +7583,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7612,10 +7607,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>584886</v>
+        <v>585141</v>
       </c>
       <c r="R73" t="n">
-        <v>7212247</v>
+        <v>7211874</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7650,6 +7645,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -7662,60 +7662,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128970882</v>
+        <v>128970918</v>
       </c>
       <c r="B74" t="n">
-        <v>75209</v>
+        <v>91877</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>1506</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>585056</v>
+        <v>584867</v>
       </c>
       <c r="R74" t="n">
-        <v>7212089</v>
+        <v>7212286</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7756,7 +7753,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7775,32 +7771,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128970918</v>
+        <v>128970913</v>
       </c>
       <c r="B75" t="n">
-        <v>91877</v>
+        <v>80230</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1506</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7810,10 +7806,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>584867</v>
+        <v>585764</v>
       </c>
       <c r="R75" t="n">
-        <v>7212286</v>
+        <v>7212207</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7872,10 +7868,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128971063</v>
+        <v>128970882</v>
       </c>
       <c r="B76" t="n">
-        <v>79124</v>
+        <v>75209</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7883,34 +7879,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>585170</v>
+        <v>585056</v>
       </c>
       <c r="R76" t="n">
-        <v>7212187</v>
+        <v>7212089</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7937,12 +7936,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -7951,28 +7950,29 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128970913</v>
+        <v>128971063</v>
       </c>
       <c r="B77" t="n">
-        <v>80230</v>
+        <v>79124</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7980,21 +7980,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>585764</v>
+        <v>585170</v>
       </c>
       <c r="R77" t="n">
-        <v>7212207</v>
+        <v>7212187</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8054,12 +8054,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8162,17 +8162,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128971031</v>
+        <v>128970887</v>
       </c>
       <c r="B79" t="n">
-        <v>80265</v>
+        <v>91473</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8180,21 +8180,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8204,10 +8204,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>585387</v>
+        <v>585554</v>
       </c>
       <c r="R79" t="n">
-        <v>7211820</v>
+        <v>7212186</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8254,22 +8254,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128970887</v>
+        <v>128971031</v>
       </c>
       <c r="B80" t="n">
-        <v>91473</v>
+        <v>80265</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8277,21 +8277,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8301,10 +8301,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>585554</v>
+        <v>585387</v>
       </c>
       <c r="R80" t="n">
-        <v>7212186</v>
+        <v>7211820</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8351,44 +8351,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128970897</v>
+        <v>128970979</v>
       </c>
       <c r="B81" t="n">
-        <v>80258</v>
+        <v>75209</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8398,10 +8398,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>585579</v>
+        <v>585258</v>
       </c>
       <c r="R81" t="n">
-        <v>7212245</v>
+        <v>7212103</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8448,22 +8448,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128971006</v>
+        <v>128970937</v>
       </c>
       <c r="B82" t="n">
-        <v>80230</v>
+        <v>79124</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8471,21 +8471,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8495,10 +8495,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>584919</v>
+        <v>584860</v>
       </c>
       <c r="R82" t="n">
-        <v>7211893</v>
+        <v>7212204</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8533,34 +8533,40 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128971047</v>
+        <v>128970920</v>
       </c>
       <c r="B83" t="n">
-        <v>91526</v>
+        <v>80229</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8568,21 +8574,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8592,10 +8598,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>585131</v>
+        <v>584863</v>
       </c>
       <c r="R83" t="n">
-        <v>7212210</v>
+        <v>7212236</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8622,12 +8628,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8642,19 +8648,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128970992</v>
+        <v>128970897</v>
       </c>
       <c r="B84" t="n">
         <v>80258</v>
@@ -8689,10 +8695,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>585172</v>
+        <v>585579</v>
       </c>
       <c r="R84" t="n">
-        <v>7212168</v>
+        <v>7212245</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8719,12 +8725,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8739,44 +8745,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128970979</v>
+        <v>128970992</v>
       </c>
       <c r="B85" t="n">
-        <v>75209</v>
+        <v>80258</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8786,10 +8792,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>585258</v>
+        <v>585172</v>
       </c>
       <c r="R85" t="n">
-        <v>7212103</v>
+        <v>7212168</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8848,32 +8854,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128970927</v>
+        <v>128970995</v>
       </c>
       <c r="B86" t="n">
-        <v>91504</v>
+        <v>80258</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8883,10 +8889,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>584905</v>
+        <v>585119</v>
       </c>
       <c r="R86" t="n">
-        <v>7212234</v>
+        <v>7212238</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8913,12 +8919,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -8933,22 +8939,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128970937</v>
+        <v>128970927</v>
       </c>
       <c r="B87" t="n">
-        <v>79124</v>
+        <v>91504</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8956,21 +8962,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8980,10 +8986,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>584860</v>
+        <v>584905</v>
       </c>
       <c r="R87" t="n">
-        <v>7212204</v>
+        <v>7212234</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9018,18 +9024,12 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9041,39 +9041,39 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128970995</v>
+        <v>128971047</v>
       </c>
       <c r="B88" t="n">
-        <v>80258</v>
+        <v>91526</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9083,10 +9083,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>585119</v>
+        <v>585131</v>
       </c>
       <c r="R88" t="n">
-        <v>7212238</v>
+        <v>7212210</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9138,17 +9138,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128970920</v>
+        <v>128971006</v>
       </c>
       <c r="B89" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9156,21 +9156,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9180,10 +9180,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>584863</v>
+        <v>584919</v>
       </c>
       <c r="R89" t="n">
-        <v>7212236</v>
+        <v>7211893</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9230,22 +9230,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128970914</v>
+        <v>128971051</v>
       </c>
       <c r="B90" t="n">
-        <v>58150</v>
+        <v>79124</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9253,21 +9253,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9277,10 +9277,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>585431</v>
+        <v>585414</v>
       </c>
       <c r="R90" t="n">
-        <v>7212208</v>
+        <v>7212007</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9307,12 +9307,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9327,12 +9327,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9436,10 +9436,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128971051</v>
+        <v>128970914</v>
       </c>
       <c r="B92" t="n">
-        <v>79124</v>
+        <v>58150</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9447,21 +9447,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9471,10 +9471,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>585414</v>
+        <v>585431</v>
       </c>
       <c r="R92" t="n">
-        <v>7212007</v>
+        <v>7212208</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9521,44 +9521,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128970891</v>
+        <v>128970904</v>
       </c>
       <c r="B93" t="n">
-        <v>92205</v>
+        <v>57717</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9568,10 +9568,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>585325</v>
+        <v>584971</v>
       </c>
       <c r="R93" t="n">
-        <v>7211962</v>
+        <v>7212140</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9630,32 +9630,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128970947</v>
+        <v>128970891</v>
       </c>
       <c r="B94" t="n">
-        <v>79124</v>
+        <v>92205</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9665,10 +9665,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>585544</v>
+        <v>585325</v>
       </c>
       <c r="R94" t="n">
-        <v>7212152</v>
+        <v>7211962</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9720,17 +9720,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128970904</v>
+        <v>128970947</v>
       </c>
       <c r="B95" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9738,21 +9738,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9762,10 +9762,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>584971</v>
+        <v>585544</v>
       </c>
       <c r="R95" t="n">
-        <v>7212140</v>
+        <v>7212152</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -9925,32 +9925,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128970919</v>
+        <v>128971003</v>
       </c>
       <c r="B97" t="n">
-        <v>80257</v>
+        <v>80230</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>585565</v>
+        <v>585171</v>
       </c>
       <c r="R97" t="n">
-        <v>7212131</v>
+        <v>7212170</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -9990,12 +9990,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10010,19 +10010,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128971003</v>
+        <v>128971008</v>
       </c>
       <c r="B98" t="n">
         <v>80230</v>
@@ -10057,10 +10057,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585171</v>
+        <v>585432</v>
       </c>
       <c r="R98" t="n">
-        <v>7212170</v>
+        <v>7211815</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10209,39 +10209,39 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128970932</v>
+        <v>128970919</v>
       </c>
       <c r="B100" t="n">
-        <v>91522</v>
+        <v>80257</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1204</v>
+        <v>6461</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>584845</v>
+        <v>585565</v>
       </c>
       <c r="R100" t="n">
-        <v>7212279</v>
+        <v>7212131</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10403,39 +10403,39 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128970929</v>
+        <v>128970994</v>
       </c>
       <c r="B102" t="n">
-        <v>91504</v>
+        <v>80258</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>584864</v>
+        <v>585434</v>
       </c>
       <c r="R102" t="n">
-        <v>7212305</v>
+        <v>7211822</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10495,22 +10495,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128970987</v>
+        <v>128970929</v>
       </c>
       <c r="B103" t="n">
-        <v>57880</v>
+        <v>91504</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10518,21 +10518,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585162</v>
+        <v>584864</v>
       </c>
       <c r="R103" t="n">
-        <v>7211759</v>
+        <v>7212305</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10592,22 +10592,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128971008</v>
+        <v>128970957</v>
       </c>
       <c r="B104" t="n">
-        <v>80230</v>
+        <v>75201</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10615,21 +10615,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>585432</v>
+        <v>585399</v>
       </c>
       <c r="R104" t="n">
-        <v>7211815</v>
+        <v>7212426</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10689,22 +10689,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128970957</v>
+        <v>128970932</v>
       </c>
       <c r="B105" t="n">
-        <v>75201</v>
+        <v>91522</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10712,21 +10712,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>585399</v>
+        <v>584845</v>
       </c>
       <c r="R105" t="n">
-        <v>7212426</v>
+        <v>7212279</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10791,39 +10791,39 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128970994</v>
+        <v>128970987</v>
       </c>
       <c r="B106" t="n">
-        <v>80258</v>
+        <v>57880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>585434</v>
+        <v>585162</v>
       </c>
       <c r="R106" t="n">
-        <v>7211822</v>
+        <v>7211759</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10895,32 +10895,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128970886</v>
+        <v>128971038</v>
       </c>
       <c r="B107" t="n">
-        <v>91473</v>
+        <v>56294</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585385</v>
+        <v>585281</v>
       </c>
       <c r="R107" t="n">
-        <v>7212233</v>
+        <v>7212091</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10960,12 +10960,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -10980,44 +10980,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128971002</v>
+        <v>128970933</v>
       </c>
       <c r="B108" t="n">
-        <v>75207</v>
+        <v>91526</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585321</v>
+        <v>585051</v>
       </c>
       <c r="R108" t="n">
-        <v>7212053</v>
+        <v>7212128</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11077,44 +11077,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128970956</v>
+        <v>128971010</v>
       </c>
       <c r="B109" t="n">
-        <v>80264</v>
+        <v>80230</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585564</v>
+        <v>585204</v>
       </c>
       <c r="R109" t="n">
-        <v>7212138</v>
+        <v>7212304</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11174,22 +11174,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128970901</v>
+        <v>128970886</v>
       </c>
       <c r="B110" t="n">
-        <v>80258</v>
+        <v>91473</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11197,21 +11197,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585719</v>
+        <v>585385</v>
       </c>
       <c r="R110" t="n">
-        <v>7212168</v>
+        <v>7212233</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11283,32 +11283,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128971032</v>
+        <v>128970980</v>
       </c>
       <c r="B111" t="n">
-        <v>80265</v>
+        <v>75209</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11318,10 +11318,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585204</v>
+        <v>585330</v>
       </c>
       <c r="R111" t="n">
-        <v>7212303</v>
+        <v>7212026</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11373,39 +11373,39 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128971021</v>
+        <v>128971043</v>
       </c>
       <c r="B112" t="n">
-        <v>57720</v>
+        <v>75192</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585207</v>
+        <v>585466</v>
       </c>
       <c r="R112" t="n">
-        <v>7211876</v>
+        <v>7211980</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11445,17 +11445,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11475,39 +11470,39 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128970933</v>
+        <v>128971002</v>
       </c>
       <c r="B113" t="n">
-        <v>91526</v>
+        <v>75207</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11517,10 +11512,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585051</v>
+        <v>585321</v>
       </c>
       <c r="R113" t="n">
-        <v>7212128</v>
+        <v>7212053</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11547,12 +11542,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11567,44 +11562,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128970980</v>
+        <v>128970956</v>
       </c>
       <c r="B114" t="n">
-        <v>75209</v>
+        <v>80264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11614,10 +11609,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585330</v>
+        <v>585564</v>
       </c>
       <c r="R114" t="n">
-        <v>7212026</v>
+        <v>7212138</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11644,12 +11639,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11664,44 +11659,44 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128971038</v>
+        <v>128970901</v>
       </c>
       <c r="B115" t="n">
-        <v>56294</v>
+        <v>80258</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>206004</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11711,10 +11706,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585281</v>
+        <v>585719</v>
       </c>
       <c r="R115" t="n">
-        <v>7212091</v>
+        <v>7212168</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11741,12 +11736,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11761,22 +11756,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128971043</v>
+        <v>128971032</v>
       </c>
       <c r="B116" t="n">
-        <v>75192</v>
+        <v>80265</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11784,21 +11779,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6439</v>
+        <v>6464</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11808,10 +11803,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>585466</v>
+        <v>585204</v>
       </c>
       <c r="R116" t="n">
-        <v>7211980</v>
+        <v>7212303</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11863,17 +11858,17 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128971010</v>
+        <v>128971021</v>
       </c>
       <c r="B117" t="n">
-        <v>80230</v>
+        <v>57720</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11881,21 +11876,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11905,10 +11900,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585204</v>
+        <v>585207</v>
       </c>
       <c r="R117" t="n">
-        <v>7212304</v>
+        <v>7211876</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11935,12 +11930,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12064,32 +12064,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128970906</v>
+        <v>128971023</v>
       </c>
       <c r="B119" t="n">
-        <v>80230</v>
+        <v>97513</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12099,10 +12099,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>585310</v>
+        <v>584761</v>
       </c>
       <c r="R119" t="n">
-        <v>7211979</v>
+        <v>7211922</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12149,12 +12149,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12251,39 +12251,39 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128970898</v>
+        <v>128970906</v>
       </c>
       <c r="B121" t="n">
-        <v>80258</v>
+        <v>80230</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12293,10 +12293,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>585563</v>
+        <v>585310</v>
       </c>
       <c r="R121" t="n">
-        <v>7212136</v>
+        <v>7211979</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12355,10 +12355,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128971045</v>
+        <v>128970938</v>
       </c>
       <c r="B122" t="n">
-        <v>78096</v>
+        <v>79124</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12366,21 +12366,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12390,10 +12390,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>585459</v>
+        <v>584869</v>
       </c>
       <c r="R122" t="n">
-        <v>7212107</v>
+        <v>7212269</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12420,12 +12420,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12434,50 +12439,51 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128970888</v>
+        <v>128970896</v>
       </c>
       <c r="B123" t="n">
-        <v>91508</v>
+        <v>80258</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12487,10 +12493,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>585158</v>
+        <v>585410</v>
       </c>
       <c r="R123" t="n">
-        <v>7212019</v>
+        <v>7212346</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12549,10 +12555,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128971023</v>
+        <v>128970898</v>
       </c>
       <c r="B124" t="n">
-        <v>97513</v>
+        <v>80258</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12560,21 +12566,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12584,10 +12590,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>584761</v>
+        <v>585563</v>
       </c>
       <c r="R124" t="n">
-        <v>7211922</v>
+        <v>7212136</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12634,44 +12640,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128970896</v>
+        <v>128971045</v>
       </c>
       <c r="B125" t="n">
-        <v>80258</v>
+        <v>78096</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>6487</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12681,10 +12687,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>585410</v>
+        <v>585459</v>
       </c>
       <c r="R125" t="n">
-        <v>7212346</v>
+        <v>7212107</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12711,12 +12717,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12731,22 +12737,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128970938</v>
+        <v>128970888</v>
       </c>
       <c r="B126" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12754,21 +12760,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12778,10 +12784,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>584869</v>
+        <v>585158</v>
       </c>
       <c r="R126" t="n">
-        <v>7212269</v>
+        <v>7212019</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12816,18 +12822,12 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -12839,39 +12839,39 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128971017</v>
+        <v>128971058</v>
       </c>
       <c r="B127" t="n">
-        <v>91962</v>
+        <v>79124</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12881,10 +12881,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>585476</v>
+        <v>585445</v>
       </c>
       <c r="R127" t="n">
-        <v>7211928</v>
+        <v>7211833</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12911,12 +12911,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128970892</v>
+        <v>128970902</v>
       </c>
       <c r="B128" t="n">
-        <v>56910</v>
+        <v>80258</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12954,21 +12954,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>585431</v>
+        <v>585764</v>
       </c>
       <c r="R128" t="n">
-        <v>7212208</v>
+        <v>7212207</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13040,10 +13040,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128970902</v>
+        <v>128970892</v>
       </c>
       <c r="B129" t="n">
-        <v>80258</v>
+        <v>56910</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13051,21 +13051,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13075,10 +13075,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>585764</v>
+        <v>585431</v>
       </c>
       <c r="R129" t="n">
-        <v>7212207</v>
+        <v>7212208</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13137,32 +13137,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128970889</v>
+        <v>128971017</v>
       </c>
       <c r="B130" t="n">
-        <v>91508</v>
+        <v>91962</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13172,10 +13172,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>585054</v>
+        <v>585476</v>
       </c>
       <c r="R130" t="n">
-        <v>7212128</v>
+        <v>7211928</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13202,12 +13202,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13222,22 +13222,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128971058</v>
+        <v>128970889</v>
       </c>
       <c r="B131" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13245,21 +13245,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13269,10 +13269,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>585445</v>
+        <v>585054</v>
       </c>
       <c r="R131" t="n">
-        <v>7211833</v>
+        <v>7212128</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13319,12 +13319,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -13622,10 +13622,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128970941</v>
+        <v>128971004</v>
       </c>
       <c r="B135" t="n">
-        <v>79124</v>
+        <v>80230</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13633,21 +13633,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>585149</v>
+        <v>585316</v>
       </c>
       <c r="R135" t="n">
-        <v>7212061</v>
+        <v>7212062</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13687,12 +13687,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -13707,22 +13707,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128971004</v>
+        <v>128970941</v>
       </c>
       <c r="B136" t="n">
-        <v>80230</v>
+        <v>79124</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13730,21 +13730,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13754,10 +13754,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>585316</v>
+        <v>585149</v>
       </c>
       <c r="R136" t="n">
-        <v>7212062</v>
+        <v>7212061</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13784,12 +13784,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -13804,22 +13804,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128970985</v>
+        <v>128970946</v>
       </c>
       <c r="B137" t="n">
-        <v>91508</v>
+        <v>79124</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13827,21 +13827,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -13851,10 +13851,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>585360</v>
+        <v>585389</v>
       </c>
       <c r="R137" t="n">
-        <v>7212010</v>
+        <v>7212237</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -13881,12 +13881,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -13901,22 +13901,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128970946</v>
+        <v>128970985</v>
       </c>
       <c r="B138" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13924,21 +13924,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -13948,10 +13948,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>585389</v>
+        <v>585360</v>
       </c>
       <c r="R138" t="n">
-        <v>7212237</v>
+        <v>7212010</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -13978,12 +13978,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -13998,12 +13998,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -14107,10 +14107,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128970958</v>
+        <v>128971012</v>
       </c>
       <c r="B140" t="n">
-        <v>75201</v>
+        <v>80230</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14118,21 +14118,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14142,10 +14142,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>585538</v>
+        <v>585414</v>
       </c>
       <c r="R140" t="n">
-        <v>7212165</v>
+        <v>7212004</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14172,12 +14172,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14192,22 +14192,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128971056</v>
+        <v>128971054</v>
       </c>
       <c r="B141" t="n">
-        <v>79124</v>
+        <v>82983</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14215,21 +14215,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>585156</v>
+        <v>585259</v>
       </c>
       <c r="R141" t="n">
-        <v>7211760</v>
+        <v>7212103</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14269,12 +14269,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14294,14 +14294,14 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128970939</v>
+        <v>128971056</v>
       </c>
       <c r="B142" t="n">
         <v>79124</v>
@@ -14336,10 +14336,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>585390</v>
+        <v>585156</v>
       </c>
       <c r="R142" t="n">
-        <v>7212280</v>
+        <v>7211760</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14374,40 +14374,34 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128970975</v>
+        <v>128970939</v>
       </c>
       <c r="B143" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14415,21 +14409,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14439,10 +14433,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>585149</v>
+        <v>585390</v>
       </c>
       <c r="R143" t="n">
-        <v>7211845</v>
+        <v>7212280</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14479,7 +14473,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14488,18 +14482,19 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -14596,39 +14591,39 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128970903</v>
+        <v>128970884</v>
       </c>
       <c r="B145" t="n">
-        <v>91458</v>
+        <v>91473</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14638,10 +14633,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>584882</v>
+        <v>584998</v>
       </c>
       <c r="R145" t="n">
-        <v>7212226</v>
+        <v>7212243</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14700,32 +14695,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128971012</v>
+        <v>128970895</v>
       </c>
       <c r="B146" t="n">
-        <v>80230</v>
+        <v>80258</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14735,10 +14730,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>585414</v>
+        <v>585156</v>
       </c>
       <c r="R146" t="n">
-        <v>7212004</v>
+        <v>7211976</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14765,12 +14760,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -14785,22 +14780,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128970884</v>
+        <v>128970899</v>
       </c>
       <c r="B147" t="n">
-        <v>91473</v>
+        <v>80258</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14808,21 +14803,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -14832,10 +14827,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>584998</v>
+        <v>585588</v>
       </c>
       <c r="R147" t="n">
-        <v>7212243</v>
+        <v>7212104</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -14894,32 +14889,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128970895</v>
+        <v>128971001</v>
       </c>
       <c r="B148" t="n">
-        <v>80258</v>
+        <v>75207</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6462</v>
+        <v>6486</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -14929,10 +14924,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>585156</v>
+        <v>585329</v>
       </c>
       <c r="R148" t="n">
-        <v>7211976</v>
+        <v>7212033</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -14959,12 +14954,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -14979,44 +14974,44 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128970899</v>
+        <v>128970975</v>
       </c>
       <c r="B149" t="n">
-        <v>80258</v>
+        <v>57720</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15026,10 +15021,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>585588</v>
+        <v>585149</v>
       </c>
       <c r="R149" t="n">
-        <v>7212104</v>
+        <v>7211845</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15064,6 +15059,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -15076,44 +15076,44 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128971001</v>
+        <v>128970958</v>
       </c>
       <c r="B150" t="n">
-        <v>75207</v>
+        <v>75201</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6486</v>
+        <v>308</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15123,10 +15123,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>585329</v>
+        <v>585538</v>
       </c>
       <c r="R150" t="n">
-        <v>7212033</v>
+        <v>7212165</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15153,12 +15153,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15173,22 +15173,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128971054</v>
+        <v>128970903</v>
       </c>
       <c r="B151" t="n">
-        <v>82983</v>
+        <v>91458</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15196,21 +15196,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15220,10 +15220,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>585259</v>
+        <v>584882</v>
       </c>
       <c r="R151" t="n">
-        <v>7212103</v>
+        <v>7212226</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15250,12 +15250,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15270,12 +15270,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -15469,7 +15469,7 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -15566,39 +15566,39 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128970909</v>
+        <v>128970885</v>
       </c>
       <c r="B155" t="n">
-        <v>80230</v>
+        <v>91473</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15608,10 +15608,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>585565</v>
+        <v>584988</v>
       </c>
       <c r="R155" t="n">
-        <v>7212137</v>
+        <v>7212367</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15767,32 +15767,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128970885</v>
+        <v>128970909</v>
       </c>
       <c r="B157" t="n">
-        <v>91473</v>
+        <v>80230</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -15802,10 +15802,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>584988</v>
+        <v>585565</v>
       </c>
       <c r="R157" t="n">
-        <v>7212367</v>
+        <v>7212137</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -15954,17 +15954,17 @@
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128971077</v>
+        <v>128970935</v>
       </c>
       <c r="B159" t="n">
-        <v>75201</v>
+        <v>91526</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15972,21 +15972,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -15996,10 +15996,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>585464</v>
+        <v>585062</v>
       </c>
       <c r="R159" t="n">
-        <v>7211979</v>
+        <v>7212390</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16026,12 +16026,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16046,22 +16046,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128970949</v>
+        <v>128970910</v>
       </c>
       <c r="B160" t="n">
-        <v>79124</v>
+        <v>80230</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16069,21 +16069,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16093,10 +16093,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>585698</v>
+        <v>585587</v>
       </c>
       <c r="R160" t="n">
-        <v>7212166</v>
+        <v>7212109</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16148,17 +16148,17 @@
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128970935</v>
+        <v>128971077</v>
       </c>
       <c r="B161" t="n">
-        <v>91526</v>
+        <v>75201</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16166,21 +16166,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>585062</v>
+        <v>585464</v>
       </c>
       <c r="R161" t="n">
-        <v>7212390</v>
+        <v>7211979</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16220,12 +16220,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16240,22 +16240,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128971041</v>
+        <v>128970917</v>
       </c>
       <c r="B162" t="n">
-        <v>75192</v>
+        <v>97513</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16263,21 +16263,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6439</v>
+        <v>221941</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16287,10 +16287,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>585389</v>
+        <v>585427</v>
       </c>
       <c r="R162" t="n">
-        <v>7212014</v>
+        <v>7212206</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16317,12 +16317,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16337,22 +16337,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128970916</v>
+        <v>128970949</v>
       </c>
       <c r="B163" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16360,21 +16360,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16384,10 +16384,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>584918</v>
+        <v>585698</v>
       </c>
       <c r="R163" t="n">
-        <v>7212370</v>
+        <v>7212166</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16422,11 +16422,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
@@ -16444,17 +16439,17 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128970917</v>
+        <v>128971041</v>
       </c>
       <c r="B164" t="n">
-        <v>97513</v>
+        <v>75192</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16462,21 +16457,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221941</v>
+        <v>6439</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16486,10 +16481,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>585427</v>
+        <v>585389</v>
       </c>
       <c r="R164" t="n">
-        <v>7212206</v>
+        <v>7212014</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16516,12 +16511,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -16536,12 +16531,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
@@ -16638,7 +16633,7 @@
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -16742,10 +16737,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128970910</v>
+        <v>128970916</v>
       </c>
       <c r="B167" t="n">
-        <v>80230</v>
+        <v>57720</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16753,21 +16748,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -16777,10 +16772,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>585587</v>
+        <v>584918</v>
       </c>
       <c r="R167" t="n">
-        <v>7212109</v>
+        <v>7212370</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -16813,6 +16808,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -16839,10 +16839,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128970915</v>
+        <v>128970976</v>
       </c>
       <c r="B168" t="n">
-        <v>75214</v>
+        <v>75209</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16850,21 +16850,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -16874,10 +16874,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>585399</v>
+        <v>584777</v>
       </c>
       <c r="R168" t="n">
-        <v>7212426</v>
+        <v>7211899</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -16924,22 +16924,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128970934</v>
+        <v>128971064</v>
       </c>
       <c r="B169" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16947,21 +16947,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -16971,10 +16971,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>584956</v>
+        <v>585286</v>
       </c>
       <c r="R169" t="n">
-        <v>7212144</v>
+        <v>7212090</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17001,12 +17001,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17021,44 +17021,44 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128970986</v>
+        <v>128970940</v>
       </c>
       <c r="B170" t="n">
-        <v>92205</v>
+        <v>79124</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17068,10 +17068,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>584943</v>
+        <v>585683</v>
       </c>
       <c r="R170" t="n">
-        <v>7211913</v>
+        <v>7212167</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17106,34 +17106,40 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128970976</v>
+        <v>128970934</v>
       </c>
       <c r="B171" t="n">
-        <v>75209</v>
+        <v>91526</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17141,21 +17147,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17165,10 +17171,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>584777</v>
+        <v>584956</v>
       </c>
       <c r="R171" t="n">
-        <v>7211899</v>
+        <v>7212144</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17215,22 +17221,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128971029</v>
+        <v>128970915</v>
       </c>
       <c r="B172" t="n">
-        <v>80229</v>
+        <v>75214</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17238,21 +17244,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17262,10 +17268,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>585439</v>
+        <v>585399</v>
       </c>
       <c r="R172" t="n">
-        <v>7211959</v>
+        <v>7212426</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17292,12 +17298,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -17312,44 +17318,44 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128971016</v>
+        <v>128970986</v>
       </c>
       <c r="B173" t="n">
-        <v>75214</v>
+        <v>92205</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1467</v>
+        <v>3298</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17359,10 +17365,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>585463</v>
+        <v>584943</v>
       </c>
       <c r="R173" t="n">
-        <v>7211979</v>
+        <v>7211913</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17389,12 +17395,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -17414,17 +17420,17 @@
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128970926</v>
+        <v>128971016</v>
       </c>
       <c r="B174" t="n">
-        <v>91504</v>
+        <v>75214</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17432,21 +17438,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17456,10 +17462,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>584975</v>
+        <v>585463</v>
       </c>
       <c r="R174" t="n">
-        <v>7212272</v>
+        <v>7211979</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17486,12 +17492,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -17506,22 +17512,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128971028</v>
+        <v>128971005</v>
       </c>
       <c r="B175" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17529,21 +17535,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17553,10 +17559,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>585603</v>
+        <v>584915</v>
       </c>
       <c r="R175" t="n">
-        <v>7212039</v>
+        <v>7211903</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17583,12 +17589,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -17615,7 +17621,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128971005</v>
+        <v>128970907</v>
       </c>
       <c r="B176" t="n">
         <v>80230</v>
@@ -17650,10 +17656,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>584915</v>
+        <v>585322</v>
       </c>
       <c r="R176" t="n">
-        <v>7211903</v>
+        <v>7211897</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -17700,22 +17706,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128971064</v>
+        <v>128971029</v>
       </c>
       <c r="B177" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17723,21 +17729,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -17747,10 +17753,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>585286</v>
+        <v>585439</v>
       </c>
       <c r="R177" t="n">
-        <v>7212090</v>
+        <v>7211959</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -17802,14 +17808,14 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128970930</v>
+        <v>128970926</v>
       </c>
       <c r="B178" t="n">
         <v>91504</v>
@@ -17844,10 +17850,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>585653</v>
+        <v>584975</v>
       </c>
       <c r="R178" t="n">
-        <v>7212149</v>
+        <v>7212272</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -17906,10 +17912,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128970907</v>
+        <v>128971028</v>
       </c>
       <c r="B179" t="n">
-        <v>80230</v>
+        <v>80229</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17917,21 +17923,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -17941,10 +17947,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>585322</v>
+        <v>585603</v>
       </c>
       <c r="R179" t="n">
-        <v>7211897</v>
+        <v>7212039</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -17971,12 +17977,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -17991,12 +17997,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
@@ -18093,17 +18099,17 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128970940</v>
+        <v>128970930</v>
       </c>
       <c r="B181" t="n">
-        <v>79124</v>
+        <v>91504</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18111,21 +18117,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18135,10 +18141,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>585683</v>
+        <v>585653</v>
       </c>
       <c r="R181" t="n">
-        <v>7212167</v>
+        <v>7212149</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18173,18 +18179,12 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -18293,17 +18293,17 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128970948</v>
+        <v>128971011</v>
       </c>
       <c r="B183" t="n">
-        <v>79124</v>
+        <v>80230</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18311,21 +18311,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18335,10 +18335,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>585646</v>
+        <v>585263</v>
       </c>
       <c r="R183" t="n">
-        <v>7212110</v>
+        <v>7212085</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18365,12 +18365,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -18385,22 +18385,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128971027</v>
+        <v>128970948</v>
       </c>
       <c r="B184" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18408,21 +18408,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18432,10 +18432,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>585336</v>
+        <v>585646</v>
       </c>
       <c r="R184" t="n">
-        <v>7211875</v>
+        <v>7212110</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18476,44 +18476,28 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128970928</v>
+        <v>128971027</v>
       </c>
       <c r="B185" t="n">
-        <v>91504</v>
+        <v>80229</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18521,21 +18505,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18545,10 +18529,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>584860</v>
+        <v>585336</v>
       </c>
       <c r="R185" t="n">
-        <v>7212286</v>
+        <v>7211875</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18589,28 +18573,44 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128970999</v>
+        <v>128970942</v>
       </c>
       <c r="B186" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18618,21 +18618,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18642,10 +18642,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>585469</v>
+        <v>585047</v>
       </c>
       <c r="R186" t="n">
-        <v>7211944</v>
+        <v>7212054</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18672,17 +18672,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Hack på låga</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -18697,22 +18692,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128970942</v>
+        <v>128970928</v>
       </c>
       <c r="B187" t="n">
-        <v>79124</v>
+        <v>91504</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18720,21 +18715,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18744,10 +18739,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>585047</v>
+        <v>584860</v>
       </c>
       <c r="R187" t="n">
-        <v>7212054</v>
+        <v>7212286</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18799,17 +18794,17 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128971011</v>
+        <v>128970936</v>
       </c>
       <c r="B188" t="n">
-        <v>80230</v>
+        <v>91526</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18817,21 +18812,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18841,10 +18836,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>585263</v>
+        <v>585451</v>
       </c>
       <c r="R188" t="n">
-        <v>7212085</v>
+        <v>7212214</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -18871,12 +18866,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -18891,22 +18886,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128970936</v>
+        <v>128971044</v>
       </c>
       <c r="B189" t="n">
-        <v>91526</v>
+        <v>91522</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18914,21 +18909,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18938,10 +18933,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>585451</v>
+        <v>585304</v>
       </c>
       <c r="R189" t="n">
-        <v>7212214</v>
+        <v>7211887</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -18988,22 +18983,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128971044</v>
+        <v>128970999</v>
       </c>
       <c r="B190" t="n">
-        <v>91522</v>
+        <v>57717</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19011,21 +19006,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19035,10 +19030,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>585304</v>
+        <v>585469</v>
       </c>
       <c r="R190" t="n">
-        <v>7211887</v>
+        <v>7211944</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19065,12 +19060,17 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Hack på låga</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -19090,7 +19090,7 @@
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>

--- a/artfynd/A 45899-2025 artfynd.xlsx
+++ b/artfynd/A 45899-2025 artfynd.xlsx
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128952852</v>
+        <v>128952863</v>
       </c>
       <c r="B11" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585386</v>
+        <v>585437</v>
       </c>
       <c r="R11" t="n">
-        <v>7212102</v>
+        <v>7212010</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128952863</v>
+        <v>128952869</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>78438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585437</v>
+        <v>585319</v>
       </c>
       <c r="R12" t="n">
-        <v>7212010</v>
+        <v>7212162</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128952869</v>
+        <v>128952864</v>
       </c>
       <c r="B13" t="n">
-        <v>78438</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585319</v>
+        <v>585455</v>
       </c>
       <c r="R13" t="n">
-        <v>7212162</v>
+        <v>7211979</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128952864</v>
+        <v>128952852</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585455</v>
+        <v>585386</v>
       </c>
       <c r="R14" t="n">
-        <v>7211979</v>
+        <v>7212102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970943</v>
+        <v>128970912</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>80141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4275,21 +4275,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585010</v>
+        <v>585753</v>
       </c>
       <c r="R39" t="n">
-        <v>7212219</v>
+        <v>7212201</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4354,17 +4354,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128971053</v>
+        <v>128970954</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>88926</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585461</v>
+        <v>585170</v>
       </c>
       <c r="R40" t="n">
-        <v>7211969</v>
+        <v>7212058</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4446,19 +4446,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128971060</v>
+        <v>128970943</v>
       </c>
       <c r="B41" t="n">
         <v>79035</v>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585277</v>
+        <v>585010</v>
       </c>
       <c r="R41" t="n">
-        <v>7212276</v>
+        <v>7212219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4523,12 +4523,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4543,44 +4543,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128971040</v>
+        <v>128971053</v>
       </c>
       <c r="B42" t="n">
-        <v>82994</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585331</v>
+        <v>585461</v>
       </c>
       <c r="R42" t="n">
-        <v>7211998</v>
+        <v>7211969</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4652,27 +4652,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128971071</v>
+        <v>128971060</v>
       </c>
       <c r="B43" t="n">
-        <v>80175</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585174</v>
+        <v>585277</v>
       </c>
       <c r="R43" t="n">
-        <v>7212174</v>
+        <v>7212276</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4749,32 +4749,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128970912</v>
+        <v>128971040</v>
       </c>
       <c r="B44" t="n">
-        <v>80141</v>
+        <v>82994</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585753</v>
+        <v>585331</v>
       </c>
       <c r="R44" t="n">
-        <v>7212201</v>
+        <v>7211998</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4834,44 +4834,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128970954</v>
+        <v>128971022</v>
       </c>
       <c r="B45" t="n">
-        <v>88926</v>
+        <v>97530</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585170</v>
+        <v>585464</v>
       </c>
       <c r="R45" t="n">
-        <v>7212058</v>
+        <v>7211949</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4911,12 +4911,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4931,22 +4931,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128971022</v>
+        <v>128971071</v>
       </c>
       <c r="B46" t="n">
-        <v>97530</v>
+        <v>80175</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4954,21 +4954,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585464</v>
+        <v>585174</v>
       </c>
       <c r="R46" t="n">
-        <v>7211949</v>
+        <v>7212174</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128971072</v>
+        <v>128970905</v>
       </c>
       <c r="B52" t="n">
-        <v>83003</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5541,21 +5541,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>308</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585126</v>
+        <v>585261</v>
       </c>
       <c r="R52" t="n">
-        <v>7212238</v>
+        <v>7212445</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5595,12 +5595,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5615,44 +5615,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128970952</v>
+        <v>128970893</v>
       </c>
       <c r="B53" t="n">
-        <v>91787</v>
+        <v>57883</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584977</v>
+        <v>584907</v>
       </c>
       <c r="R53" t="n">
-        <v>7212268</v>
+        <v>7212296</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5717,17 +5717,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128970983</v>
+        <v>128970911</v>
       </c>
       <c r="B54" t="n">
-        <v>96905</v>
+        <v>80141</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585336</v>
+        <v>585705</v>
       </c>
       <c r="R54" t="n">
-        <v>7212194</v>
+        <v>7212154</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5809,44 +5809,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128970953</v>
+        <v>128971072</v>
       </c>
       <c r="B55" t="n">
-        <v>91787</v>
+        <v>83003</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585429</v>
+        <v>585126</v>
       </c>
       <c r="R55" t="n">
-        <v>7212208</v>
+        <v>7212238</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5886,12 +5886,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5906,44 +5906,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128970905</v>
+        <v>128970952</v>
       </c>
       <c r="B56" t="n">
-        <v>57720</v>
+        <v>91787</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>65</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585261</v>
+        <v>584977</v>
       </c>
       <c r="R56" t="n">
-        <v>7212445</v>
+        <v>7212268</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6008,17 +6008,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128970893</v>
+        <v>128970983</v>
       </c>
       <c r="B57" t="n">
-        <v>57883</v>
+        <v>96905</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6026,21 +6026,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584907</v>
+        <v>585336</v>
       </c>
       <c r="R57" t="n">
-        <v>7212296</v>
+        <v>7212194</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6100,44 +6100,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128970911</v>
+        <v>128970953</v>
       </c>
       <c r="B58" t="n">
-        <v>80141</v>
+        <v>91787</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>65</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>585705</v>
+        <v>585429</v>
       </c>
       <c r="R58" t="n">
-        <v>7212154</v>
+        <v>7212208</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -8363,10 +8363,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128970927</v>
+        <v>128971006</v>
       </c>
       <c r="B81" t="n">
-        <v>91522</v>
+        <v>80141</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8374,21 +8374,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8398,10 +8398,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>584905</v>
+        <v>584919</v>
       </c>
       <c r="R81" t="n">
-        <v>7212234</v>
+        <v>7211893</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8448,44 +8448,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128970995</v>
+        <v>128970927</v>
       </c>
       <c r="B82" t="n">
-        <v>80169</v>
+        <v>91522</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8495,10 +8495,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>585119</v>
+        <v>584905</v>
       </c>
       <c r="R82" t="n">
-        <v>7212238</v>
+        <v>7212234</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8525,12 +8525,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8545,22 +8545,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128971006</v>
+        <v>128971047</v>
       </c>
       <c r="B83" t="n">
-        <v>80141</v>
+        <v>91544</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8568,21 +8568,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>584919</v>
+        <v>585131</v>
       </c>
       <c r="R83" t="n">
-        <v>7211893</v>
+        <v>7212210</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8622,12 +8622,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8654,10 +8654,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128971047</v>
+        <v>128970937</v>
       </c>
       <c r="B84" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8665,21 +8665,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>585131</v>
+        <v>584860</v>
       </c>
       <c r="R84" t="n">
-        <v>7212210</v>
+        <v>7212204</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8719,12 +8719,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8733,28 +8738,29 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128970937</v>
+        <v>128970979</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>83011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8762,21 +8768,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8786,10 +8792,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>584860</v>
+        <v>585258</v>
       </c>
       <c r="R85" t="n">
-        <v>7212204</v>
+        <v>7212103</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8816,17 +8822,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8835,29 +8836,28 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128970979</v>
+        <v>128970920</v>
       </c>
       <c r="B86" t="n">
-        <v>83011</v>
+        <v>80140</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8865,21 +8865,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>585258</v>
+        <v>584863</v>
       </c>
       <c r="R86" t="n">
-        <v>7212103</v>
+        <v>7212236</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -8939,44 +8939,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128970920</v>
+        <v>128970897</v>
       </c>
       <c r="B87" t="n">
-        <v>80140</v>
+        <v>80169</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8986,10 +8986,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>584863</v>
+        <v>585579</v>
       </c>
       <c r="R87" t="n">
-        <v>7212236</v>
+        <v>7212245</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9048,7 +9048,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128970897</v>
+        <v>128970992</v>
       </c>
       <c r="B88" t="n">
         <v>80169</v>
@@ -9083,10 +9083,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>585579</v>
+        <v>585172</v>
       </c>
       <c r="R88" t="n">
-        <v>7212245</v>
+        <v>7212168</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9113,12 +9113,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9133,19 +9133,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128970992</v>
+        <v>128970995</v>
       </c>
       <c r="B89" t="n">
         <v>80169</v>
@@ -9180,10 +9180,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>585172</v>
+        <v>585119</v>
       </c>
       <c r="R89" t="n">
-        <v>7212168</v>
+        <v>7212238</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10895,32 +10895,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128971010</v>
+        <v>128970886</v>
       </c>
       <c r="B107" t="n">
-        <v>80141</v>
+        <v>91491</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585204</v>
+        <v>585385</v>
       </c>
       <c r="R107" t="n">
-        <v>7212304</v>
+        <v>7212233</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10960,12 +10960,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -10980,44 +10980,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128970886</v>
+        <v>128970933</v>
       </c>
       <c r="B108" t="n">
-        <v>91491</v>
+        <v>91544</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585385</v>
+        <v>585051</v>
       </c>
       <c r="R108" t="n">
-        <v>7212233</v>
+        <v>7212128</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11089,10 +11089,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128970933</v>
+        <v>128970980</v>
       </c>
       <c r="B109" t="n">
-        <v>91544</v>
+        <v>83011</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11100,21 +11100,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585051</v>
+        <v>585330</v>
       </c>
       <c r="R109" t="n">
-        <v>7212128</v>
+        <v>7212026</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11174,44 +11174,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128970980</v>
+        <v>128971043</v>
       </c>
       <c r="B110" t="n">
-        <v>83011</v>
+        <v>82994</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585330</v>
+        <v>585466</v>
       </c>
       <c r="R110" t="n">
-        <v>7212026</v>
+        <v>7211980</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11276,39 +11276,39 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128971043</v>
+        <v>128971021</v>
       </c>
       <c r="B111" t="n">
-        <v>82994</v>
+        <v>57723</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11318,10 +11318,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585466</v>
+        <v>585207</v>
       </c>
       <c r="R111" t="n">
-        <v>7211980</v>
+        <v>7211876</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11348,12 +11348,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11380,32 +11385,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128971021</v>
+        <v>128971002</v>
       </c>
       <c r="B112" t="n">
-        <v>57723</v>
+        <v>83009</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11415,10 +11420,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585207</v>
+        <v>585321</v>
       </c>
       <c r="R112" t="n">
-        <v>7211876</v>
+        <v>7212053</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11445,17 +11450,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11482,32 +11482,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128971002</v>
+        <v>128970956</v>
       </c>
       <c r="B113" t="n">
-        <v>83009</v>
+        <v>80175</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6486</v>
+        <v>6463</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11517,10 +11517,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585321</v>
+        <v>585564</v>
       </c>
       <c r="R113" t="n">
-        <v>7212053</v>
+        <v>7212138</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11547,12 +11547,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11567,22 +11567,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128970956</v>
+        <v>128970901</v>
       </c>
       <c r="B114" t="n">
-        <v>80175</v>
+        <v>80169</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11590,21 +11590,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11614,10 +11614,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585564</v>
+        <v>585719</v>
       </c>
       <c r="R114" t="n">
-        <v>7212138</v>
+        <v>7212168</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11669,17 +11669,17 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128970901</v>
+        <v>128971032</v>
       </c>
       <c r="B115" t="n">
-        <v>80169</v>
+        <v>80176</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11687,21 +11687,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11711,10 +11711,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585719</v>
+        <v>585204</v>
       </c>
       <c r="R115" t="n">
-        <v>7212168</v>
+        <v>7212303</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11741,12 +11741,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11761,44 +11761,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128971032</v>
+        <v>128971010</v>
       </c>
       <c r="B116" t="n">
-        <v>80176</v>
+        <v>80141</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11811,7 +11811,7 @@
         <v>585204</v>
       </c>
       <c r="R116" t="n">
-        <v>7212303</v>
+        <v>7212304</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11967,10 +11967,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128970906</v>
+        <v>128971050</v>
       </c>
       <c r="B118" t="n">
-        <v>80141</v>
+        <v>91544</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11978,21 +11978,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12002,10 +12002,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>585310</v>
+        <v>585494</v>
       </c>
       <c r="R118" t="n">
-        <v>7211979</v>
+        <v>7211881</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12032,12 +12032,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12052,44 +12052,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128970888</v>
+        <v>128970896</v>
       </c>
       <c r="B119" t="n">
-        <v>91526</v>
+        <v>80169</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12099,10 +12099,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>585158</v>
+        <v>585410</v>
       </c>
       <c r="R119" t="n">
-        <v>7212019</v>
+        <v>7212346</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12161,10 +12161,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128971050</v>
+        <v>128970906</v>
       </c>
       <c r="B120" t="n">
-        <v>91544</v>
+        <v>80141</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12172,21 +12172,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12196,10 +12196,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>585494</v>
+        <v>585310</v>
       </c>
       <c r="R120" t="n">
-        <v>7211881</v>
+        <v>7211979</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12226,12 +12226,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12246,44 +12246,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128970896</v>
+        <v>128970888</v>
       </c>
       <c r="B121" t="n">
-        <v>80169</v>
+        <v>91526</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12293,10 +12293,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>585410</v>
+        <v>585158</v>
       </c>
       <c r="R121" t="n">
-        <v>7212346</v>
+        <v>7212019</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12355,32 +12355,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128970898</v>
+        <v>128970938</v>
       </c>
       <c r="B122" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12390,10 +12390,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>585563</v>
+        <v>584869</v>
       </c>
       <c r="R122" t="n">
-        <v>7212136</v>
+        <v>7212269</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12428,12 +12428,18 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12445,39 +12451,39 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128971045</v>
+        <v>128970898</v>
       </c>
       <c r="B123" t="n">
-        <v>78043</v>
+        <v>80169</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12487,10 +12493,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>585459</v>
+        <v>585563</v>
       </c>
       <c r="R123" t="n">
-        <v>7212107</v>
+        <v>7212136</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12517,12 +12523,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12537,44 +12543,44 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128971023</v>
+        <v>128971045</v>
       </c>
       <c r="B124" t="n">
-        <v>97536</v>
+        <v>78043</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221941</v>
+        <v>6487</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12584,10 +12590,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>584761</v>
+        <v>585459</v>
       </c>
       <c r="R124" t="n">
-        <v>7211922</v>
+        <v>7212107</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12614,12 +12620,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12646,32 +12652,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128970938</v>
+        <v>128971023</v>
       </c>
       <c r="B125" t="n">
-        <v>79035</v>
+        <v>97536</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12681,10 +12687,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>584869</v>
+        <v>584761</v>
       </c>
       <c r="R125" t="n">
-        <v>7212269</v>
+        <v>7211922</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12719,30 +12725,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -13525,10 +13525,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128970985</v>
+        <v>128971004</v>
       </c>
       <c r="B134" t="n">
-        <v>91526</v>
+        <v>80141</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13536,21 +13536,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13560,10 +13560,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>585360</v>
+        <v>585316</v>
       </c>
       <c r="R134" t="n">
-        <v>7212010</v>
+        <v>7212062</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13615,14 +13615,14 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128970890</v>
+        <v>128970985</v>
       </c>
       <c r="B135" t="n">
         <v>91526</v>
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>585002</v>
+        <v>585360</v>
       </c>
       <c r="R135" t="n">
-        <v>7212200</v>
+        <v>7212010</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13687,12 +13687,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -13707,22 +13707,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128970941</v>
+        <v>128970890</v>
       </c>
       <c r="B136" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13730,21 +13730,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13754,10 +13754,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>585149</v>
+        <v>585002</v>
       </c>
       <c r="R136" t="n">
-        <v>7212061</v>
+        <v>7212200</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -13809,14 +13809,14 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128970946</v>
+        <v>128970941</v>
       </c>
       <c r="B137" t="n">
         <v>79035</v>
@@ -13851,10 +13851,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>585389</v>
+        <v>585149</v>
       </c>
       <c r="R137" t="n">
-        <v>7212237</v>
+        <v>7212061</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -13913,10 +13913,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128971004</v>
+        <v>128970946</v>
       </c>
       <c r="B138" t="n">
-        <v>80141</v>
+        <v>79035</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13924,21 +13924,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -13948,10 +13948,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>585316</v>
+        <v>585389</v>
       </c>
       <c r="R138" t="n">
-        <v>7212062</v>
+        <v>7212237</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -13978,12 +13978,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -13998,12 +13998,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -15185,32 +15185,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128970993</v>
+        <v>128970909</v>
       </c>
       <c r="B151" t="n">
-        <v>80169</v>
+        <v>80141</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15220,10 +15220,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>585161</v>
+        <v>585565</v>
       </c>
       <c r="R151" t="n">
-        <v>7211868</v>
+        <v>7212137</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15270,44 +15270,44 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128970909</v>
+        <v>128970885</v>
       </c>
       <c r="B152" t="n">
-        <v>80141</v>
+        <v>91491</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15317,10 +15317,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>585565</v>
+        <v>584988</v>
       </c>
       <c r="R152" t="n">
-        <v>7212137</v>
+        <v>7212367</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15379,32 +15379,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128970885</v>
+        <v>128970945</v>
       </c>
       <c r="B153" t="n">
-        <v>91491</v>
+        <v>79035</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15414,10 +15414,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>584988</v>
+        <v>584857</v>
       </c>
       <c r="R153" t="n">
-        <v>7212367</v>
+        <v>7212300</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15469,17 +15469,17 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128970945</v>
+        <v>128970981</v>
       </c>
       <c r="B154" t="n">
-        <v>79035</v>
+        <v>83011</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15487,21 +15487,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15511,10 +15511,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>584857</v>
+        <v>585399</v>
       </c>
       <c r="R154" t="n">
-        <v>7212300</v>
+        <v>7212011</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15541,12 +15541,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -15561,22 +15561,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128970981</v>
+        <v>128971057</v>
       </c>
       <c r="B155" t="n">
-        <v>83011</v>
+        <v>79035</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15584,21 +15584,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15608,10 +15608,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>585399</v>
+        <v>585238</v>
       </c>
       <c r="R155" t="n">
-        <v>7212011</v>
+        <v>7211876</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15638,12 +15638,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -15663,39 +15663,39 @@
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128971057</v>
+        <v>128970993</v>
       </c>
       <c r="B156" t="n">
-        <v>79035</v>
+        <v>80169</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15705,10 +15705,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>585238</v>
+        <v>585161</v>
       </c>
       <c r="R156" t="n">
-        <v>7211876</v>
+        <v>7211868</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -16645,10 +16645,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128971073</v>
+        <v>128971005</v>
       </c>
       <c r="B166" t="n">
-        <v>83003</v>
+        <v>80141</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16656,21 +16656,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -16680,10 +16680,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>585334</v>
+        <v>584915</v>
       </c>
       <c r="R166" t="n">
-        <v>7212000</v>
+        <v>7211903</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -16710,12 +16710,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -16742,10 +16742,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128970976</v>
+        <v>128971073</v>
       </c>
       <c r="B167" t="n">
-        <v>83011</v>
+        <v>83003</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16753,21 +16753,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -16777,10 +16777,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>584777</v>
+        <v>585334</v>
       </c>
       <c r="R167" t="n">
-        <v>7211899</v>
+        <v>7212000</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -16807,12 +16807,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -16839,10 +16839,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128971064</v>
+        <v>128970915</v>
       </c>
       <c r="B168" t="n">
-        <v>79035</v>
+        <v>83016</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16850,21 +16850,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -16874,10 +16874,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>585286</v>
+        <v>585399</v>
       </c>
       <c r="R168" t="n">
-        <v>7212090</v>
+        <v>7212426</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -16904,12 +16904,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -16924,22 +16924,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128971029</v>
+        <v>128971016</v>
       </c>
       <c r="B169" t="n">
-        <v>80140</v>
+        <v>83016</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16947,21 +16947,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -16971,10 +16971,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>585439</v>
+        <v>585463</v>
       </c>
       <c r="R169" t="n">
-        <v>7211959</v>
+        <v>7211979</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17033,10 +17033,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128971028</v>
+        <v>128970926</v>
       </c>
       <c r="B170" t="n">
-        <v>80140</v>
+        <v>91522</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17044,21 +17044,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17068,10 +17068,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>585603</v>
+        <v>584975</v>
       </c>
       <c r="R170" t="n">
-        <v>7212039</v>
+        <v>7212272</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17098,12 +17098,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17118,44 +17118,44 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128970986</v>
+        <v>128970930</v>
       </c>
       <c r="B171" t="n">
-        <v>92226</v>
+        <v>91522</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17165,10 +17165,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>584943</v>
+        <v>585653</v>
       </c>
       <c r="R171" t="n">
-        <v>7211913</v>
+        <v>7212149</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17215,22 +17215,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128971005</v>
+        <v>128970934</v>
       </c>
       <c r="B172" t="n">
-        <v>80141</v>
+        <v>91544</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17238,21 +17238,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17262,10 +17262,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>584915</v>
+        <v>584956</v>
       </c>
       <c r="R172" t="n">
-        <v>7211903</v>
+        <v>7212144</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17312,22 +17312,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128970907</v>
+        <v>128970976</v>
       </c>
       <c r="B173" t="n">
-        <v>80141</v>
+        <v>83011</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17335,21 +17335,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17359,10 +17359,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>585322</v>
+        <v>584777</v>
       </c>
       <c r="R173" t="n">
-        <v>7211897</v>
+        <v>7211899</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17409,22 +17409,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128970915</v>
+        <v>128971064</v>
       </c>
       <c r="B174" t="n">
-        <v>83016</v>
+        <v>79035</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17432,21 +17432,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17456,10 +17456,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>585399</v>
+        <v>585286</v>
       </c>
       <c r="R174" t="n">
-        <v>7212426</v>
+        <v>7212090</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17486,12 +17486,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -17506,44 +17506,44 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128971016</v>
+        <v>128970986</v>
       </c>
       <c r="B175" t="n">
-        <v>83016</v>
+        <v>92226</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1467</v>
+        <v>3298</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17553,10 +17553,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>585463</v>
+        <v>584943</v>
       </c>
       <c r="R175" t="n">
-        <v>7211979</v>
+        <v>7211913</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17583,12 +17583,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128970926</v>
+        <v>128970907</v>
       </c>
       <c r="B176" t="n">
-        <v>91522</v>
+        <v>80141</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17626,21 +17626,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -17650,10 +17650,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>584975</v>
+        <v>585322</v>
       </c>
       <c r="R176" t="n">
-        <v>7212272</v>
+        <v>7211897</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -17712,10 +17712,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128970930</v>
+        <v>128970940</v>
       </c>
       <c r="B177" t="n">
-        <v>91522</v>
+        <v>79035</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17723,21 +17723,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -17747,10 +17747,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>585653</v>
+        <v>585683</v>
       </c>
       <c r="R177" t="n">
-        <v>7212149</v>
+        <v>7212167</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -17785,12 +17785,18 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -17802,17 +17808,17 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128970934</v>
+        <v>128971029</v>
       </c>
       <c r="B178" t="n">
-        <v>91544</v>
+        <v>80140</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17820,21 +17826,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -17844,10 +17850,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>584956</v>
+        <v>585439</v>
       </c>
       <c r="R178" t="n">
-        <v>7212144</v>
+        <v>7211959</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -17874,12 +17880,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -17894,22 +17900,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128970940</v>
+        <v>128971028</v>
       </c>
       <c r="B179" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17917,21 +17923,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -17941,10 +17947,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>585683</v>
+        <v>585603</v>
       </c>
       <c r="R179" t="n">
-        <v>7212167</v>
+        <v>7212039</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -17971,17 +17977,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -17990,19 +17991,18 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
@@ -21867,48 +21867,48 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128995949</v>
+        <v>128996010</v>
       </c>
       <c r="B219" t="n">
-        <v>79035</v>
+        <v>58093</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>585449</v>
+        <v>585591</v>
       </c>
       <c r="R219" t="n">
-        <v>7212279</v>
+        <v>7212135</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -21948,48 +21948,53 @@
       </c>
       <c r="AG219" t="b">
         <v>0</v>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Henny My Lindqvist, Embla Berg, Elin Kannerby, Alva Danielsson</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128995841</v>
+        <v>128995949</v>
       </c>
       <c r="B220" t="n">
-        <v>80168</v>
+        <v>79035</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -21999,10 +22004,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>585295</v>
+        <v>585449</v>
       </c>
       <c r="R220" t="n">
-        <v>7212209</v>
+        <v>7212279</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22029,12 +22034,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -22049,22 +22054,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
+          <t>Magdalena Nilsson, Henny My Lindqvist, Embla Berg, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128996010</v>
+        <v>128995841</v>
       </c>
       <c r="B221" t="n">
-        <v>58093</v>
+        <v>80168</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22072,37 +22077,37 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>103015</v>
+        <v>6461</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>585591</v>
+        <v>585295</v>
       </c>
       <c r="R221" t="n">
-        <v>7212135</v>
+        <v>7212209</v>
       </c>
       <c r="S221" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -22126,12 +22131,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -22142,21 +22147,16 @@
       </c>
       <c r="AG221" t="b">
         <v>0</v>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
@@ -22265,10 +22265,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128995908</v>
+        <v>128995844</v>
       </c>
       <c r="B223" t="n">
-        <v>80169</v>
+        <v>80168</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22276,21 +22276,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22300,10 +22300,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>585324</v>
+        <v>585365</v>
       </c>
       <c r="R223" t="n">
-        <v>7211986</v>
+        <v>7212081</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22350,22 +22350,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson, Embla Berg, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128995932</v>
+        <v>128995908</v>
       </c>
       <c r="B224" t="n">
-        <v>80176</v>
+        <v>80169</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22373,21 +22373,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -22397,10 +22397,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>584973</v>
+        <v>585324</v>
       </c>
       <c r="R224" t="n">
-        <v>7211930</v>
+        <v>7211986</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22427,12 +22427,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -22452,17 +22452,17 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Alva Danielsson</t>
+          <t>Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson, Embla Berg, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128995844</v>
+        <v>128995932</v>
       </c>
       <c r="B225" t="n">
-        <v>80168</v>
+        <v>80176</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22470,21 +22470,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22494,10 +22494,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>585365</v>
+        <v>584973</v>
       </c>
       <c r="R225" t="n">
-        <v>7212081</v>
+        <v>7211930</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22524,12 +22524,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -22544,12 +22544,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Henny My Lindqvist, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
@@ -23173,45 +23173,49 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128996000</v>
+        <v>128995995</v>
       </c>
       <c r="B232" t="n">
-        <v>97530</v>
+        <v>57723</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>585440</v>
+        <v>584838</v>
       </c>
       <c r="R232" t="n">
-        <v>7212032</v>
+        <v>7212145</v>
       </c>
       <c r="S232" t="n">
         <v>15</v>
@@ -23238,12 +23242,17 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -23275,10 +23284,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128995947</v>
+        <v>128995994</v>
       </c>
       <c r="B233" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23286,37 +23295,41 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>585239</v>
+        <v>584839</v>
       </c>
       <c r="R233" t="n">
-        <v>7211879</v>
+        <v>7212144</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -23348,6 +23361,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD233" t="b">
         <v>0</v>
       </c>
@@ -23356,48 +23374,53 @@
       </c>
       <c r="AG233" t="b">
         <v>0</v>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Henny My Lindqvist, Embla Berg, Elin Kannerby, Alva Danielsson</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128995838</v>
+        <v>128995947</v>
       </c>
       <c r="B234" t="n">
-        <v>80168</v>
+        <v>79035</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -23407,10 +23430,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>584779</v>
+        <v>585239</v>
       </c>
       <c r="R234" t="n">
-        <v>7211856</v>
+        <v>7211879</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -23457,64 +23480,60 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
+          <t>Magdalena Nilsson, Henny My Lindqvist, Embla Berg, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128995995</v>
+        <v>128995838</v>
       </c>
       <c r="B235" t="n">
-        <v>57723</v>
+        <v>80168</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>584838</v>
+        <v>584779</v>
       </c>
       <c r="R235" t="n">
-        <v>7212145</v>
+        <v>7211856</v>
       </c>
       <c r="S235" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -23546,11 +23565,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD235" t="b">
         <v>0</v>
       </c>
@@ -23559,70 +23573,61 @@
       </c>
       <c r="AG235" t="b">
         <v>0</v>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128995994</v>
+        <v>128996000</v>
       </c>
       <c r="B236" t="n">
-        <v>57723</v>
+        <v>97530</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>584839</v>
+        <v>585440</v>
       </c>
       <c r="R236" t="n">
-        <v>7212144</v>
+        <v>7212032</v>
       </c>
       <c r="S236" t="n">
         <v>15</v>
@@ -23649,17 +23654,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -23691,10 +23691,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128995985</v>
+        <v>128995919</v>
       </c>
       <c r="B237" t="n">
-        <v>80141</v>
+        <v>91811</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23702,37 +23702,37 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>585343</v>
+        <v>585128</v>
       </c>
       <c r="R237" t="n">
-        <v>7211931</v>
+        <v>7212334</v>
       </c>
       <c r="S237" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -23756,12 +23756,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -23772,69 +23772,64 @@
       </c>
       <c r="AG237" t="b">
         <v>0</v>
-      </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Henny My Lindqvist, Embla Berg, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128996042</v>
+        <v>128995948</v>
       </c>
       <c r="B238" t="n">
-        <v>91887</v>
+        <v>79035</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>585044</v>
+        <v>585381</v>
       </c>
       <c r="R238" t="n">
-        <v>7212452</v>
+        <v>7212289</v>
       </c>
       <c r="S238" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -23874,28 +23869,23 @@
       </c>
       <c r="AG238" t="b">
         <v>0</v>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Henny My Lindqvist, Embla Berg, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128995916</v>
+        <v>128995985</v>
       </c>
       <c r="B239" t="n">
         <v>80141</v>
@@ -23926,17 +23916,17 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>585465</v>
+        <v>585343</v>
       </c>
       <c r="R239" t="n">
-        <v>7211972</v>
+        <v>7211931</v>
       </c>
       <c r="S239" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -23960,12 +23950,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -23976,64 +23966,69 @@
       </c>
       <c r="AG239" t="b">
         <v>0</v>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Henny My Lindqvist, Embla Berg, Elin Kannerby, Alva Danielsson</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128995919</v>
+        <v>128996042</v>
       </c>
       <c r="B240" t="n">
-        <v>91811</v>
+        <v>91887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>658</v>
+        <v>2063</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>585128</v>
+        <v>585044</v>
       </c>
       <c r="R240" t="n">
-        <v>7212334</v>
+        <v>7212452</v>
       </c>
       <c r="S240" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -24057,12 +24052,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -24073,26 +24068,31 @@
       </c>
       <c r="AG240" t="b">
         <v>0</v>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Henny My Lindqvist, Embla Berg, Elin Kannerby, Alva Danielsson</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128995948</v>
+        <v>128995916</v>
       </c>
       <c r="B241" t="n">
-        <v>79035</v>
+        <v>80141</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24100,21 +24100,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24124,10 +24124,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>585381</v>
+        <v>585465</v>
       </c>
       <c r="R241" t="n">
-        <v>7212289</v>
+        <v>7211972</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24154,12 +24154,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -24574,32 +24574,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128995933</v>
+        <v>128995913</v>
       </c>
       <c r="B246" t="n">
-        <v>80176</v>
+        <v>80141</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -24609,10 +24609,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>584847</v>
+        <v>584976</v>
       </c>
       <c r="R246" t="n">
-        <v>7212088</v>
+        <v>7211927</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -24671,10 +24671,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128995913</v>
+        <v>128995859</v>
       </c>
       <c r="B247" t="n">
-        <v>80141</v>
+        <v>79035</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24682,21 +24682,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -24706,10 +24706,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>584976</v>
+        <v>585374</v>
       </c>
       <c r="R247" t="n">
-        <v>7211927</v>
+        <v>7212193</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -24736,12 +24736,12 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -24756,19 +24756,19 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128995859</v>
+        <v>128995873</v>
       </c>
       <c r="B248" t="n">
         <v>79035</v>
@@ -24803,10 +24803,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>585374</v>
+        <v>585359</v>
       </c>
       <c r="R248" t="n">
-        <v>7212193</v>
+        <v>7211881</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -24833,12 +24833,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -24865,48 +24865,48 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128995873</v>
+        <v>128995975</v>
       </c>
       <c r="B249" t="n">
-        <v>79035</v>
+        <v>80169</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>585359</v>
+        <v>584970</v>
       </c>
       <c r="R249" t="n">
-        <v>7211881</v>
+        <v>7211976</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -24946,26 +24946,31 @@
       </c>
       <c r="AG249" t="b">
         <v>0</v>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128995975</v>
+        <v>128995933</v>
       </c>
       <c r="B250" t="n">
-        <v>80169</v>
+        <v>80176</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -24973,37 +24978,37 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>584970</v>
+        <v>584847</v>
       </c>
       <c r="R250" t="n">
-        <v>7211976</v>
+        <v>7212088</v>
       </c>
       <c r="S250" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -25043,21 +25048,16 @@
       </c>
       <c r="AG250" t="b">
         <v>0</v>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
@@ -26966,10 +26966,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128995912</v>
+        <v>128995864</v>
       </c>
       <c r="B270" t="n">
-        <v>80141</v>
+        <v>79035</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -26977,21 +26977,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -27001,10 +27001,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>584990</v>
+        <v>585345</v>
       </c>
       <c r="R270" t="n">
-        <v>7211932</v>
+        <v>7211890</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27051,22 +27051,22 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128995864</v>
+        <v>128995912</v>
       </c>
       <c r="B271" t="n">
-        <v>79035</v>
+        <v>80141</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27074,21 +27074,21 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -27098,10 +27098,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>585345</v>
+        <v>584990</v>
       </c>
       <c r="R271" t="n">
-        <v>7211890</v>
+        <v>7211932</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27148,12 +27148,12 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
@@ -27257,48 +27257,52 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128995906</v>
+        <v>128995993</v>
       </c>
       <c r="B273" t="n">
-        <v>80169</v>
+        <v>57723</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>584836</v>
+        <v>584850</v>
       </c>
       <c r="R273" t="n">
-        <v>7212031</v>
+        <v>7212144</v>
       </c>
       <c r="S273" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -27330,6 +27334,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD273" t="b">
         <v>0</v>
       </c>
@@ -27338,48 +27347,53 @@
       </c>
       <c r="AG273" t="b">
         <v>0</v>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson, Embla Berg, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128995936</v>
+        <v>128995830</v>
       </c>
       <c r="B274" t="n">
-        <v>80176</v>
+        <v>57883</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -27389,10 +27403,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>585498</v>
+        <v>585373</v>
       </c>
       <c r="R274" t="n">
-        <v>7211887</v>
+        <v>7211857</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -27419,12 +27433,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -27439,64 +27453,60 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128995993</v>
+        <v>128995906</v>
       </c>
       <c r="B275" t="n">
-        <v>57723</v>
+        <v>80169</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>584850</v>
+        <v>584836</v>
       </c>
       <c r="R275" t="n">
-        <v>7212144</v>
+        <v>7212031</v>
       </c>
       <c r="S275" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -27528,11 +27538,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD275" t="b">
         <v>0</v>
       </c>
@@ -27541,53 +27546,48 @@
       </c>
       <c r="AG275" t="b">
         <v>0</v>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Henny My Lindqvist, Alva Danielsson, Embla Berg, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128995830</v>
+        <v>128995936</v>
       </c>
       <c r="B276" t="n">
-        <v>57883</v>
+        <v>80176</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -27597,10 +27597,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>585373</v>
+        <v>585498</v>
       </c>
       <c r="R276" t="n">
-        <v>7211857</v>
+        <v>7211887</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -27627,12 +27627,12 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -27647,12 +27647,12 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
@@ -28251,32 +28251,32 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>128995931</v>
+        <v>128995959</v>
       </c>
       <c r="B283" t="n">
-        <v>80140</v>
+        <v>80175</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -28348,32 +28348,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128995840</v>
+        <v>128995931</v>
       </c>
       <c r="B284" t="n">
-        <v>80168</v>
+        <v>80140</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -28383,10 +28383,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>585334</v>
+        <v>585498</v>
       </c>
       <c r="R284" t="n">
-        <v>7212251</v>
+        <v>7211887</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -28433,22 +28433,22 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
+          <t>Magdalena Nilsson, Henny My Lindqvist, Embla Berg, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128995959</v>
+        <v>128995840</v>
       </c>
       <c r="B285" t="n">
-        <v>80175</v>
+        <v>80168</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -28456,21 +28456,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -28480,10 +28480,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>585498</v>
+        <v>585334</v>
       </c>
       <c r="R285" t="n">
-        <v>7211887</v>
+        <v>7212251</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -28530,12 +28530,12 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Henny My Lindqvist, Embla Berg, Elin Kannerby, Alva Danielsson</t>
+          <t>Henny My Lindqvist, Elin Kannerby, Alva Danielsson, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>

--- a/artfynd/A 45899-2025 artfynd.xlsx
+++ b/artfynd/A 45899-2025 artfynd.xlsx
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128952863</v>
+        <v>128952852</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>91551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585437</v>
+        <v>585386</v>
       </c>
       <c r="R11" t="n">
-        <v>7212010</v>
+        <v>7212102</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128952864</v>
+        <v>128952863</v>
       </c>
       <c r="B12" t="n">
         <v>79039</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585455</v>
+        <v>585437</v>
       </c>
       <c r="R12" t="n">
-        <v>7211979</v>
+        <v>7212010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128952869</v>
+        <v>128952864</v>
       </c>
       <c r="B13" t="n">
-        <v>78442</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585319</v>
+        <v>585455</v>
       </c>
       <c r="R13" t="n">
-        <v>7212162</v>
+        <v>7211979</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128952852</v>
+        <v>128952869</v>
       </c>
       <c r="B14" t="n">
-        <v>91551</v>
+        <v>78442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585386</v>
+        <v>585319</v>
       </c>
       <c r="R14" t="n">
-        <v>7212102</v>
+        <v>7212162</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128952843</v>
+        <v>128952829</v>
       </c>
       <c r="B22" t="n">
-        <v>80180</v>
+        <v>83015</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585493</v>
+        <v>585380</v>
       </c>
       <c r="R22" t="n">
-        <v>7211911</v>
+        <v>7212123</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128952829</v>
+        <v>128952843</v>
       </c>
       <c r="B23" t="n">
-        <v>83015</v>
+        <v>80180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585380</v>
+        <v>585493</v>
       </c>
       <c r="R23" t="n">
-        <v>7212123</v>
+        <v>7211911</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128971060</v>
+        <v>128971053</v>
       </c>
       <c r="B39" t="n">
         <v>79039</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585277</v>
+        <v>585461</v>
       </c>
       <c r="R39" t="n">
-        <v>7212276</v>
+        <v>7211969</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128971053</v>
+        <v>128970912</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>80145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585461</v>
+        <v>585753</v>
       </c>
       <c r="R40" t="n">
-        <v>7211969</v>
+        <v>7212201</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4446,22 +4446,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970943</v>
+        <v>128970954</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>88930</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4469,21 +4469,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585010</v>
+        <v>585170</v>
       </c>
       <c r="R41" t="n">
-        <v>7212219</v>
+        <v>7212058</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4555,32 +4555,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970912</v>
+        <v>128971022</v>
       </c>
       <c r="B42" t="n">
-        <v>80145</v>
+        <v>97540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585753</v>
+        <v>585464</v>
       </c>
       <c r="R42" t="n">
-        <v>7212201</v>
+        <v>7211949</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4640,44 +4640,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128970954</v>
+        <v>128971071</v>
       </c>
       <c r="B43" t="n">
-        <v>88930</v>
+        <v>80179</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585170</v>
+        <v>585174</v>
       </c>
       <c r="R43" t="n">
-        <v>7212058</v>
+        <v>7212174</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4737,44 +4737,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128971022</v>
+        <v>128971060</v>
       </c>
       <c r="B44" t="n">
-        <v>97540</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585464</v>
+        <v>585277</v>
       </c>
       <c r="R44" t="n">
-        <v>7211949</v>
+        <v>7212276</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4846,27 +4846,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128971071</v>
+        <v>128970943</v>
       </c>
       <c r="B45" t="n">
-        <v>80179</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585174</v>
+        <v>585010</v>
       </c>
       <c r="R45" t="n">
-        <v>7212174</v>
+        <v>7212219</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4911,12 +4911,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4931,12 +4931,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6893,10 +6893,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128971036</v>
+        <v>128970944</v>
       </c>
       <c r="B66" t="n">
-        <v>91529</v>
+        <v>79039</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6904,21 +6904,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>584592</v>
+        <v>584886</v>
       </c>
       <c r="R66" t="n">
-        <v>7211936</v>
+        <v>7212247</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6978,22 +6978,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128971019</v>
+        <v>128970978</v>
       </c>
       <c r="B67" t="n">
-        <v>57725</v>
+        <v>83015</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7001,21 +7001,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>585141</v>
+        <v>585096</v>
       </c>
       <c r="R67" t="n">
-        <v>7211874</v>
+        <v>7212243</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7055,17 +7055,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7092,32 +7087,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128970997</v>
+        <v>128971061</v>
       </c>
       <c r="B68" t="n">
-        <v>80173</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7127,10 +7122,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>585430</v>
+        <v>585189</v>
       </c>
       <c r="R68" t="n">
-        <v>7211964</v>
+        <v>7212297</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7182,39 +7177,39 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128970900</v>
+        <v>128971036</v>
       </c>
       <c r="B69" t="n">
-        <v>80173</v>
+        <v>91529</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7224,10 +7219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>585705</v>
+        <v>584592</v>
       </c>
       <c r="R69" t="n">
-        <v>7212153</v>
+        <v>7211936</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7274,22 +7269,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128970944</v>
+        <v>128971046</v>
       </c>
       <c r="B70" t="n">
-        <v>79039</v>
+        <v>91551</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7297,21 +7292,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7321,10 +7316,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>584886</v>
+        <v>584663</v>
       </c>
       <c r="R70" t="n">
-        <v>7212247</v>
+        <v>7211977</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7371,44 +7366,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128970978</v>
+        <v>128970997</v>
       </c>
       <c r="B71" t="n">
-        <v>83015</v>
+        <v>80173</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7418,10 +7413,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>585096</v>
+        <v>585430</v>
       </c>
       <c r="R71" t="n">
-        <v>7212243</v>
+        <v>7211964</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7473,39 +7468,39 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128971061</v>
+        <v>128970900</v>
       </c>
       <c r="B72" t="n">
-        <v>79039</v>
+        <v>80173</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7515,10 +7510,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>585189</v>
+        <v>585705</v>
       </c>
       <c r="R72" t="n">
-        <v>7212297</v>
+        <v>7212153</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7545,12 +7540,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7565,22 +7560,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128971046</v>
+        <v>128971019</v>
       </c>
       <c r="B73" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7588,21 +7583,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7612,10 +7607,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>584663</v>
+        <v>585141</v>
       </c>
       <c r="R73" t="n">
-        <v>7211977</v>
+        <v>7211874</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7648,6 +7643,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128971055</v>
+        <v>128970887</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>91497</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>585255</v>
+        <v>585554</v>
       </c>
       <c r="R74" t="n">
-        <v>7212100</v>
+        <v>7212186</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7739,17 +7739,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7758,51 +7753,50 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128971063</v>
+        <v>128971031</v>
       </c>
       <c r="B75" t="n">
-        <v>79039</v>
+        <v>80180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7812,10 +7806,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>585170</v>
+        <v>585387</v>
       </c>
       <c r="R75" t="n">
-        <v>7212187</v>
+        <v>7211820</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7842,12 +7836,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7874,10 +7868,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128970882</v>
+        <v>128971055</v>
       </c>
       <c r="B76" t="n">
-        <v>83015</v>
+        <v>79039</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7885,37 +7879,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>585056</v>
+        <v>585255</v>
       </c>
       <c r="R76" t="n">
-        <v>7212089</v>
+        <v>7212100</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7942,12 +7933,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -7963,44 +7959,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128970918</v>
+        <v>128971063</v>
       </c>
       <c r="B77" t="n">
-        <v>91903</v>
+        <v>79039</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8010,10 +8006,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>584867</v>
+        <v>585170</v>
       </c>
       <c r="R77" t="n">
-        <v>7212286</v>
+        <v>7212187</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8040,12 +8036,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8060,22 +8056,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128970913</v>
+        <v>128970882</v>
       </c>
       <c r="B78" t="n">
-        <v>80145</v>
+        <v>83015</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8083,34 +8079,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>585764</v>
+        <v>585056</v>
       </c>
       <c r="R78" t="n">
-        <v>7212207</v>
+        <v>7212089</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8151,6 +8150,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8169,32 +8169,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128971031</v>
+        <v>128970918</v>
       </c>
       <c r="B79" t="n">
-        <v>80180</v>
+        <v>91903</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>1506</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8204,10 +8204,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>585387</v>
+        <v>584867</v>
       </c>
       <c r="R79" t="n">
-        <v>7211820</v>
+        <v>7212286</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8254,44 +8254,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128970887</v>
+        <v>128970913</v>
       </c>
       <c r="B80" t="n">
-        <v>91497</v>
+        <v>80145</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8301,10 +8301,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>585554</v>
+        <v>585764</v>
       </c>
       <c r="R80" t="n">
-        <v>7212186</v>
+        <v>7212207</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8557,32 +8557,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128970979</v>
+        <v>128970995</v>
       </c>
       <c r="B83" t="n">
-        <v>83015</v>
+        <v>80173</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>585258</v>
+        <v>585119</v>
       </c>
       <c r="R83" t="n">
-        <v>7212103</v>
+        <v>7212238</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8654,10 +8654,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128970920</v>
+        <v>128971006</v>
       </c>
       <c r="B84" t="n">
-        <v>80144</v>
+        <v>80145</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8665,21 +8665,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>584863</v>
+        <v>584919</v>
       </c>
       <c r="R84" t="n">
-        <v>7212236</v>
+        <v>7211893</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8739,22 +8739,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128970937</v>
+        <v>128971047</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>91551</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8762,21 +8762,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>584860</v>
+        <v>585131</v>
       </c>
       <c r="R85" t="n">
-        <v>7212204</v>
+        <v>7212210</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8816,17 +8816,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8835,29 +8830,28 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128971006</v>
+        <v>128970979</v>
       </c>
       <c r="B86" t="n">
-        <v>80145</v>
+        <v>83015</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8865,21 +8859,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8889,10 +8883,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>584919</v>
+        <v>585258</v>
       </c>
       <c r="R86" t="n">
-        <v>7211893</v>
+        <v>7212103</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8919,12 +8913,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -8944,17 +8938,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128970927</v>
+        <v>128970920</v>
       </c>
       <c r="B87" t="n">
-        <v>91529</v>
+        <v>80144</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8962,21 +8956,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8986,10 +8980,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>584905</v>
+        <v>584863</v>
       </c>
       <c r="R87" t="n">
-        <v>7212234</v>
+        <v>7212236</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9048,10 +9042,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128971047</v>
+        <v>128970937</v>
       </c>
       <c r="B88" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9059,21 +9053,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9083,10 +9077,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>585131</v>
+        <v>584860</v>
       </c>
       <c r="R88" t="n">
-        <v>7212210</v>
+        <v>7212204</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9113,12 +9107,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9127,50 +9126,51 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128970995</v>
+        <v>128970927</v>
       </c>
       <c r="B89" t="n">
-        <v>80173</v>
+        <v>91529</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9180,10 +9180,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>585119</v>
+        <v>584905</v>
       </c>
       <c r="R89" t="n">
-        <v>7212238</v>
+        <v>7212234</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9210,12 +9210,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9230,22 +9230,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128971051</v>
+        <v>128970914</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>58155</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9253,21 +9253,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9277,10 +9277,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>585414</v>
+        <v>585431</v>
       </c>
       <c r="R90" t="n">
-        <v>7212007</v>
+        <v>7212208</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9307,12 +9307,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9327,44 +9327,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128970914</v>
+        <v>128970924</v>
       </c>
       <c r="B91" t="n">
-        <v>58155</v>
+        <v>58095</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>585431</v>
+        <v>585103</v>
       </c>
       <c r="R91" t="n">
-        <v>7212208</v>
+        <v>7212451</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9436,32 +9436,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128970924</v>
+        <v>128971051</v>
       </c>
       <c r="B92" t="n">
-        <v>58095</v>
+        <v>79039</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9471,10 +9471,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>585103</v>
+        <v>585414</v>
       </c>
       <c r="R92" t="n">
-        <v>7212451</v>
+        <v>7212007</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9521,12 +9521,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9925,32 +9925,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128970919</v>
+        <v>128971003</v>
       </c>
       <c r="B97" t="n">
-        <v>80172</v>
+        <v>80145</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>585565</v>
+        <v>585171</v>
       </c>
       <c r="R97" t="n">
-        <v>7212131</v>
+        <v>7212170</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -9990,12 +9990,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10010,44 +10010,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128971026</v>
+        <v>128971008</v>
       </c>
       <c r="B98" t="n">
-        <v>80172</v>
+        <v>80145</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10057,10 +10057,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585477</v>
+        <v>585432</v>
       </c>
       <c r="R98" t="n">
-        <v>7211932</v>
+        <v>7211815</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10119,10 +10119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128970994</v>
+        <v>128970919</v>
       </c>
       <c r="B99" t="n">
-        <v>80173</v>
+        <v>80172</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10130,21 +10130,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10154,10 +10154,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>585434</v>
+        <v>585565</v>
       </c>
       <c r="R99" t="n">
-        <v>7211822</v>
+        <v>7212131</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10204,44 +10204,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128970957</v>
+        <v>128971026</v>
       </c>
       <c r="B100" t="n">
-        <v>83007</v>
+        <v>80172</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>308</v>
+        <v>6461</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>585399</v>
+        <v>585477</v>
       </c>
       <c r="R100" t="n">
-        <v>7212426</v>
+        <v>7211932</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10281,12 +10281,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10301,44 +10301,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128971059</v>
+        <v>128970994</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>80173</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10348,10 +10348,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>585592</v>
+        <v>585434</v>
       </c>
       <c r="R101" t="n">
-        <v>7212039</v>
+        <v>7211822</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10378,12 +10378,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10403,17 +10403,17 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128971003</v>
+        <v>128970957</v>
       </c>
       <c r="B102" t="n">
-        <v>80145</v>
+        <v>83007</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10421,21 +10421,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>585171</v>
+        <v>585399</v>
       </c>
       <c r="R102" t="n">
-        <v>7212170</v>
+        <v>7212426</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10475,12 +10475,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10495,22 +10495,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128971008</v>
+        <v>128971059</v>
       </c>
       <c r="B103" t="n">
-        <v>80145</v>
+        <v>79039</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10518,21 +10518,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585432</v>
+        <v>585592</v>
       </c>
       <c r="R103" t="n">
-        <v>7211815</v>
+        <v>7212039</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10572,12 +10572,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10895,32 +10895,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128971002</v>
+        <v>128971010</v>
       </c>
       <c r="B107" t="n">
-        <v>83013</v>
+        <v>80145</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6486</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585321</v>
+        <v>585204</v>
       </c>
       <c r="R107" t="n">
-        <v>7212053</v>
+        <v>7212304</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10992,32 +10992,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128970956</v>
+        <v>128970933</v>
       </c>
       <c r="B108" t="n">
-        <v>80179</v>
+        <v>91551</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585564</v>
+        <v>585051</v>
       </c>
       <c r="R108" t="n">
-        <v>7212138</v>
+        <v>7212128</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11082,17 +11082,17 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128970901</v>
+        <v>128970886</v>
       </c>
       <c r="B109" t="n">
-        <v>80173</v>
+        <v>91497</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11100,21 +11100,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585719</v>
+        <v>585385</v>
       </c>
       <c r="R109" t="n">
-        <v>7212168</v>
+        <v>7212233</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11186,32 +11186,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128971032</v>
+        <v>128971002</v>
       </c>
       <c r="B110" t="n">
-        <v>80180</v>
+        <v>83013</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6464</v>
+        <v>6486</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585204</v>
+        <v>585321</v>
       </c>
       <c r="R110" t="n">
-        <v>7212303</v>
+        <v>7212053</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11283,10 +11283,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128970886</v>
+        <v>128970956</v>
       </c>
       <c r="B111" t="n">
-        <v>91497</v>
+        <v>80179</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11294,21 +11294,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11318,10 +11318,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585385</v>
+        <v>585564</v>
       </c>
       <c r="R111" t="n">
-        <v>7212233</v>
+        <v>7212138</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11373,17 +11373,17 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128971024</v>
+        <v>128970901</v>
       </c>
       <c r="B112" t="n">
-        <v>97546</v>
+        <v>80173</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11391,21 +11391,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585308</v>
+        <v>585719</v>
       </c>
       <c r="R112" t="n">
-        <v>7211853</v>
+        <v>7212168</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11465,22 +11465,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128971043</v>
+        <v>128971032</v>
       </c>
       <c r="B113" t="n">
-        <v>82998</v>
+        <v>80180</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11488,21 +11488,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6439</v>
+        <v>6464</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585466</v>
+        <v>585204</v>
       </c>
       <c r="R113" t="n">
-        <v>7211980</v>
+        <v>7212303</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11574,32 +11574,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128970980</v>
+        <v>128971043</v>
       </c>
       <c r="B114" t="n">
-        <v>83015</v>
+        <v>82998</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585330</v>
+        <v>585466</v>
       </c>
       <c r="R114" t="n">
-        <v>7212026</v>
+        <v>7211980</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11664,17 +11664,17 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128971010</v>
+        <v>128970980</v>
       </c>
       <c r="B115" t="n">
-        <v>80145</v>
+        <v>83015</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11682,21 +11682,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11706,10 +11706,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585204</v>
+        <v>585330</v>
       </c>
       <c r="R115" t="n">
-        <v>7212304</v>
+        <v>7212026</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11761,17 +11761,17 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128970933</v>
+        <v>128971021</v>
       </c>
       <c r="B116" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11779,21 +11779,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11803,10 +11803,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>585051</v>
+        <v>585207</v>
       </c>
       <c r="R116" t="n">
-        <v>7212128</v>
+        <v>7211876</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11841,6 +11841,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -11853,44 +11858,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128971021</v>
+        <v>128971024</v>
       </c>
       <c r="B117" t="n">
-        <v>57725</v>
+        <v>97546</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11900,10 +11905,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585207</v>
+        <v>585308</v>
       </c>
       <c r="R117" t="n">
-        <v>7211876</v>
+        <v>7211853</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11936,11 +11941,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12749,32 +12749,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128970902</v>
+        <v>128971017</v>
       </c>
       <c r="B126" t="n">
-        <v>80173</v>
+        <v>91988</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12784,10 +12784,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>585764</v>
+        <v>585476</v>
       </c>
       <c r="R126" t="n">
-        <v>7212207</v>
+        <v>7211928</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12814,12 +12814,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -12834,44 +12834,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128971017</v>
+        <v>128970889</v>
       </c>
       <c r="B127" t="n">
-        <v>91988</v>
+        <v>91533</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12881,10 +12881,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>585476</v>
+        <v>585054</v>
       </c>
       <c r="R127" t="n">
-        <v>7211928</v>
+        <v>7212128</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12911,12 +12911,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -12931,22 +12931,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128970889</v>
+        <v>128970950</v>
       </c>
       <c r="B128" t="n">
-        <v>91533</v>
+        <v>82902</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12954,21 +12954,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>585054</v>
+        <v>585064</v>
       </c>
       <c r="R128" t="n">
-        <v>7212128</v>
+        <v>7212391</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13033,39 +13033,39 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128970950</v>
+        <v>128970902</v>
       </c>
       <c r="B129" t="n">
-        <v>82902</v>
+        <v>80173</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13075,10 +13075,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>585064</v>
+        <v>585764</v>
       </c>
       <c r="R129" t="n">
-        <v>7212391</v>
+        <v>7212207</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13130,39 +13130,39 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128970892</v>
+        <v>128971058</v>
       </c>
       <c r="B130" t="n">
-        <v>56915</v>
+        <v>79039</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13172,10 +13172,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>585431</v>
+        <v>585445</v>
       </c>
       <c r="R130" t="n">
-        <v>7212208</v>
+        <v>7211833</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13222,22 +13222,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128971058</v>
+        <v>128970908</v>
       </c>
       <c r="B131" t="n">
-        <v>79039</v>
+        <v>80145</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13245,21 +13245,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13269,10 +13269,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>585445</v>
+        <v>585176</v>
       </c>
       <c r="R131" t="n">
-        <v>7211833</v>
+        <v>7212008</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13319,22 +13319,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128970908</v>
+        <v>128971014</v>
       </c>
       <c r="B132" t="n">
-        <v>80145</v>
+        <v>83020</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13342,21 +13342,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13366,10 +13366,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>585176</v>
+        <v>585266</v>
       </c>
       <c r="R132" t="n">
-        <v>7212008</v>
+        <v>7212088</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13396,12 +13396,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13416,44 +13416,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128971014</v>
+        <v>128970892</v>
       </c>
       <c r="B133" t="n">
-        <v>83020</v>
+        <v>56915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1467</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13463,10 +13463,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>585266</v>
+        <v>585431</v>
       </c>
       <c r="R133" t="n">
-        <v>7212088</v>
+        <v>7212208</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13493,12 +13493,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -13513,12 +13513,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -15767,10 +15767,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128970910</v>
+        <v>128971077</v>
       </c>
       <c r="B157" t="n">
-        <v>80145</v>
+        <v>83007</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15778,21 +15778,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -15802,10 +15802,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>585587</v>
+        <v>585464</v>
       </c>
       <c r="R157" t="n">
-        <v>7212109</v>
+        <v>7211979</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -15832,12 +15832,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -15852,44 +15852,44 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128971077</v>
+        <v>128971041</v>
       </c>
       <c r="B158" t="n">
-        <v>83007</v>
+        <v>82998</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -15899,10 +15899,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>585464</v>
+        <v>585389</v>
       </c>
       <c r="R158" t="n">
-        <v>7211979</v>
+        <v>7212014</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -15961,32 +15961,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128971041</v>
+        <v>128970949</v>
       </c>
       <c r="B159" t="n">
-        <v>82998</v>
+        <v>79039</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -15996,10 +15996,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>585389</v>
+        <v>585698</v>
       </c>
       <c r="R159" t="n">
-        <v>7212014</v>
+        <v>7212166</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16026,12 +16026,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16046,19 +16046,19 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128970949</v>
+        <v>128971065</v>
       </c>
       <c r="B160" t="n">
         <v>79039</v>
@@ -16093,10 +16093,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>585698</v>
+        <v>585476</v>
       </c>
       <c r="R160" t="n">
-        <v>7212166</v>
+        <v>7211994</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16123,12 +16123,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16143,22 +16143,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128971065</v>
+        <v>128970977</v>
       </c>
       <c r="B161" t="n">
-        <v>79039</v>
+        <v>83015</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16166,21 +16166,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>585476</v>
+        <v>585241</v>
       </c>
       <c r="R161" t="n">
-        <v>7211994</v>
+        <v>7212290</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16252,10 +16252,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128970977</v>
+        <v>128970910</v>
       </c>
       <c r="B162" t="n">
-        <v>83015</v>
+        <v>80145</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16263,21 +16263,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16287,10 +16287,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>585241</v>
+        <v>585587</v>
       </c>
       <c r="R162" t="n">
-        <v>7212290</v>
+        <v>7212109</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16317,12 +16317,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16337,12 +16337,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -16645,10 +16645,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128970915</v>
+        <v>128970926</v>
       </c>
       <c r="B166" t="n">
-        <v>83020</v>
+        <v>91529</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16656,21 +16656,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -16680,10 +16680,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>585399</v>
+        <v>584975</v>
       </c>
       <c r="R166" t="n">
-        <v>7212426</v>
+        <v>7212272</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -16742,10 +16742,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128971016</v>
+        <v>128970934</v>
       </c>
       <c r="B167" t="n">
-        <v>83020</v>
+        <v>91551</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16753,21 +16753,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -16777,10 +16777,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>585463</v>
+        <v>584956</v>
       </c>
       <c r="R167" t="n">
-        <v>7211979</v>
+        <v>7212144</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -16807,12 +16807,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -16827,22 +16827,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128971005</v>
+        <v>128971029</v>
       </c>
       <c r="B168" t="n">
-        <v>80145</v>
+        <v>80144</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16850,21 +16850,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -16874,10 +16874,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>584915</v>
+        <v>585439</v>
       </c>
       <c r="R168" t="n">
-        <v>7211903</v>
+        <v>7211959</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -16904,12 +16904,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -16936,32 +16936,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128970907</v>
+        <v>128971070</v>
       </c>
       <c r="B169" t="n">
-        <v>80145</v>
+        <v>80179</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -16971,10 +16971,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>585322</v>
+        <v>585168</v>
       </c>
       <c r="R169" t="n">
-        <v>7211897</v>
+        <v>7212176</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17001,12 +17001,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17021,22 +17021,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128971029</v>
+        <v>128971073</v>
       </c>
       <c r="B170" t="n">
-        <v>80144</v>
+        <v>83007</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17044,21 +17044,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17068,10 +17068,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>585439</v>
+        <v>585334</v>
       </c>
       <c r="R170" t="n">
-        <v>7211959</v>
+        <v>7212000</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17130,10 +17130,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128971070</v>
+        <v>128970986</v>
       </c>
       <c r="B171" t="n">
-        <v>80179</v>
+        <v>92233</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17141,21 +17141,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6463</v>
+        <v>3298</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17165,10 +17165,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>585168</v>
+        <v>584943</v>
       </c>
       <c r="R171" t="n">
-        <v>7212176</v>
+        <v>7211913</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17195,12 +17195,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17220,17 +17220,17 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128971073</v>
+        <v>128970976</v>
       </c>
       <c r="B172" t="n">
-        <v>83007</v>
+        <v>83015</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17238,21 +17238,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17262,10 +17262,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>585334</v>
+        <v>584777</v>
       </c>
       <c r="R172" t="n">
-        <v>7212000</v>
+        <v>7211899</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17292,12 +17292,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -17324,32 +17324,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128970986</v>
+        <v>128971028</v>
       </c>
       <c r="B173" t="n">
-        <v>92233</v>
+        <v>80144</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17359,10 +17359,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>584943</v>
+        <v>585603</v>
       </c>
       <c r="R173" t="n">
-        <v>7211913</v>
+        <v>7212039</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17389,12 +17389,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -17414,17 +17414,17 @@
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128970976</v>
+        <v>128970940</v>
       </c>
       <c r="B174" t="n">
-        <v>83015</v>
+        <v>79039</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17432,21 +17432,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17456,10 +17456,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>584777</v>
+        <v>585683</v>
       </c>
       <c r="R174" t="n">
-        <v>7211899</v>
+        <v>7212167</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17494,34 +17494,40 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128971028</v>
+        <v>128971064</v>
       </c>
       <c r="B175" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17529,21 +17535,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17553,10 +17559,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>585603</v>
+        <v>585286</v>
       </c>
       <c r="R175" t="n">
-        <v>7212039</v>
+        <v>7212090</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -17615,10 +17621,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128970940</v>
+        <v>128970915</v>
       </c>
       <c r="B176" t="n">
-        <v>79039</v>
+        <v>83020</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17626,21 +17632,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -17650,10 +17656,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>585683</v>
+        <v>585399</v>
       </c>
       <c r="R176" t="n">
-        <v>7212167</v>
+        <v>7212426</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -17688,18 +17694,12 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -17711,17 +17711,17 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128971064</v>
+        <v>128971016</v>
       </c>
       <c r="B177" t="n">
-        <v>79039</v>
+        <v>83020</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17729,21 +17729,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -17753,10 +17753,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>585286</v>
+        <v>585463</v>
       </c>
       <c r="R177" t="n">
-        <v>7212090</v>
+        <v>7211979</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -17815,10 +17815,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128970926</v>
+        <v>128971005</v>
       </c>
       <c r="B178" t="n">
-        <v>91529</v>
+        <v>80145</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17826,21 +17826,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -17850,10 +17850,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>584975</v>
+        <v>584915</v>
       </c>
       <c r="R178" t="n">
-        <v>7212272</v>
+        <v>7211903</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -17900,22 +17900,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128970930</v>
+        <v>128970907</v>
       </c>
       <c r="B179" t="n">
-        <v>91529</v>
+        <v>80145</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17923,21 +17923,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -17947,10 +17947,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>585653</v>
+        <v>585322</v>
       </c>
       <c r="R179" t="n">
-        <v>7212149</v>
+        <v>7211897</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18009,10 +18009,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128970934</v>
+        <v>128970930</v>
       </c>
       <c r="B180" t="n">
-        <v>91551</v>
+        <v>91529</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18020,21 +18020,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18044,10 +18044,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>584956</v>
+        <v>585653</v>
       </c>
       <c r="R180" t="n">
-        <v>7212144</v>
+        <v>7212149</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18099,17 +18099,17 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128970999</v>
+        <v>128971027</v>
       </c>
       <c r="B181" t="n">
-        <v>57722</v>
+        <v>80144</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18117,21 +18117,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18141,10 +18141,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>585469</v>
+        <v>585336</v>
       </c>
       <c r="R181" t="n">
-        <v>7211944</v>
+        <v>7211875</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18171,17 +18171,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Hack på låga</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18190,8 +18185,24 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
@@ -18201,17 +18212,17 @@
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128970948</v>
+        <v>128970999</v>
       </c>
       <c r="B182" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18219,21 +18230,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18243,10 +18254,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>585646</v>
+        <v>585469</v>
       </c>
       <c r="R182" t="n">
-        <v>7212110</v>
+        <v>7211944</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18273,12 +18284,17 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Hack på låga</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -18293,22 +18309,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128970942</v>
+        <v>128971011</v>
       </c>
       <c r="B183" t="n">
-        <v>79039</v>
+        <v>80145</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18316,21 +18332,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18340,10 +18356,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>585047</v>
+        <v>585263</v>
       </c>
       <c r="R183" t="n">
-        <v>7212054</v>
+        <v>7212085</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18370,12 +18386,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -18390,12 +18406,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -18499,10 +18515,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128971027</v>
+        <v>128970948</v>
       </c>
       <c r="B185" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18510,21 +18526,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18534,10 +18550,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>585336</v>
+        <v>585646</v>
       </c>
       <c r="R185" t="n">
-        <v>7211875</v>
+        <v>7212110</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18578,44 +18594,28 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128971011</v>
+        <v>128970942</v>
       </c>
       <c r="B186" t="n">
-        <v>80145</v>
+        <v>79039</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18623,21 +18623,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18647,10 +18647,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>585263</v>
+        <v>585047</v>
       </c>
       <c r="R186" t="n">
-        <v>7212085</v>
+        <v>7212054</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18677,12 +18677,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -18697,12 +18697,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
@@ -19800,32 +19800,32 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128995941</v>
+        <v>128995956</v>
       </c>
       <c r="B198" t="n">
-        <v>91529</v>
+        <v>80179</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -19835,10 +19835,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>584945</v>
+        <v>585314</v>
       </c>
       <c r="R198" t="n">
-        <v>7211920</v>
+        <v>7211978</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -19865,12 +19865,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -19897,10 +19897,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128995952</v>
+        <v>128995941</v>
       </c>
       <c r="B199" t="n">
-        <v>82902</v>
+        <v>91529</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19908,21 +19908,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -19932,10 +19932,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>584830</v>
+        <v>584945</v>
       </c>
       <c r="R199" t="n">
-        <v>7212146</v>
+        <v>7211920</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -19994,32 +19994,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128995956</v>
+        <v>128995952</v>
       </c>
       <c r="B200" t="n">
-        <v>80179</v>
+        <v>82902</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20029,10 +20029,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>585314</v>
+        <v>584830</v>
       </c>
       <c r="R200" t="n">
-        <v>7211978</v>
+        <v>7212146</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20059,12 +20059,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -20091,32 +20091,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128995938</v>
+        <v>128995828</v>
       </c>
       <c r="B201" t="n">
-        <v>78796</v>
+        <v>56915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20126,10 +20126,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>585313</v>
+        <v>585296</v>
       </c>
       <c r="R201" t="n">
-        <v>7212215</v>
+        <v>7212121</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20176,39 +20176,39 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128995867</v>
+        <v>128995955</v>
       </c>
       <c r="B202" t="n">
-        <v>79039</v>
+        <v>80179</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -20223,10 +20223,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>585364</v>
+        <v>584836</v>
       </c>
       <c r="R202" t="n">
-        <v>7211892</v>
+        <v>7212031</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20273,44 +20273,44 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128995984</v>
+        <v>128996034</v>
       </c>
       <c r="B203" t="n">
-        <v>80145</v>
+        <v>80179</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20320,10 +20320,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>585176</v>
+        <v>585497</v>
       </c>
       <c r="R203" t="n">
-        <v>7212169</v>
+        <v>7212005</v>
       </c>
       <c r="S203" t="n">
         <v>15</v>
@@ -20387,32 +20387,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128995914</v>
+        <v>128995934</v>
       </c>
       <c r="B204" t="n">
-        <v>80145</v>
+        <v>80180</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20422,10 +20422,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>585318</v>
+        <v>585213</v>
       </c>
       <c r="R204" t="n">
-        <v>7211888</v>
+        <v>7212298</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20484,10 +20484,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128995925</v>
+        <v>128995938</v>
       </c>
       <c r="B205" t="n">
-        <v>93022</v>
+        <v>78796</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20495,21 +20495,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -20519,10 +20519,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>585205</v>
+        <v>585313</v>
       </c>
       <c r="R205" t="n">
-        <v>7212472</v>
+        <v>7212215</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20549,12 +20549,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -20581,27 +20581,27 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128995955</v>
+        <v>128995867</v>
       </c>
       <c r="B206" t="n">
-        <v>80179</v>
+        <v>79039</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -20616,10 +20616,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>584836</v>
+        <v>585364</v>
       </c>
       <c r="R206" t="n">
-        <v>7212031</v>
+        <v>7211892</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -20666,44 +20666,44 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128996034</v>
+        <v>128995984</v>
       </c>
       <c r="B207" t="n">
-        <v>80179</v>
+        <v>80145</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -20713,10 +20713,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>585497</v>
+        <v>585176</v>
       </c>
       <c r="R207" t="n">
-        <v>7212005</v>
+        <v>7212169</v>
       </c>
       <c r="S207" t="n">
         <v>15</v>
@@ -20780,32 +20780,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128995934</v>
+        <v>128995914</v>
       </c>
       <c r="B208" t="n">
-        <v>80180</v>
+        <v>80145</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -20815,10 +20815,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>585213</v>
+        <v>585318</v>
       </c>
       <c r="R208" t="n">
-        <v>7212298</v>
+        <v>7211888</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -20877,32 +20877,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128995828</v>
+        <v>128995925</v>
       </c>
       <c r="B209" t="n">
-        <v>56915</v>
+        <v>93022</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -20912,10 +20912,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>585296</v>
+        <v>585205</v>
       </c>
       <c r="R209" t="n">
-        <v>7212121</v>
+        <v>7212472</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -20942,12 +20942,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -20962,12 +20962,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
@@ -22163,32 +22163,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128996026</v>
+        <v>128996001</v>
       </c>
       <c r="B222" t="n">
-        <v>79039</v>
+        <v>97546</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22198,10 +22198,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>585489</v>
+        <v>585205</v>
       </c>
       <c r="R222" t="n">
-        <v>7211976</v>
+        <v>7212417</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -22228,12 +22228,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -22556,32 +22556,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128996001</v>
+        <v>128996026</v>
       </c>
       <c r="B226" t="n">
-        <v>97546</v>
+        <v>79039</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -22591,10 +22591,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>585205</v>
+        <v>585489</v>
       </c>
       <c r="R226" t="n">
-        <v>7212417</v>
+        <v>7211976</v>
       </c>
       <c r="S226" t="n">
         <v>15</v>
@@ -22621,12 +22621,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -23076,10 +23076,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128996000</v>
+        <v>128995838</v>
       </c>
       <c r="B231" t="n">
-        <v>97540</v>
+        <v>80172</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23087,37 +23087,37 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>585440</v>
+        <v>584779</v>
       </c>
       <c r="R231" t="n">
-        <v>7212032</v>
+        <v>7211856</v>
       </c>
       <c r="S231" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -23141,12 +23141,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -23157,69 +23157,64 @@
       </c>
       <c r="AG231" t="b">
         <v>0</v>
-      </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128995947</v>
+        <v>128996000</v>
       </c>
       <c r="B232" t="n">
-        <v>79039</v>
+        <v>97540</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>585239</v>
+        <v>585440</v>
       </c>
       <c r="R232" t="n">
-        <v>7211879</v>
+        <v>7212032</v>
       </c>
       <c r="S232" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -23243,12 +23238,12 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -23259,26 +23254,31 @@
       </c>
       <c r="AG232" t="b">
         <v>0</v>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128995902</v>
+        <v>128995947</v>
       </c>
       <c r="B233" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23286,21 +23286,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -23310,10 +23310,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>584932</v>
+        <v>585239</v>
       </c>
       <c r="R233" t="n">
-        <v>7211934</v>
+        <v>7211879</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23365,17 +23365,17 @@
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128995995</v>
+        <v>128995902</v>
       </c>
       <c r="B234" t="n">
-        <v>57725</v>
+        <v>91533</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23383,41 +23383,37 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>584838</v>
+        <v>584932</v>
       </c>
       <c r="R234" t="n">
-        <v>7212145</v>
+        <v>7211934</v>
       </c>
       <c r="S234" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -23449,11 +23445,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD234" t="b">
         <v>0</v>
       </c>
@@ -23462,28 +23453,23 @@
       </c>
       <c r="AG234" t="b">
         <v>0</v>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128995994</v>
+        <v>128995995</v>
       </c>
       <c r="B235" t="n">
         <v>57725</v>
@@ -23522,10 +23508,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>584839</v>
+        <v>584838</v>
       </c>
       <c r="R235" t="n">
-        <v>7212144</v>
+        <v>7212145</v>
       </c>
       <c r="S235" t="n">
         <v>15</v>
@@ -23562,7 +23548,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -23594,48 +23580,52 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128995838</v>
+        <v>128995994</v>
       </c>
       <c r="B236" t="n">
-        <v>80172</v>
+        <v>57725</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>584779</v>
+        <v>584839</v>
       </c>
       <c r="R236" t="n">
-        <v>7211856</v>
+        <v>7212144</v>
       </c>
       <c r="S236" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -23667,6 +23657,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD236" t="b">
         <v>0</v>
       </c>
@@ -23675,16 +23670,21 @@
       </c>
       <c r="AG236" t="b">
         <v>0</v>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
@@ -25064,45 +25064,45 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128971038</v>
+        <v>128995942</v>
       </c>
       <c r="B251" t="n">
-        <v>56299</v>
+        <v>82998</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>206004</v>
+        <v>6439</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Inre Verkansliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>585281</v>
+        <v>585375</v>
       </c>
       <c r="R251" t="n">
-        <v>7212091</v>
+        <v>7212068</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25149,44 +25149,44 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128995942</v>
+        <v>128995915</v>
       </c>
       <c r="B252" t="n">
-        <v>82998</v>
+        <v>80145</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25196,10 +25196,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>585375</v>
+        <v>585212</v>
       </c>
       <c r="R252" t="n">
-        <v>7212068</v>
+        <v>7212298</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -25258,10 +25258,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128995915</v>
+        <v>128971038</v>
       </c>
       <c r="B253" t="n">
-        <v>80145</v>
+        <v>56299</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -25269,34 +25269,34 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2081</v>
+        <v>206004</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>585212</v>
+        <v>585281</v>
       </c>
       <c r="R253" t="n">
-        <v>7212298</v>
+        <v>7212091</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -25343,22 +25343,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128995950</v>
+        <v>128995926</v>
       </c>
       <c r="B254" t="n">
-        <v>79039</v>
+        <v>83010</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -25366,21 +25366,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -25390,10 +25390,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>585251</v>
+        <v>585749</v>
       </c>
       <c r="R254" t="n">
-        <v>7212276</v>
+        <v>7212196</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -25420,12 +25420,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -25452,10 +25452,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128996022</v>
+        <v>128995982</v>
       </c>
       <c r="B255" t="n">
-        <v>91551</v>
+        <v>80145</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -25463,21 +25463,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -25487,10 +25487,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>585044</v>
+        <v>585762</v>
       </c>
       <c r="R255" t="n">
-        <v>7212452</v>
+        <v>7212189</v>
       </c>
       <c r="S255" t="n">
         <v>15</v>
@@ -25554,10 +25554,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128995992</v>
+        <v>128996022</v>
       </c>
       <c r="B256" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -25565,38 +25565,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
-      <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>584913</v>
+        <v>585044</v>
       </c>
       <c r="R256" t="n">
-        <v>7211982</v>
+        <v>7212452</v>
       </c>
       <c r="S256" t="n">
         <v>15</v>
@@ -25629,11 +25625,6 @@
       <c r="AA256" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -25665,10 +25656,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128995982</v>
+        <v>128995992</v>
       </c>
       <c r="B257" t="n">
-        <v>80145</v>
+        <v>57725</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -25676,34 +25667,38 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>585762</v>
+        <v>584913</v>
       </c>
       <c r="R257" t="n">
-        <v>7212189</v>
+        <v>7211982</v>
       </c>
       <c r="S257" t="n">
         <v>15</v>
@@ -25736,6 +25731,11 @@
       <c r="AA257" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -25767,10 +25767,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128995926</v>
+        <v>128995950</v>
       </c>
       <c r="B258" t="n">
-        <v>83010</v>
+        <v>79039</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -25778,21 +25778,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -25802,10 +25802,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>585749</v>
+        <v>585251</v>
       </c>
       <c r="R258" t="n">
-        <v>7212196</v>
+        <v>7212276</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -25832,12 +25832,12 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -25966,48 +25966,48 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128996043</v>
+        <v>128995958</v>
       </c>
       <c r="B260" t="n">
-        <v>88930</v>
+        <v>80179</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>585400</v>
+        <v>585463</v>
       </c>
       <c r="R260" t="n">
-        <v>7212315</v>
+        <v>7211957</v>
       </c>
       <c r="S260" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -26047,53 +26047,48 @@
       </c>
       <c r="AG260" t="b">
         <v>0</v>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128995958</v>
+        <v>128995929</v>
       </c>
       <c r="B261" t="n">
-        <v>80179</v>
+        <v>80144</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26103,10 +26098,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>585463</v>
+        <v>584848</v>
       </c>
       <c r="R261" t="n">
-        <v>7211957</v>
+        <v>7212088</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26133,12 +26128,12 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -26165,10 +26160,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128995929</v>
+        <v>128996043</v>
       </c>
       <c r="B262" t="n">
-        <v>80144</v>
+        <v>88930</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26176,37 +26171,37 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>584848</v>
+        <v>585400</v>
       </c>
       <c r="R262" t="n">
-        <v>7212088</v>
+        <v>7212315</v>
       </c>
       <c r="S262" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -26246,16 +26241,21 @@
       </c>
       <c r="AG262" t="b">
         <v>0</v>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
@@ -26767,48 +26767,48 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128995965</v>
+        <v>128995874</v>
       </c>
       <c r="B268" t="n">
-        <v>105717</v>
+        <v>79039</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>585233</v>
+        <v>585370</v>
       </c>
       <c r="R268" t="n">
-        <v>7212183</v>
+        <v>7211866</v>
       </c>
       <c r="S268" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -26832,12 +26832,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -26848,69 +26848,64 @@
       </c>
       <c r="AG268" t="b">
         <v>0</v>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128995874</v>
+        <v>128995965</v>
       </c>
       <c r="B269" t="n">
-        <v>79039</v>
+        <v>105717</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>585370</v>
+        <v>585233</v>
       </c>
       <c r="R269" t="n">
-        <v>7211866</v>
+        <v>7212183</v>
       </c>
       <c r="S269" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -26934,12 +26929,12 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -26950,16 +26945,21 @@
       </c>
       <c r="AG269" t="b">
         <v>0</v>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
@@ -27257,32 +27257,32 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128995906</v>
+        <v>128995830</v>
       </c>
       <c r="B273" t="n">
-        <v>80173</v>
+        <v>57885</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27292,10 +27292,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>584836</v>
+        <v>585373</v>
       </c>
       <c r="R273" t="n">
-        <v>7212031</v>
+        <v>7211857</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27342,22 +27342,22 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128995936</v>
+        <v>128995906</v>
       </c>
       <c r="B274" t="n">
-        <v>80180</v>
+        <v>80173</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -27365,21 +27365,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -27389,10 +27389,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>585498</v>
+        <v>584836</v>
       </c>
       <c r="R274" t="n">
-        <v>7211887</v>
+        <v>7212031</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -27419,12 +27419,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -27444,59 +27444,55 @@
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128995993</v>
+        <v>128995936</v>
       </c>
       <c r="B275" t="n">
-        <v>57725</v>
+        <v>80180</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>584850</v>
+        <v>585498</v>
       </c>
       <c r="R275" t="n">
-        <v>7212144</v>
+        <v>7211887</v>
       </c>
       <c r="S275" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -27520,17 +27516,12 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -27541,31 +27532,26 @@
       </c>
       <c r="AG275" t="b">
         <v>0</v>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128995830</v>
+        <v>128995993</v>
       </c>
       <c r="B276" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -27573,37 +27559,41 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>585373</v>
+        <v>584850</v>
       </c>
       <c r="R276" t="n">
-        <v>7211857</v>
+        <v>7212144</v>
       </c>
       <c r="S276" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -27635,6 +27625,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD276" t="b">
         <v>0</v>
       </c>
@@ -27643,16 +27638,21 @@
       </c>
       <c r="AG276" t="b">
         <v>0</v>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>

--- a/artfynd/A 45899-2025 artfynd.xlsx
+++ b/artfynd/A 45899-2025 artfynd.xlsx
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128952841</v>
+        <v>128952838</v>
       </c>
       <c r="B29" t="n">
-        <v>80174</v>
+        <v>97555</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585473</v>
+        <v>585402</v>
       </c>
       <c r="R29" t="n">
-        <v>7211954</v>
+        <v>7212035</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3391,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128952860</v>
+        <v>128952837</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>97555</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585411</v>
+        <v>585315</v>
       </c>
       <c r="R30" t="n">
-        <v>7212074</v>
+        <v>7212252</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128952838</v>
+        <v>128952841</v>
       </c>
       <c r="B31" t="n">
-        <v>97555</v>
+        <v>80174</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3499,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585402</v>
+        <v>585473</v>
       </c>
       <c r="R31" t="n">
-        <v>7212035</v>
+        <v>7211954</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3585,32 +3585,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128952837</v>
+        <v>128952860</v>
       </c>
       <c r="B32" t="n">
-        <v>97555</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585315</v>
+        <v>585411</v>
       </c>
       <c r="R32" t="n">
-        <v>7212252</v>
+        <v>7212074</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,32 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128970955</v>
+        <v>128971049</v>
       </c>
       <c r="B35" t="n">
-        <v>80181</v>
+        <v>91560</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585580</v>
+        <v>585222</v>
       </c>
       <c r="R35" t="n">
-        <v>7212249</v>
+        <v>7212119</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3961,22 +3961,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128970996</v>
+        <v>128970955</v>
       </c>
       <c r="B36" t="n">
-        <v>80175</v>
+        <v>80181</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3984,21 +3984,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585166</v>
+        <v>585580</v>
       </c>
       <c r="R36" t="n">
-        <v>7212177</v>
+        <v>7212249</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4058,44 +4058,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128971049</v>
+        <v>128970996</v>
       </c>
       <c r="B37" t="n">
-        <v>91560</v>
+        <v>80175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585222</v>
+        <v>585166</v>
       </c>
       <c r="R37" t="n">
-        <v>7212119</v>
+        <v>7212177</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -7674,48 +7674,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128970882</v>
+        <v>128971031</v>
       </c>
       <c r="B74" t="n">
-        <v>83007</v>
+        <v>80182</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>585056</v>
+        <v>585387</v>
       </c>
       <c r="R74" t="n">
-        <v>7212089</v>
+        <v>7211820</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7756,29 +7753,28 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128971063</v>
+        <v>128970882</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>83007</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7786,34 +7782,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>585170</v>
+        <v>585056</v>
       </c>
       <c r="R75" t="n">
-        <v>7212187</v>
+        <v>7212089</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7840,12 +7839,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7854,25 +7853,26 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128971055</v>
+        <v>128971063</v>
       </c>
       <c r="B76" t="n">
         <v>79041</v>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>585255</v>
+        <v>585170</v>
       </c>
       <c r="R76" t="n">
-        <v>7212100</v>
+        <v>7212187</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7945,18 +7945,12 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -7975,10 +7969,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128970913</v>
+        <v>128971055</v>
       </c>
       <c r="B77" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7986,21 +7980,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8010,10 +8004,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>585764</v>
+        <v>585255</v>
       </c>
       <c r="R77" t="n">
-        <v>7212207</v>
+        <v>7212100</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8040,12 +8034,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8054,50 +8053,51 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128970918</v>
+        <v>128970913</v>
       </c>
       <c r="B78" t="n">
-        <v>91912</v>
+        <v>80147</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1506</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8107,10 +8107,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>584867</v>
+        <v>585764</v>
       </c>
       <c r="R78" t="n">
-        <v>7212286</v>
+        <v>7212207</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8169,32 +8169,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128970887</v>
+        <v>128970918</v>
       </c>
       <c r="B79" t="n">
-        <v>91506</v>
+        <v>91912</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>1506</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8204,10 +8204,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>585554</v>
+        <v>584867</v>
       </c>
       <c r="R79" t="n">
-        <v>7212186</v>
+        <v>7212286</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8266,10 +8266,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128971031</v>
+        <v>128970887</v>
       </c>
       <c r="B80" t="n">
-        <v>80182</v>
+        <v>91506</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8277,21 +8277,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8301,10 +8301,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>585387</v>
+        <v>585554</v>
       </c>
       <c r="R80" t="n">
-        <v>7211820</v>
+        <v>7212186</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8351,22 +8351,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128971006</v>
+        <v>128970927</v>
       </c>
       <c r="B81" t="n">
-        <v>80147</v>
+        <v>91538</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8374,21 +8374,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8398,10 +8398,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>584919</v>
+        <v>584905</v>
       </c>
       <c r="R81" t="n">
-        <v>7211893</v>
+        <v>7212234</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8448,22 +8448,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128970927</v>
+        <v>128971047</v>
       </c>
       <c r="B82" t="n">
-        <v>91538</v>
+        <v>91560</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8471,21 +8471,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8495,10 +8495,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>584905</v>
+        <v>585131</v>
       </c>
       <c r="R82" t="n">
-        <v>7212234</v>
+        <v>7212210</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8525,12 +8525,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8545,12 +8545,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9145,10 +9145,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128971047</v>
+        <v>128971006</v>
       </c>
       <c r="B89" t="n">
-        <v>91560</v>
+        <v>80147</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9156,21 +9156,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9180,10 +9180,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>585131</v>
+        <v>584919</v>
       </c>
       <c r="R89" t="n">
-        <v>7212210</v>
+        <v>7211893</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9210,12 +9210,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9533,32 +9533,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128970947</v>
+        <v>128970891</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>92242</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9568,10 +9568,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>585544</v>
+        <v>585325</v>
       </c>
       <c r="R93" t="n">
-        <v>7212152</v>
+        <v>7211962</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9623,17 +9623,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128970883</v>
+        <v>128970947</v>
       </c>
       <c r="B94" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9641,37 +9641,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>585518</v>
+        <v>585544</v>
       </c>
       <c r="R94" t="n">
-        <v>7212240</v>
+        <v>7212152</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9712,7 +9709,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9724,17 +9720,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128970904</v>
+        <v>128970883</v>
       </c>
       <c r="B95" t="n">
-        <v>57724</v>
+        <v>83007</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9742,34 +9738,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>584971</v>
+        <v>585518</v>
       </c>
       <c r="R95" t="n">
-        <v>7212140</v>
+        <v>7212240</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9810,6 +9809,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9828,32 +9828,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128970891</v>
+        <v>128970904</v>
       </c>
       <c r="B96" t="n">
-        <v>92242</v>
+        <v>57724</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9863,10 +9863,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>585325</v>
+        <v>584971</v>
       </c>
       <c r="R96" t="n">
-        <v>7211962</v>
+        <v>7212140</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9925,10 +9925,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128971003</v>
+        <v>128970929</v>
       </c>
       <c r="B97" t="n">
-        <v>80147</v>
+        <v>91538</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9936,21 +9936,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>585171</v>
+        <v>584864</v>
       </c>
       <c r="R97" t="n">
-        <v>7212170</v>
+        <v>7212305</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -9990,12 +9990,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10010,22 +10010,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128971008</v>
+        <v>128970957</v>
       </c>
       <c r="B98" t="n">
-        <v>80147</v>
+        <v>82999</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10033,21 +10033,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10057,10 +10057,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585432</v>
+        <v>585399</v>
       </c>
       <c r="R98" t="n">
-        <v>7211815</v>
+        <v>7212426</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10107,22 +10107,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128970929</v>
+        <v>128970932</v>
       </c>
       <c r="B99" t="n">
-        <v>91538</v>
+        <v>91556</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10130,21 +10130,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10154,10 +10154,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>584864</v>
+        <v>584845</v>
       </c>
       <c r="R99" t="n">
-        <v>7212305</v>
+        <v>7212279</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10216,32 +10216,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128970957</v>
+        <v>128970919</v>
       </c>
       <c r="B100" t="n">
-        <v>82999</v>
+        <v>80174</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>308</v>
+        <v>6461</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>585399</v>
+        <v>585565</v>
       </c>
       <c r="R100" t="n">
-        <v>7212426</v>
+        <v>7212131</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10306,39 +10306,39 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128970932</v>
+        <v>128971026</v>
       </c>
       <c r="B101" t="n">
-        <v>91556</v>
+        <v>80174</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>6461</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10348,10 +10348,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>584845</v>
+        <v>585477</v>
       </c>
       <c r="R101" t="n">
-        <v>7212279</v>
+        <v>7211932</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10378,12 +10378,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10398,22 +10398,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128970919</v>
+        <v>128970994</v>
       </c>
       <c r="B102" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10421,21 +10421,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>585565</v>
+        <v>585434</v>
       </c>
       <c r="R102" t="n">
-        <v>7212131</v>
+        <v>7211822</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10495,44 +10495,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128971026</v>
+        <v>128971059</v>
       </c>
       <c r="B103" t="n">
-        <v>80174</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585477</v>
+        <v>585592</v>
       </c>
       <c r="R103" t="n">
-        <v>7211932</v>
+        <v>7212039</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10604,32 +10604,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128970994</v>
+        <v>128971003</v>
       </c>
       <c r="B104" t="n">
-        <v>80175</v>
+        <v>80147</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>585434</v>
+        <v>585171</v>
       </c>
       <c r="R104" t="n">
-        <v>7211822</v>
+        <v>7212170</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10669,12 +10669,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128971059</v>
+        <v>128971008</v>
       </c>
       <c r="B105" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10712,21 +10712,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>585592</v>
+        <v>585432</v>
       </c>
       <c r="R105" t="n">
-        <v>7212039</v>
+        <v>7211815</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10766,12 +10766,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10895,32 +10895,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128971002</v>
+        <v>128970886</v>
       </c>
       <c r="B107" t="n">
-        <v>83005</v>
+        <v>91506</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6486</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585321</v>
+        <v>585385</v>
       </c>
       <c r="R107" t="n">
-        <v>7212053</v>
+        <v>7212233</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10960,12 +10960,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -10980,44 +10980,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128970956</v>
+        <v>128970933</v>
       </c>
       <c r="B108" t="n">
-        <v>80181</v>
+        <v>91560</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585564</v>
+        <v>585051</v>
       </c>
       <c r="R108" t="n">
-        <v>7212138</v>
+        <v>7212128</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11082,39 +11082,39 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128970901</v>
+        <v>128971002</v>
       </c>
       <c r="B109" t="n">
-        <v>80175</v>
+        <v>83005</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6462</v>
+        <v>6486</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585719</v>
+        <v>585321</v>
       </c>
       <c r="R109" t="n">
-        <v>7212168</v>
+        <v>7212053</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11174,22 +11174,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128971032</v>
+        <v>128970956</v>
       </c>
       <c r="B110" t="n">
-        <v>80182</v>
+        <v>80181</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11197,21 +11197,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585204</v>
+        <v>585564</v>
       </c>
       <c r="R110" t="n">
-        <v>7212303</v>
+        <v>7212138</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11251,12 +11251,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11271,44 +11271,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128970980</v>
+        <v>128970901</v>
       </c>
       <c r="B111" t="n">
-        <v>83007</v>
+        <v>80175</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11318,10 +11318,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585330</v>
+        <v>585719</v>
       </c>
       <c r="R111" t="n">
-        <v>7212026</v>
+        <v>7212168</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11368,22 +11368,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128971043</v>
+        <v>128971032</v>
       </c>
       <c r="B112" t="n">
-        <v>82990</v>
+        <v>80182</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11391,21 +11391,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6439</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585466</v>
+        <v>585204</v>
       </c>
       <c r="R112" t="n">
-        <v>7211980</v>
+        <v>7212303</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11477,32 +11477,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128971024</v>
+        <v>128970980</v>
       </c>
       <c r="B113" t="n">
-        <v>97555</v>
+        <v>83007</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>6440</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585308</v>
+        <v>585330</v>
       </c>
       <c r="R113" t="n">
-        <v>7211853</v>
+        <v>7212026</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11542,12 +11542,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11567,39 +11567,39 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128971010</v>
+        <v>128971043</v>
       </c>
       <c r="B114" t="n">
-        <v>80147</v>
+        <v>82990</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585204</v>
+        <v>585466</v>
       </c>
       <c r="R114" t="n">
-        <v>7212304</v>
+        <v>7211980</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11671,32 +11671,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128970886</v>
+        <v>128971010</v>
       </c>
       <c r="B115" t="n">
-        <v>91506</v>
+        <v>80147</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11706,10 +11706,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585385</v>
+        <v>585204</v>
       </c>
       <c r="R115" t="n">
-        <v>7212233</v>
+        <v>7212304</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11756,22 +11756,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128970933</v>
+        <v>128971021</v>
       </c>
       <c r="B116" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11779,21 +11779,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11803,10 +11803,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>585051</v>
+        <v>585207</v>
       </c>
       <c r="R116" t="n">
-        <v>7212128</v>
+        <v>7211876</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11841,6 +11841,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -11853,44 +11858,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128971021</v>
+        <v>128971024</v>
       </c>
       <c r="B117" t="n">
-        <v>57727</v>
+        <v>97555</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11900,10 +11905,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585207</v>
+        <v>585308</v>
       </c>
       <c r="R117" t="n">
-        <v>7211876</v>
+        <v>7211853</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11936,11 +11941,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12846,32 +12846,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128970902</v>
+        <v>128970908</v>
       </c>
       <c r="B127" t="n">
-        <v>80175</v>
+        <v>80147</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12881,10 +12881,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>585764</v>
+        <v>585176</v>
       </c>
       <c r="R127" t="n">
-        <v>7212207</v>
+        <v>7212008</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12943,10 +12943,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128971058</v>
+        <v>128970950</v>
       </c>
       <c r="B128" t="n">
-        <v>79041</v>
+        <v>82873</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12954,21 +12954,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>585445</v>
+        <v>585064</v>
       </c>
       <c r="R128" t="n">
-        <v>7211833</v>
+        <v>7212391</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13028,44 +13028,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128970908</v>
+        <v>128971017</v>
       </c>
       <c r="B129" t="n">
-        <v>80147</v>
+        <v>91997</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13075,10 +13075,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>585176</v>
+        <v>585476</v>
       </c>
       <c r="R129" t="n">
-        <v>7212008</v>
+        <v>7211928</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13125,22 +13125,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128970950</v>
+        <v>128971014</v>
       </c>
       <c r="B130" t="n">
-        <v>82873</v>
+        <v>83012</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13148,21 +13148,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13172,10 +13172,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>585064</v>
+        <v>585266</v>
       </c>
       <c r="R130" t="n">
-        <v>7212391</v>
+        <v>7212088</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13202,12 +13202,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13222,44 +13222,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128971017</v>
+        <v>128970892</v>
       </c>
       <c r="B131" t="n">
-        <v>91997</v>
+        <v>56917</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13269,10 +13269,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>585476</v>
+        <v>585431</v>
       </c>
       <c r="R131" t="n">
-        <v>7211928</v>
+        <v>7212208</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13319,44 +13319,44 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128971014</v>
+        <v>128970902</v>
       </c>
       <c r="B132" t="n">
-        <v>83012</v>
+        <v>80175</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13366,10 +13366,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>585266</v>
+        <v>585764</v>
       </c>
       <c r="R132" t="n">
-        <v>7212088</v>
+        <v>7212207</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13396,12 +13396,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13416,44 +13416,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128970892</v>
+        <v>128971058</v>
       </c>
       <c r="B133" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13463,10 +13463,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>585431</v>
+        <v>585445</v>
       </c>
       <c r="R133" t="n">
-        <v>7212208</v>
+        <v>7211833</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13513,12 +13513,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -15185,10 +15185,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128970885</v>
+        <v>128970993</v>
       </c>
       <c r="B151" t="n">
-        <v>91506</v>
+        <v>80175</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15196,21 +15196,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15220,10 +15220,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>584988</v>
+        <v>585161</v>
       </c>
       <c r="R151" t="n">
-        <v>7212367</v>
+        <v>7211868</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15270,22 +15270,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128970993</v>
+        <v>128970885</v>
       </c>
       <c r="B152" t="n">
-        <v>80175</v>
+        <v>91506</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15293,21 +15293,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15317,10 +15317,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>585161</v>
+        <v>584988</v>
       </c>
       <c r="R152" t="n">
-        <v>7211868</v>
+        <v>7212367</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15367,12 +15367,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -18106,10 +18106,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128971027</v>
+        <v>128970928</v>
       </c>
       <c r="B181" t="n">
-        <v>80146</v>
+        <v>91538</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18117,21 +18117,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18141,10 +18141,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>585336</v>
+        <v>584860</v>
       </c>
       <c r="R181" t="n">
-        <v>7211875</v>
+        <v>7212286</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18185,44 +18185,28 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128970999</v>
+        <v>128971044</v>
       </c>
       <c r="B182" t="n">
-        <v>57724</v>
+        <v>91556</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18230,21 +18214,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18254,10 +18238,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>585469</v>
+        <v>585304</v>
       </c>
       <c r="R182" t="n">
-        <v>7211944</v>
+        <v>7211887</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18284,17 +18268,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Hack på låga</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -18314,17 +18293,17 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128970928</v>
+        <v>128971011</v>
       </c>
       <c r="B183" t="n">
-        <v>91538</v>
+        <v>80147</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18332,21 +18311,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18356,10 +18335,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>584860</v>
+        <v>585263</v>
       </c>
       <c r="R183" t="n">
-        <v>7212286</v>
+        <v>7212085</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18386,12 +18365,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -18406,22 +18385,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128971044</v>
+        <v>128970948</v>
       </c>
       <c r="B184" t="n">
-        <v>91556</v>
+        <v>79041</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18429,21 +18408,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18453,10 +18432,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>585304</v>
+        <v>585646</v>
       </c>
       <c r="R184" t="n">
-        <v>7211887</v>
+        <v>7212110</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18503,22 +18482,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128971011</v>
+        <v>128970942</v>
       </c>
       <c r="B185" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18526,21 +18505,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18550,10 +18529,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>585263</v>
+        <v>585047</v>
       </c>
       <c r="R185" t="n">
-        <v>7212085</v>
+        <v>7212054</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -18580,12 +18559,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -18600,22 +18579,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128970948</v>
+        <v>128970936</v>
       </c>
       <c r="B186" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18623,21 +18602,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18647,10 +18626,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>585646</v>
+        <v>585451</v>
       </c>
       <c r="R186" t="n">
-        <v>7212110</v>
+        <v>7212214</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -18709,10 +18688,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128970942</v>
+        <v>128971027</v>
       </c>
       <c r="B187" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18720,21 +18699,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18744,10 +18723,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>585047</v>
+        <v>585336</v>
       </c>
       <c r="R187" t="n">
-        <v>7212054</v>
+        <v>7211875</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -18788,28 +18767,44 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128970936</v>
+        <v>128970999</v>
       </c>
       <c r="B188" t="n">
-        <v>91560</v>
+        <v>57724</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18817,21 +18812,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18841,10 +18836,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>585451</v>
+        <v>585469</v>
       </c>
       <c r="R188" t="n">
-        <v>7212214</v>
+        <v>7211944</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -18871,12 +18866,17 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Hack på låga</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -18891,60 +18891,60 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128995946</v>
+        <v>128995974</v>
       </c>
       <c r="B189" t="n">
-        <v>91560</v>
+        <v>80175</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>585705</v>
+        <v>585277</v>
       </c>
       <c r="R189" t="n">
-        <v>7212158</v>
+        <v>7212051</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -18984,64 +18984,69 @@
       </c>
       <c r="AG189" t="b">
         <v>0</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128995998</v>
+        <v>128995836</v>
       </c>
       <c r="B190" t="n">
-        <v>57727</v>
+        <v>80174</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>584932</v>
+        <v>585450</v>
       </c>
       <c r="R190" t="n">
-        <v>7212335</v>
+        <v>7211984</v>
       </c>
       <c r="S190" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19065,17 +19070,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -19086,31 +19086,26 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128995974</v>
+        <v>128995852</v>
       </c>
       <c r="B191" t="n">
-        <v>80175</v>
+        <v>80182</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19118,37 +19113,37 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>585277</v>
+        <v>585436</v>
       </c>
       <c r="R191" t="n">
-        <v>7212051</v>
+        <v>7211794</v>
       </c>
       <c r="S191" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19188,28 +19183,23 @@
       </c>
       <c r="AG191" t="b">
         <v>0</v>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128995836</v>
+        <v>128995846</v>
       </c>
       <c r="B192" t="n">
         <v>80174</v>
@@ -19244,10 +19234,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>585450</v>
+        <v>585437</v>
       </c>
       <c r="R192" t="n">
-        <v>7211984</v>
+        <v>7212018</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19306,32 +19296,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128995852</v>
+        <v>128995850</v>
       </c>
       <c r="B193" t="n">
-        <v>80182</v>
+        <v>80146</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19341,10 +19331,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>585436</v>
+        <v>584906</v>
       </c>
       <c r="R193" t="n">
-        <v>7211794</v>
+        <v>7211902</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19403,32 +19393,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128995846</v>
+        <v>128995946</v>
       </c>
       <c r="B194" t="n">
-        <v>80174</v>
+        <v>91560</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19438,10 +19428,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>585437</v>
+        <v>585705</v>
       </c>
       <c r="R194" t="n">
-        <v>7212018</v>
+        <v>7212158</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19468,12 +19458,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -19488,22 +19478,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128995850</v>
+        <v>128995998</v>
       </c>
       <c r="B195" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19511,37 +19501,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>584906</v>
+        <v>584932</v>
       </c>
       <c r="R195" t="n">
-        <v>7211902</v>
+        <v>7212335</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -19573,6 +19563,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
@@ -19581,16 +19576,21 @@
       </c>
       <c r="AG195" t="b">
         <v>0</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
@@ -23173,48 +23173,52 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128995838</v>
+        <v>128995995</v>
       </c>
       <c r="B232" t="n">
-        <v>80174</v>
+        <v>57727</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>584779</v>
+        <v>584838</v>
       </c>
       <c r="R232" t="n">
-        <v>7211856</v>
+        <v>7212145</v>
       </c>
       <c r="S232" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -23246,6 +23250,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD232" t="b">
         <v>0</v>
       </c>
@@ -23254,26 +23263,31 @@
       </c>
       <c r="AG232" t="b">
         <v>0</v>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128995947</v>
+        <v>128995994</v>
       </c>
       <c r="B233" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23281,37 +23295,41 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>585239</v>
+        <v>584839</v>
       </c>
       <c r="R233" t="n">
-        <v>7211879</v>
+        <v>7212144</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -23343,6 +23361,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD233" t="b">
         <v>0</v>
       </c>
@@ -23351,68 +23374,69 @@
       </c>
       <c r="AG233" t="b">
         <v>0</v>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128995995</v>
+        <v>128995838</v>
       </c>
       <c r="B234" t="n">
-        <v>57727</v>
+        <v>80174</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>584838</v>
+        <v>584779</v>
       </c>
       <c r="R234" t="n">
-        <v>7212145</v>
+        <v>7211856</v>
       </c>
       <c r="S234" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -23444,11 +23468,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD234" t="b">
         <v>0</v>
       </c>
@@ -23457,31 +23476,26 @@
       </c>
       <c r="AG234" t="b">
         <v>0</v>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128995994</v>
+        <v>128995947</v>
       </c>
       <c r="B235" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23489,41 +23503,37 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>584839</v>
+        <v>585239</v>
       </c>
       <c r="R235" t="n">
-        <v>7212144</v>
+        <v>7211879</v>
       </c>
       <c r="S235" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -23555,11 +23565,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD235" t="b">
         <v>0</v>
       </c>
@@ -23568,21 +23573,16 @@
       </c>
       <c r="AG235" t="b">
         <v>0</v>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
@@ -23691,10 +23691,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128995948</v>
+        <v>128995919</v>
       </c>
       <c r="B237" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23702,21 +23702,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -23726,10 +23726,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>585381</v>
+        <v>585128</v>
       </c>
       <c r="R237" t="n">
-        <v>7212289</v>
+        <v>7212334</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -23756,12 +23756,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -23788,10 +23788,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128995919</v>
+        <v>128995948</v>
       </c>
       <c r="B238" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23799,21 +23799,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -23823,10 +23823,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>585128</v>
+        <v>585381</v>
       </c>
       <c r="R238" t="n">
-        <v>7212334</v>
+        <v>7212289</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -23853,12 +23853,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -24574,48 +24574,48 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128995975</v>
+        <v>128995913</v>
       </c>
       <c r="B246" t="n">
-        <v>80175</v>
+        <v>80147</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>584970</v>
+        <v>584976</v>
       </c>
       <c r="R246" t="n">
-        <v>7211976</v>
+        <v>7211927</v>
       </c>
       <c r="S246" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -24655,31 +24655,26 @@
       </c>
       <c r="AG246" t="b">
         <v>0</v>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128995933</v>
+        <v>128995975</v>
       </c>
       <c r="B247" t="n">
-        <v>80182</v>
+        <v>80175</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24687,37 +24682,37 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>584847</v>
+        <v>584970</v>
       </c>
       <c r="R247" t="n">
-        <v>7212088</v>
+        <v>7211976</v>
       </c>
       <c r="S247" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -24757,48 +24752,53 @@
       </c>
       <c r="AG247" t="b">
         <v>0</v>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128995873</v>
+        <v>128995933</v>
       </c>
       <c r="B248" t="n">
-        <v>79041</v>
+        <v>80182</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -24808,10 +24808,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>585359</v>
+        <v>584847</v>
       </c>
       <c r="R248" t="n">
-        <v>7211881</v>
+        <v>7212088</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -24858,19 +24858,19 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128995859</v>
+        <v>128995873</v>
       </c>
       <c r="B249" t="n">
         <v>79041</v>
@@ -24905,10 +24905,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>585374</v>
+        <v>585359</v>
       </c>
       <c r="R249" t="n">
-        <v>7212193</v>
+        <v>7211881</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -24935,12 +24935,12 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -24967,10 +24967,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128995913</v>
+        <v>128995859</v>
       </c>
       <c r="B250" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -24978,21 +24978,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -25002,10 +25002,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>584976</v>
+        <v>585374</v>
       </c>
       <c r="R250" t="n">
-        <v>7211927</v>
+        <v>7212193</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25032,12 +25032,12 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -25052,44 +25052,44 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128995915</v>
+        <v>128995942</v>
       </c>
       <c r="B251" t="n">
-        <v>80147</v>
+        <v>82990</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25099,10 +25099,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>585212</v>
+        <v>585375</v>
       </c>
       <c r="R251" t="n">
-        <v>7212298</v>
+        <v>7212068</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25161,32 +25161,32 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128995942</v>
+        <v>128995915</v>
       </c>
       <c r="B252" t="n">
-        <v>82990</v>
+        <v>80147</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -25196,10 +25196,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>585375</v>
+        <v>585212</v>
       </c>
       <c r="R252" t="n">
-        <v>7212068</v>
+        <v>7212298</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26359,32 +26359,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128995999</v>
+        <v>128995983</v>
       </c>
       <c r="B264" t="n">
-        <v>97549</v>
+        <v>80147</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -26394,10 +26394,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>585573</v>
+        <v>585170</v>
       </c>
       <c r="R264" t="n">
-        <v>7212171</v>
+        <v>7212204</v>
       </c>
       <c r="S264" t="n">
         <v>15</v>
@@ -26424,12 +26424,12 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -26461,7 +26461,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128995983</v>
+        <v>128995979</v>
       </c>
       <c r="B265" t="n">
         <v>80147</v>
@@ -26496,10 +26496,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>585170</v>
+        <v>584970</v>
       </c>
       <c r="R265" t="n">
-        <v>7212204</v>
+        <v>7211976</v>
       </c>
       <c r="S265" t="n">
         <v>15</v>
@@ -26526,12 +26526,12 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -26563,32 +26563,32 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128995979</v>
+        <v>128995999</v>
       </c>
       <c r="B266" t="n">
-        <v>80147</v>
+        <v>97549</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -26598,10 +26598,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>584970</v>
+        <v>585573</v>
       </c>
       <c r="R266" t="n">
-        <v>7211976</v>
+        <v>7212171</v>
       </c>
       <c r="S266" t="n">
         <v>15</v>
@@ -26767,48 +26767,48 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128995874</v>
+        <v>128995965</v>
       </c>
       <c r="B268" t="n">
-        <v>79041</v>
+        <v>105726</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>585370</v>
+        <v>585233</v>
       </c>
       <c r="R268" t="n">
-        <v>7211866</v>
+        <v>7212183</v>
       </c>
       <c r="S268" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -26832,12 +26832,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -26848,64 +26848,69 @@
       </c>
       <c r="AG268" t="b">
         <v>0</v>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128995965</v>
+        <v>128995874</v>
       </c>
       <c r="B269" t="n">
-        <v>105726</v>
+        <v>79041</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>585233</v>
+        <v>585370</v>
       </c>
       <c r="R269" t="n">
-        <v>7212183</v>
+        <v>7211866</v>
       </c>
       <c r="S269" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -26929,12 +26934,12 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -26945,53 +26950,48 @@
       </c>
       <c r="AG269" t="b">
         <v>0</v>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128995856</v>
+        <v>128995912</v>
       </c>
       <c r="B270" t="n">
-        <v>57831</v>
+        <v>80147</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -27001,10 +27001,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>585522</v>
+        <v>584990</v>
       </c>
       <c r="R270" t="n">
-        <v>7211894</v>
+        <v>7211932</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27031,12 +27031,12 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -27051,22 +27051,22 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128995912</v>
+        <v>128995864</v>
       </c>
       <c r="B271" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27074,21 +27074,21 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -27098,10 +27098,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>584990</v>
+        <v>585345</v>
       </c>
       <c r="R271" t="n">
-        <v>7211932</v>
+        <v>7211890</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27148,44 +27148,44 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128995864</v>
+        <v>128995856</v>
       </c>
       <c r="B272" t="n">
-        <v>79041</v>
+        <v>57831</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -27195,10 +27195,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>585345</v>
+        <v>585522</v>
       </c>
       <c r="R272" t="n">
-        <v>7211890</v>
+        <v>7211894</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27225,12 +27225,12 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -27257,32 +27257,32 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128995830</v>
+        <v>128995906</v>
       </c>
       <c r="B273" t="n">
-        <v>57887</v>
+        <v>80175</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -27292,10 +27292,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>585373</v>
+        <v>584836</v>
       </c>
       <c r="R273" t="n">
-        <v>7211857</v>
+        <v>7212031</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -27342,22 +27342,22 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128995906</v>
+        <v>128995936</v>
       </c>
       <c r="B274" t="n">
-        <v>80175</v>
+        <v>80182</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -27365,21 +27365,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -27389,10 +27389,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>584836</v>
+        <v>585498</v>
       </c>
       <c r="R274" t="n">
-        <v>7212031</v>
+        <v>7211887</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -27419,12 +27419,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -27444,39 +27444,39 @@
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128995936</v>
+        <v>128995830</v>
       </c>
       <c r="B275" t="n">
-        <v>80182</v>
+        <v>57887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -27486,10 +27486,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>585498</v>
+        <v>585373</v>
       </c>
       <c r="R275" t="n">
-        <v>7211887</v>
+        <v>7211857</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -27516,12 +27516,12 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -27536,12 +27536,12 @@
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
@@ -27659,10 +27659,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>128995951</v>
+        <v>128995970</v>
       </c>
       <c r="B277" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -27670,37 +27670,37 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>585462</v>
+        <v>585041</v>
       </c>
       <c r="R277" t="n">
-        <v>7211963</v>
+        <v>7212398</v>
       </c>
       <c r="S277" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -27724,12 +27724,12 @@
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -27740,64 +27740,69 @@
       </c>
       <c r="AG277" t="b">
         <v>0</v>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT277" t="inlineStr"/>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128995928</v>
+        <v>128996002</v>
       </c>
       <c r="B278" t="n">
-        <v>80147</v>
+        <v>97555</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>585749</v>
+        <v>585221</v>
       </c>
       <c r="R278" t="n">
-        <v>7212194</v>
+        <v>7212396</v>
       </c>
       <c r="S278" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -27837,48 +27842,53 @@
       </c>
       <c r="AG278" t="b">
         <v>0</v>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128995862</v>
+        <v>128995853</v>
       </c>
       <c r="B279" t="n">
-        <v>79041</v>
+        <v>57831</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -27888,10 +27898,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>585258</v>
+        <v>585109</v>
       </c>
       <c r="R279" t="n">
-        <v>7211874</v>
+        <v>7211888</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -27950,48 +27960,48 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128996002</v>
+        <v>128995862</v>
       </c>
       <c r="B280" t="n">
-        <v>97555</v>
+        <v>79041</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>585221</v>
+        <v>585258</v>
       </c>
       <c r="R280" t="n">
-        <v>7212396</v>
+        <v>7211874</v>
       </c>
       <c r="S280" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -28031,31 +28041,26 @@
       </c>
       <c r="AG280" t="b">
         <v>0</v>
-      </c>
-      <c r="AH280" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>128995970</v>
+        <v>128995951</v>
       </c>
       <c r="B281" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28063,37 +28068,37 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>585041</v>
+        <v>585462</v>
       </c>
       <c r="R281" t="n">
-        <v>7212398</v>
+        <v>7211963</v>
       </c>
       <c r="S281" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -28117,12 +28122,12 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -28133,53 +28138,48 @@
       </c>
       <c r="AG281" t="b">
         <v>0</v>
-      </c>
-      <c r="AH281" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>128995853</v>
+        <v>128995928</v>
       </c>
       <c r="B282" t="n">
-        <v>57831</v>
+        <v>80147</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -28189,10 +28189,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>585109</v>
+        <v>585749</v>
       </c>
       <c r="R282" t="n">
-        <v>7211888</v>
+        <v>7212194</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -28239,12 +28239,12 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>

--- a/artfynd/A 45899-2025 artfynd.xlsx
+++ b/artfynd/A 45899-2025 artfynd.xlsx
@@ -2417,10 +2417,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128952861</v>
+        <v>128952834</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,21 +2428,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585400</v>
+        <v>585327</v>
       </c>
       <c r="R20" t="n">
-        <v>7212047</v>
+        <v>7212199</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128952834</v>
+        <v>128952861</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585327</v>
+        <v>585400</v>
       </c>
       <c r="R21" t="n">
-        <v>7212199</v>
+        <v>7212047</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970912</v>
+        <v>128971060</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585753</v>
+        <v>585277</v>
       </c>
       <c r="R39" t="n">
-        <v>7212201</v>
+        <v>7212276</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4341,39 +4341,39 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128971071</v>
+        <v>128971053</v>
       </c>
       <c r="B40" t="n">
-        <v>80183</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585174</v>
+        <v>585461</v>
       </c>
       <c r="R40" t="n">
-        <v>7212174</v>
+        <v>7211969</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128971060</v>
+        <v>128970943</v>
       </c>
       <c r="B41" t="n">
         <v>79043</v>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585277</v>
+        <v>585010</v>
       </c>
       <c r="R41" t="n">
-        <v>7212276</v>
+        <v>7212219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4535,22 +4535,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128971053</v>
+        <v>128970912</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4558,21 +4558,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585461</v>
+        <v>585753</v>
       </c>
       <c r="R42" t="n">
-        <v>7211969</v>
+        <v>7212201</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4632,22 +4632,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128970943</v>
+        <v>128970954</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>88943</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4655,21 +4655,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585010</v>
+        <v>585170</v>
       </c>
       <c r="R43" t="n">
-        <v>7212219</v>
+        <v>7212058</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4741,10 +4741,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128971040</v>
+        <v>128971071</v>
       </c>
       <c r="B44" t="n">
-        <v>82994</v>
+        <v>80183</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6439</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585331</v>
+        <v>585174</v>
       </c>
       <c r="R44" t="n">
-        <v>7211998</v>
+        <v>7212174</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4838,32 +4838,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128970954</v>
+        <v>128971040</v>
       </c>
       <c r="B45" t="n">
-        <v>88943</v>
+        <v>82994</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>510</v>
+        <v>6439</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585170</v>
+        <v>585331</v>
       </c>
       <c r="R45" t="n">
-        <v>7212058</v>
+        <v>7211998</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4903,12 +4903,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4923,12 +4923,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5518,10 +5518,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128970905</v>
+        <v>128970911</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,21 +5529,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585261</v>
+        <v>585705</v>
       </c>
       <c r="R52" t="n">
-        <v>7212445</v>
+        <v>7212154</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5615,10 +5615,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128970893</v>
+        <v>128971072</v>
       </c>
       <c r="B53" t="n">
-        <v>57887</v>
+        <v>83003</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5626,21 +5626,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5650,10 +5650,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584907</v>
+        <v>585126</v>
       </c>
       <c r="R53" t="n">
-        <v>7212296</v>
+        <v>7212238</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5680,12 +5680,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5700,44 +5700,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128970911</v>
+        <v>128970952</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>91816</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>65</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585705</v>
+        <v>584977</v>
       </c>
       <c r="R54" t="n">
-        <v>7212154</v>
+        <v>7212268</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5802,17 +5802,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128971072</v>
+        <v>128970983</v>
       </c>
       <c r="B55" t="n">
-        <v>83003</v>
+        <v>96956</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5820,21 +5820,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5844,10 +5844,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585126</v>
+        <v>585336</v>
       </c>
       <c r="R55" t="n">
-        <v>7212238</v>
+        <v>7212194</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5899,14 +5899,14 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128970952</v>
+        <v>128970953</v>
       </c>
       <c r="B56" t="n">
         <v>91816</v>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584977</v>
+        <v>585429</v>
       </c>
       <c r="R56" t="n">
-        <v>7212268</v>
+        <v>7212208</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128970983</v>
+        <v>128970905</v>
       </c>
       <c r="B57" t="n">
-        <v>96956</v>
+        <v>57724</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6014,21 +6014,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>585336</v>
+        <v>585261</v>
       </c>
       <c r="R57" t="n">
-        <v>7212194</v>
+        <v>7212445</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6088,44 +6088,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128970953</v>
+        <v>128970893</v>
       </c>
       <c r="B58" t="n">
-        <v>91816</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>65</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>585429</v>
+        <v>584907</v>
       </c>
       <c r="R58" t="n">
-        <v>7212208</v>
+        <v>7212296</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6294,32 +6294,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128971009</v>
+        <v>128971069</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>80183</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>585602</v>
+        <v>585209</v>
       </c>
       <c r="R60" t="n">
-        <v>7212039</v>
+        <v>7212303</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6391,32 +6391,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128971020</v>
+        <v>128970894</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6426,10 +6426,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>585163</v>
+        <v>585309</v>
       </c>
       <c r="R61" t="n">
-        <v>7211880</v>
+        <v>7211980</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6464,11 +6464,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6481,39 +6476,39 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128971069</v>
+        <v>128971062</v>
       </c>
       <c r="B62" t="n">
-        <v>80183</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6528,10 +6523,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>585209</v>
+        <v>585119</v>
       </c>
       <c r="R62" t="n">
-        <v>7212303</v>
+        <v>7212230</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6590,32 +6585,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128970894</v>
+        <v>128971020</v>
       </c>
       <c r="B63" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6625,10 +6620,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>585309</v>
+        <v>585163</v>
       </c>
       <c r="R63" t="n">
-        <v>7211980</v>
+        <v>7211880</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6663,6 +6658,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -6675,44 +6675,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128971033</v>
+        <v>128971009</v>
       </c>
       <c r="B64" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>585316</v>
+        <v>585602</v>
       </c>
       <c r="R64" t="n">
-        <v>7212062</v>
+        <v>7212039</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6784,32 +6784,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128971062</v>
+        <v>128971033</v>
       </c>
       <c r="B65" t="n">
-        <v>79043</v>
+        <v>80184</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>585119</v>
+        <v>585316</v>
       </c>
       <c r="R65" t="n">
-        <v>7212230</v>
+        <v>7212062</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6974,10 +6974,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128970944</v>
+        <v>128970978</v>
       </c>
       <c r="B67" t="n">
-        <v>79043</v>
+        <v>83011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6985,21 +6985,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>584886</v>
+        <v>585096</v>
       </c>
       <c r="R67" t="n">
-        <v>7212247</v>
+        <v>7212243</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7039,12 +7039,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7059,22 +7059,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128971061</v>
+        <v>128971019</v>
       </c>
       <c r="B68" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7082,21 +7082,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>585189</v>
+        <v>585141</v>
       </c>
       <c r="R68" t="n">
-        <v>7212297</v>
+        <v>7211874</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7136,12 +7136,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7168,10 +7173,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128970978</v>
+        <v>128971036</v>
       </c>
       <c r="B69" t="n">
-        <v>83011</v>
+        <v>91539</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7179,21 +7184,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7203,10 +7208,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>585096</v>
+        <v>584592</v>
       </c>
       <c r="R69" t="n">
-        <v>7212243</v>
+        <v>7211936</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7233,12 +7238,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7459,10 +7464,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128971019</v>
+        <v>128970944</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7470,21 +7475,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7494,10 +7499,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>585141</v>
+        <v>584886</v>
       </c>
       <c r="R72" t="n">
-        <v>7211874</v>
+        <v>7212247</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7532,11 +7537,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7549,22 +7549,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128971036</v>
+        <v>128971061</v>
       </c>
       <c r="B73" t="n">
-        <v>91539</v>
+        <v>79043</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7572,21 +7572,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>584592</v>
+        <v>585189</v>
       </c>
       <c r="R73" t="n">
-        <v>7211936</v>
+        <v>7212297</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7626,12 +7626,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128970918</v>
+        <v>128970913</v>
       </c>
       <c r="B74" t="n">
-        <v>91925</v>
+        <v>80149</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1506</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>584867</v>
+        <v>585764</v>
       </c>
       <c r="R74" t="n">
-        <v>7212286</v>
+        <v>7212207</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7755,32 +7755,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128970913</v>
+        <v>128970887</v>
       </c>
       <c r="B75" t="n">
-        <v>80149</v>
+        <v>91507</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>585764</v>
+        <v>585554</v>
       </c>
       <c r="R75" t="n">
-        <v>7212207</v>
+        <v>7212186</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7852,32 +7852,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128971055</v>
+        <v>128971031</v>
       </c>
       <c r="B76" t="n">
-        <v>79043</v>
+        <v>80184</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>585255</v>
+        <v>585387</v>
       </c>
       <c r="R76" t="n">
-        <v>7212100</v>
+        <v>7211820</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7917,17 +7917,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -7936,7 +7931,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -7955,32 +7949,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128971063</v>
+        <v>128970918</v>
       </c>
       <c r="B77" t="n">
-        <v>79043</v>
+        <v>91925</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -7990,10 +7984,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>585170</v>
+        <v>584867</v>
       </c>
       <c r="R77" t="n">
-        <v>7212187</v>
+        <v>7212286</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8020,12 +8014,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8040,44 +8034,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128970887</v>
+        <v>128971055</v>
       </c>
       <c r="B78" t="n">
-        <v>91507</v>
+        <v>79043</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8087,10 +8081,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>585554</v>
+        <v>585255</v>
       </c>
       <c r="R78" t="n">
-        <v>7212186</v>
+        <v>7212100</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8117,12 +8111,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8131,50 +8130,51 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128971031</v>
+        <v>128971063</v>
       </c>
       <c r="B79" t="n">
-        <v>80184</v>
+        <v>79043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>585387</v>
+        <v>585170</v>
       </c>
       <c r="R79" t="n">
-        <v>7211820</v>
+        <v>7212187</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8214,12 +8214,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8444,32 +8444,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128971006</v>
+        <v>128970897</v>
       </c>
       <c r="B82" t="n">
-        <v>80149</v>
+        <v>80177</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>584919</v>
+        <v>585579</v>
       </c>
       <c r="R82" t="n">
-        <v>7211893</v>
+        <v>7212245</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8529,44 +8529,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128970937</v>
+        <v>128970992</v>
       </c>
       <c r="B83" t="n">
-        <v>79043</v>
+        <v>80177</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>584860</v>
+        <v>585172</v>
       </c>
       <c r="R83" t="n">
-        <v>7212204</v>
+        <v>7212168</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8606,17 +8606,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8625,51 +8620,50 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128970979</v>
+        <v>128970995</v>
       </c>
       <c r="B84" t="n">
-        <v>83011</v>
+        <v>80177</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8679,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>585258</v>
+        <v>585119</v>
       </c>
       <c r="R84" t="n">
-        <v>7212103</v>
+        <v>7212238</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8741,10 +8735,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128971047</v>
+        <v>128970937</v>
       </c>
       <c r="B85" t="n">
-        <v>91563</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8752,19 +8746,23 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -8772,10 +8770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>585131</v>
+        <v>584860</v>
       </c>
       <c r="R85" t="n">
-        <v>7212210</v>
+        <v>7212204</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8802,12 +8800,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8816,50 +8819,51 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128970897</v>
+        <v>128971006</v>
       </c>
       <c r="B86" t="n">
-        <v>80177</v>
+        <v>80149</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8869,10 +8873,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>585579</v>
+        <v>584919</v>
       </c>
       <c r="R86" t="n">
-        <v>7212245</v>
+        <v>7211893</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8919,46 +8923,42 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128970992</v>
+        <v>128971047</v>
       </c>
       <c r="B87" t="n">
-        <v>80177</v>
+        <v>91563</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -8966,10 +8966,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>585172</v>
+        <v>585131</v>
       </c>
       <c r="R87" t="n">
-        <v>7212168</v>
+        <v>7212210</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9021,39 +9021,39 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128970995</v>
+        <v>128970979</v>
       </c>
       <c r="B88" t="n">
-        <v>80177</v>
+        <v>83011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>585119</v>
+        <v>585258</v>
       </c>
       <c r="R88" t="n">
-        <v>7212238</v>
+        <v>7212103</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9513,48 +9513,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128970883</v>
+        <v>128970891</v>
       </c>
       <c r="B93" t="n">
-        <v>83011</v>
+        <v>92261</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>585518</v>
+        <v>585325</v>
       </c>
       <c r="R93" t="n">
-        <v>7212240</v>
+        <v>7211962</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9595,7 +9592,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9614,45 +9610,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128970891</v>
+        <v>128970883</v>
       </c>
       <c r="B94" t="n">
-        <v>92261</v>
+        <v>83011</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Inre Verkansliden, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>585325</v>
+        <v>585518</v>
       </c>
       <c r="R94" t="n">
-        <v>7211962</v>
+        <v>7212240</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9693,6 +9692,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9711,10 +9711,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128970947</v>
+        <v>128970904</v>
       </c>
       <c r="B95" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9722,21 +9722,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9746,10 +9746,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>585544</v>
+        <v>584971</v>
       </c>
       <c r="R95" t="n">
-        <v>7212152</v>
+        <v>7212140</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9801,17 +9801,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128970904</v>
+        <v>128970947</v>
       </c>
       <c r="B96" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9819,21 +9819,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>584971</v>
+        <v>585544</v>
       </c>
       <c r="R96" t="n">
-        <v>7212140</v>
+        <v>7212152</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10875,32 +10875,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128970886</v>
+        <v>128971010</v>
       </c>
       <c r="B107" t="n">
-        <v>91507</v>
+        <v>80149</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10910,10 +10910,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585385</v>
+        <v>585204</v>
       </c>
       <c r="R107" t="n">
-        <v>7212233</v>
+        <v>7212304</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -10940,12 +10940,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -10960,22 +10960,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128970933</v>
+        <v>128970980</v>
       </c>
       <c r="B108" t="n">
-        <v>91563</v>
+        <v>83011</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10983,19 +10983,23 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11003,10 +11007,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585051</v>
+        <v>585330</v>
       </c>
       <c r="R108" t="n">
-        <v>7212128</v>
+        <v>7212026</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11033,12 +11037,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11053,44 +11057,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128971002</v>
+        <v>128971043</v>
       </c>
       <c r="B109" t="n">
-        <v>83009</v>
+        <v>82994</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6486</v>
+        <v>6439</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11100,10 +11104,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585321</v>
+        <v>585466</v>
       </c>
       <c r="R109" t="n">
-        <v>7212053</v>
+        <v>7211980</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11162,32 +11166,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128970956</v>
+        <v>128971021</v>
       </c>
       <c r="B110" t="n">
-        <v>80183</v>
+        <v>57727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11197,10 +11201,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585564</v>
+        <v>585207</v>
       </c>
       <c r="R110" t="n">
-        <v>7212138</v>
+        <v>7211876</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11235,6 +11239,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -11247,22 +11256,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128970901</v>
+        <v>128970886</v>
       </c>
       <c r="B111" t="n">
-        <v>80177</v>
+        <v>91507</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11270,21 +11279,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11294,10 +11303,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585719</v>
+        <v>585385</v>
       </c>
       <c r="R111" t="n">
-        <v>7212168</v>
+        <v>7212233</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11356,34 +11365,30 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128971032</v>
+        <v>128970933</v>
       </c>
       <c r="B112" t="n">
-        <v>80184</v>
+        <v>91563</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11391,10 +11396,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585204</v>
+        <v>585051</v>
       </c>
       <c r="R112" t="n">
-        <v>7212303</v>
+        <v>7212128</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11421,12 +11426,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11441,44 +11446,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128970980</v>
+        <v>128971002</v>
       </c>
       <c r="B113" t="n">
-        <v>83011</v>
+        <v>83009</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11488,10 +11493,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585330</v>
+        <v>585321</v>
       </c>
       <c r="R113" t="n">
-        <v>7212026</v>
+        <v>7212053</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11543,17 +11548,17 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128971043</v>
+        <v>128970956</v>
       </c>
       <c r="B114" t="n">
-        <v>82994</v>
+        <v>80183</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11561,21 +11566,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6439</v>
+        <v>6463</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11585,10 +11590,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585466</v>
+        <v>585564</v>
       </c>
       <c r="R114" t="n">
-        <v>7211980</v>
+        <v>7212138</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11615,12 +11620,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11635,44 +11640,44 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128971021</v>
+        <v>128970901</v>
       </c>
       <c r="B115" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11682,10 +11687,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585207</v>
+        <v>585719</v>
       </c>
       <c r="R115" t="n">
-        <v>7211876</v>
+        <v>7212168</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11720,11 +11725,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -11737,44 +11737,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128971010</v>
+        <v>128971032</v>
       </c>
       <c r="B116" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11787,7 +11787,7 @@
         <v>585204</v>
       </c>
       <c r="R116" t="n">
-        <v>7212304</v>
+        <v>7212303</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13303,32 +13303,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128971058</v>
+        <v>128970892</v>
       </c>
       <c r="B132" t="n">
-        <v>79043</v>
+        <v>56917</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13338,10 +13338,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>585445</v>
+        <v>585431</v>
       </c>
       <c r="R132" t="n">
-        <v>7211833</v>
+        <v>7212208</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13388,44 +13388,44 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128970892</v>
+        <v>128971058</v>
       </c>
       <c r="B133" t="n">
-        <v>56917</v>
+        <v>79043</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13435,10 +13435,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>585431</v>
+        <v>585445</v>
       </c>
       <c r="R133" t="n">
-        <v>7212208</v>
+        <v>7211833</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13485,12 +13485,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -13982,10 +13982,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128971054</v>
+        <v>128971012</v>
       </c>
       <c r="B139" t="n">
-        <v>82877</v>
+        <v>80149</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13993,21 +13993,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14017,10 +14017,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>585259</v>
+        <v>585414</v>
       </c>
       <c r="R139" t="n">
-        <v>7212103</v>
+        <v>7212004</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14079,10 +14079,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128971012</v>
+        <v>128970958</v>
       </c>
       <c r="B140" t="n">
-        <v>80149</v>
+        <v>83003</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14090,21 +14090,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14114,10 +14114,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>585414</v>
+        <v>585538</v>
       </c>
       <c r="R140" t="n">
-        <v>7212004</v>
+        <v>7212165</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14144,12 +14144,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14164,44 +14164,44 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128970895</v>
+        <v>128970903</v>
       </c>
       <c r="B141" t="n">
-        <v>80177</v>
+        <v>91494</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6462</v>
+        <v>112</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14211,10 +14211,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>585156</v>
+        <v>584882</v>
       </c>
       <c r="R141" t="n">
-        <v>7211976</v>
+        <v>7212226</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14273,10 +14273,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128970899</v>
+        <v>128970884</v>
       </c>
       <c r="B142" t="n">
-        <v>80177</v>
+        <v>91507</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14284,21 +14284,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14308,10 +14308,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>585588</v>
+        <v>584998</v>
       </c>
       <c r="R142" t="n">
-        <v>7212104</v>
+        <v>7212243</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14370,32 +14370,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128971001</v>
+        <v>128971054</v>
       </c>
       <c r="B143" t="n">
-        <v>83009</v>
+        <v>82877</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6486</v>
+        <v>1312</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>585329</v>
+        <v>585259</v>
       </c>
       <c r="R143" t="n">
-        <v>7212033</v>
+        <v>7212103</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14467,32 +14467,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128970958</v>
+        <v>128970895</v>
       </c>
       <c r="B144" t="n">
-        <v>83003</v>
+        <v>80177</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14502,10 +14502,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>585538</v>
+        <v>585156</v>
       </c>
       <c r="R144" t="n">
-        <v>7212165</v>
+        <v>7211976</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14557,39 +14557,39 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128970903</v>
+        <v>128970899</v>
       </c>
       <c r="B145" t="n">
-        <v>91494</v>
+        <v>80177</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14599,10 +14599,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>584882</v>
+        <v>585588</v>
       </c>
       <c r="R145" t="n">
-        <v>7212226</v>
+        <v>7212104</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -14661,32 +14661,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128970884</v>
+        <v>128971001</v>
       </c>
       <c r="B146" t="n">
-        <v>91507</v>
+        <v>83009</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5447</v>
+        <v>6486</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14696,10 +14696,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>584998</v>
+        <v>585329</v>
       </c>
       <c r="R146" t="n">
-        <v>7212243</v>
+        <v>7212033</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -14746,12 +14746,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -15157,10 +15157,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128970945</v>
+        <v>128970909</v>
       </c>
       <c r="B151" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15168,21 +15168,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15192,10 +15192,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>584857</v>
+        <v>585565</v>
       </c>
       <c r="R151" t="n">
-        <v>7212300</v>
+        <v>7212137</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15247,39 +15247,39 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128971057</v>
+        <v>128970993</v>
       </c>
       <c r="B152" t="n">
-        <v>79043</v>
+        <v>80177</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15289,10 +15289,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>585238</v>
+        <v>585161</v>
       </c>
       <c r="R152" t="n">
-        <v>7211876</v>
+        <v>7211868</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15344,39 +15344,39 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128970885</v>
+        <v>128970945</v>
       </c>
       <c r="B153" t="n">
-        <v>91507</v>
+        <v>79043</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15386,10 +15386,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>584988</v>
+        <v>584857</v>
       </c>
       <c r="R153" t="n">
-        <v>7212367</v>
+        <v>7212300</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15441,39 +15441,39 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Elin Kannerby, Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128970993</v>
+        <v>128971057</v>
       </c>
       <c r="B154" t="n">
-        <v>80177</v>
+        <v>79043</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15483,10 +15483,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>585161</v>
+        <v>585238</v>
       </c>
       <c r="R154" t="n">
-        <v>7211868</v>
+        <v>7211876</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15538,17 +15538,17 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128970909</v>
+        <v>128970981</v>
       </c>
       <c r="B155" t="n">
-        <v>80149</v>
+        <v>83011</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15556,21 +15556,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15580,10 +15580,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>585565</v>
+        <v>585399</v>
       </c>
       <c r="R155" t="n">
-        <v>7212137</v>
+        <v>7212011</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15610,12 +15610,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -15630,44 +15630,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128970981</v>
+        <v>128970885</v>
       </c>
       <c r="B156" t="n">
-        <v>83011</v>
+        <v>91507</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15677,10 +15677,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>585399</v>
+        <v>584988</v>
       </c>
       <c r="R156" t="n">
-        <v>7212011</v>
+        <v>7212367</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -15707,12 +15707,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -15727,12 +15727,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
+          <t>Elin Kannerby, Alva Danielsson, Embla Berg, Henny My Lindqvist, Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -20930,48 +20930,48 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128995957</v>
+        <v>128995981</v>
       </c>
       <c r="B210" t="n">
-        <v>80183</v>
+        <v>80149</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>585466</v>
+        <v>585760</v>
       </c>
       <c r="R210" t="n">
-        <v>7211970</v>
+        <v>7212191</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -20995,12 +20995,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -21011,26 +21011,31 @@
       </c>
       <c r="AG210" t="b">
         <v>0</v>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128995869</v>
+        <v>128995917</v>
       </c>
       <c r="B211" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21038,21 +21043,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21062,10 +21067,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>585359</v>
+        <v>585498</v>
       </c>
       <c r="R211" t="n">
-        <v>7211888</v>
+        <v>7211889</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21092,12 +21097,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -21112,22 +21117,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128995871</v>
+        <v>128995980</v>
       </c>
       <c r="B212" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21135,37 +21140,37 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>585355</v>
+        <v>585364</v>
       </c>
       <c r="R212" t="n">
-        <v>7211878</v>
+        <v>7212436</v>
       </c>
       <c r="S212" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -21205,26 +21210,31 @@
       </c>
       <c r="AG212" t="b">
         <v>0</v>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128995866</v>
+        <v>128995997</v>
       </c>
       <c r="B213" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21232,37 +21242,37 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>585353</v>
+        <v>584895</v>
       </c>
       <c r="R213" t="n">
-        <v>7211885</v>
+        <v>7212228</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -21294,6 +21304,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD213" t="b">
         <v>0</v>
       </c>
@@ -21302,43 +21317,48 @@
       </c>
       <c r="AG213" t="b">
         <v>0</v>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128995872</v>
+        <v>128995957</v>
       </c>
       <c r="B214" t="n">
-        <v>79043</v>
+        <v>80183</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -21353,10 +21373,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>585359</v>
+        <v>585466</v>
       </c>
       <c r="R214" t="n">
-        <v>7211883</v>
+        <v>7211970</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21383,12 +21403,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -21403,22 +21423,22 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128995981</v>
+        <v>128995869</v>
       </c>
       <c r="B215" t="n">
-        <v>80149</v>
+        <v>79043</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21426,37 +21446,37 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>585760</v>
+        <v>585359</v>
       </c>
       <c r="R215" t="n">
-        <v>7212191</v>
+        <v>7211888</v>
       </c>
       <c r="S215" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -21496,31 +21516,26 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128995917</v>
+        <v>128995871</v>
       </c>
       <c r="B216" t="n">
-        <v>80149</v>
+        <v>79043</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21528,21 +21543,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -21552,10 +21567,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>585498</v>
+        <v>585355</v>
       </c>
       <c r="R216" t="n">
-        <v>7211889</v>
+        <v>7211878</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -21582,12 +21597,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -21602,22 +21617,22 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128995980</v>
+        <v>128995866</v>
       </c>
       <c r="B217" t="n">
-        <v>80149</v>
+        <v>79043</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21625,37 +21640,37 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>585364</v>
+        <v>585353</v>
       </c>
       <c r="R217" t="n">
-        <v>7212436</v>
+        <v>7211885</v>
       </c>
       <c r="S217" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -21695,31 +21710,26 @@
       </c>
       <c r="AG217" t="b">
         <v>0</v>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128995997</v>
+        <v>128995872</v>
       </c>
       <c r="B218" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21727,37 +21737,37 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>584895</v>
+        <v>585359</v>
       </c>
       <c r="R218" t="n">
-        <v>7212228</v>
+        <v>7211883</v>
       </c>
       <c r="S218" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -21789,11 +21799,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD218" t="b">
         <v>0</v>
       </c>
@@ -21802,21 +21807,16 @@
       </c>
       <c r="AG218" t="b">
         <v>0</v>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
@@ -22119,10 +22119,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128996001</v>
+        <v>128995908</v>
       </c>
       <c r="B222" t="n">
-        <v>97587</v>
+        <v>80177</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22130,37 +22130,37 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>585205</v>
+        <v>585324</v>
       </c>
       <c r="R222" t="n">
-        <v>7212417</v>
+        <v>7211986</v>
       </c>
       <c r="S222" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -22184,12 +22184,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -22200,69 +22200,64 @@
       </c>
       <c r="AG222" t="b">
         <v>0</v>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128996026</v>
+        <v>128995932</v>
       </c>
       <c r="B223" t="n">
-        <v>79043</v>
+        <v>80184</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>585489</v>
+        <v>584973</v>
       </c>
       <c r="R223" t="n">
-        <v>7211976</v>
+        <v>7211930</v>
       </c>
       <c r="S223" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -22286,12 +22281,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -22302,31 +22297,26 @@
       </c>
       <c r="AG223" t="b">
         <v>0</v>
-      </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128995908</v>
+        <v>128995844</v>
       </c>
       <c r="B224" t="n">
-        <v>80177</v>
+        <v>80176</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22334,21 +22324,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -22358,10 +22348,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>585324</v>
+        <v>585365</v>
       </c>
       <c r="R224" t="n">
-        <v>7211986</v>
+        <v>7212081</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22408,60 +22398,60 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128995932</v>
+        <v>128996026</v>
       </c>
       <c r="B225" t="n">
-        <v>80184</v>
+        <v>79043</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>584973</v>
+        <v>585489</v>
       </c>
       <c r="R225" t="n">
-        <v>7211930</v>
+        <v>7211976</v>
       </c>
       <c r="S225" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -22485,12 +22475,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -22501,26 +22491,31 @@
       </c>
       <c r="AG225" t="b">
         <v>0</v>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128995844</v>
+        <v>128996001</v>
       </c>
       <c r="B226" t="n">
-        <v>80176</v>
+        <v>97587</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22528,37 +22523,37 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6461</v>
+        <v>221941</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>585365</v>
+        <v>585205</v>
       </c>
       <c r="R226" t="n">
-        <v>7212081</v>
+        <v>7212417</v>
       </c>
       <c r="S226" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -22582,12 +22577,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -22598,16 +22593,21 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
@@ -23647,10 +23647,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128995985</v>
+        <v>128995919</v>
       </c>
       <c r="B237" t="n">
-        <v>80149</v>
+        <v>91841</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23658,37 +23658,37 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>585343</v>
+        <v>585128</v>
       </c>
       <c r="R237" t="n">
-        <v>7211931</v>
+        <v>7212334</v>
       </c>
       <c r="S237" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -23712,12 +23712,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -23728,53 +23728,48 @@
       </c>
       <c r="AG237" t="b">
         <v>0</v>
-      </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128996042</v>
+        <v>128995985</v>
       </c>
       <c r="B238" t="n">
-        <v>91916</v>
+        <v>80149</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -23784,10 +23779,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>585044</v>
+        <v>585343</v>
       </c>
       <c r="R238" t="n">
-        <v>7212452</v>
+        <v>7211931</v>
       </c>
       <c r="S238" t="n">
         <v>15</v>
@@ -23851,48 +23846,48 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128995916</v>
+        <v>128996042</v>
       </c>
       <c r="B239" t="n">
-        <v>80149</v>
+        <v>91916</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>585465</v>
+        <v>585044</v>
       </c>
       <c r="R239" t="n">
-        <v>7211972</v>
+        <v>7212452</v>
       </c>
       <c r="S239" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -23916,12 +23911,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -23932,26 +23927,31 @@
       </c>
       <c r="AG239" t="b">
         <v>0</v>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128995919</v>
+        <v>128995916</v>
       </c>
       <c r="B240" t="n">
-        <v>91841</v>
+        <v>80149</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23959,21 +23959,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -23983,10 +23983,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>585128</v>
+        <v>585465</v>
       </c>
       <c r="R240" t="n">
-        <v>7212334</v>
+        <v>7211972</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26719,48 +26719,48 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128995965</v>
+        <v>128995874</v>
       </c>
       <c r="B268" t="n">
-        <v>105759</v>
+        <v>79043</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>585233</v>
+        <v>585370</v>
       </c>
       <c r="R268" t="n">
-        <v>7212183</v>
+        <v>7211866</v>
       </c>
       <c r="S268" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -26784,12 +26784,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -26800,69 +26800,64 @@
       </c>
       <c r="AG268" t="b">
         <v>0</v>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128995874</v>
+        <v>128995965</v>
       </c>
       <c r="B269" t="n">
-        <v>79043</v>
+        <v>105759</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>585370</v>
+        <v>585233</v>
       </c>
       <c r="R269" t="n">
-        <v>7211866</v>
+        <v>7212183</v>
       </c>
       <c r="S269" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -26886,12 +26881,12 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -26902,26 +26897,31 @@
       </c>
       <c r="AG269" t="b">
         <v>0</v>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128995864</v>
+        <v>128995912</v>
       </c>
       <c r="B270" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -26929,21 +26929,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -26953,10 +26953,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>585345</v>
+        <v>584990</v>
       </c>
       <c r="R270" t="n">
-        <v>7211890</v>
+        <v>7211932</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27003,44 +27003,44 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128995856</v>
+        <v>128995864</v>
       </c>
       <c r="B271" t="n">
-        <v>57831</v>
+        <v>79043</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -27050,10 +27050,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>585522</v>
+        <v>585345</v>
       </c>
       <c r="R271" t="n">
-        <v>7211894</v>
+        <v>7211890</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27080,12 +27080,12 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -27112,32 +27112,32 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128995912</v>
+        <v>128995856</v>
       </c>
       <c r="B272" t="n">
-        <v>80149</v>
+        <v>57831</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -27147,10 +27147,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>584990</v>
+        <v>585522</v>
       </c>
       <c r="R272" t="n">
-        <v>7211932</v>
+        <v>7211894</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27177,12 +27177,12 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -27197,22 +27197,22 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128995830</v>
+        <v>128995993</v>
       </c>
       <c r="B273" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -27220,37 +27220,41 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>585373</v>
+        <v>584850</v>
       </c>
       <c r="R273" t="n">
-        <v>7211857</v>
+        <v>7212144</v>
       </c>
       <c r="S273" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -27282,6 +27286,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD273" t="b">
         <v>0</v>
       </c>
@@ -27290,48 +27299,53 @@
       </c>
       <c r="AG273" t="b">
         <v>0</v>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128995906</v>
+        <v>128995830</v>
       </c>
       <c r="B274" t="n">
-        <v>80177</v>
+        <v>57887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -27341,10 +27355,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>584836</v>
+        <v>585373</v>
       </c>
       <c r="R274" t="n">
-        <v>7212031</v>
+        <v>7211857</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -27391,22 +27405,22 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128995936</v>
+        <v>128995906</v>
       </c>
       <c r="B275" t="n">
-        <v>80184</v>
+        <v>80177</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -27414,21 +27428,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -27438,10 +27452,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>585498</v>
+        <v>584836</v>
       </c>
       <c r="R275" t="n">
-        <v>7211887</v>
+        <v>7212031</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -27468,12 +27482,12 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -27493,59 +27507,55 @@
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128995993</v>
+        <v>128995936</v>
       </c>
       <c r="B276" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr"/>
-      <c r="N276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>584850</v>
+        <v>585498</v>
       </c>
       <c r="R276" t="n">
-        <v>7212144</v>
+        <v>7211887</v>
       </c>
       <c r="S276" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -27569,17 +27579,12 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -27590,21 +27595,16 @@
       </c>
       <c r="AG276" t="b">
         <v>0</v>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
@@ -27708,10 +27708,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>128995970</v>
+        <v>128995862</v>
       </c>
       <c r="B278" t="n">
-        <v>57887</v>
+        <v>79043</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -27719,37 +27719,37 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>585041</v>
+        <v>585258</v>
       </c>
       <c r="R278" t="n">
-        <v>7212398</v>
+        <v>7211874</v>
       </c>
       <c r="S278" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -27789,53 +27789,48 @@
       </c>
       <c r="AG278" t="b">
         <v>0</v>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>128996002</v>
+        <v>128995970</v>
       </c>
       <c r="B279" t="n">
-        <v>97587</v>
+        <v>57887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -27845,10 +27840,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>585221</v>
+        <v>585041</v>
       </c>
       <c r="R279" t="n">
-        <v>7212396</v>
+        <v>7212398</v>
       </c>
       <c r="S279" t="n">
         <v>15</v>
@@ -27912,32 +27907,32 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128995928</v>
+        <v>128995853</v>
       </c>
       <c r="B280" t="n">
-        <v>80149</v>
+        <v>57831</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -27947,10 +27942,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>585749</v>
+        <v>585109</v>
       </c>
       <c r="R280" t="n">
-        <v>7212194</v>
+        <v>7211888</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -27997,22 +27992,22 @@
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>128995862</v>
+        <v>128995928</v>
       </c>
       <c r="B281" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -28020,21 +28015,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -28044,10 +28039,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>585258</v>
+        <v>585749</v>
       </c>
       <c r="R281" t="n">
-        <v>7211874</v>
+        <v>7212194</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -28094,22 +28089,22 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>128995853</v>
+        <v>128996002</v>
       </c>
       <c r="B282" t="n">
-        <v>57831</v>
+        <v>97587</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -28117,37 +28112,37 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>103031</v>
+        <v>221941</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>585109</v>
+        <v>585221</v>
       </c>
       <c r="R282" t="n">
-        <v>7211888</v>
+        <v>7212396</v>
       </c>
       <c r="S282" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -28187,16 +28182,21 @@
       </c>
       <c r="AG282" t="b">
         <v>0</v>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>

--- a/artfynd/A 45899-2025 artfynd.xlsx
+++ b/artfynd/A 45899-2025 artfynd.xlsx
@@ -20047,10 +20047,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128995938</v>
+        <v>128995925</v>
       </c>
       <c r="B201" t="n">
-        <v>78801</v>
+        <v>91603</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20058,21 +20058,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20082,10 +20082,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>585313</v>
+        <v>585205</v>
       </c>
       <c r="R201" t="n">
-        <v>7212215</v>
+        <v>7212472</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20112,12 +20112,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -20144,48 +20144,48 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128995955</v>
+        <v>128995984</v>
       </c>
       <c r="B202" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>584836</v>
+        <v>585176</v>
       </c>
       <c r="R202" t="n">
-        <v>7212031</v>
+        <v>7212169</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -20209,12 +20209,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -20225,64 +20225,69 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128996034</v>
+        <v>128995914</v>
       </c>
       <c r="B203" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>585497</v>
+        <v>585318</v>
       </c>
       <c r="R203" t="n">
-        <v>7212005</v>
+        <v>7211888</v>
       </c>
       <c r="S203" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -20322,53 +20327,48 @@
       </c>
       <c r="AG203" t="b">
         <v>0</v>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128995934</v>
+        <v>128995938</v>
       </c>
       <c r="B204" t="n">
-        <v>80185</v>
+        <v>78801</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20378,10 +20378,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>585213</v>
+        <v>585313</v>
       </c>
       <c r="R204" t="n">
-        <v>7212298</v>
+        <v>7212215</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20440,10 +20440,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128995828</v>
+        <v>128995955</v>
       </c>
       <c r="B205" t="n">
-        <v>56917</v>
+        <v>80184</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20451,21 +20451,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -20475,10 +20475,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>585296</v>
+        <v>584836</v>
       </c>
       <c r="R205" t="n">
-        <v>7212121</v>
+        <v>7212031</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20505,12 +20505,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -20525,60 +20525,60 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128995925</v>
+        <v>128996034</v>
       </c>
       <c r="B206" t="n">
-        <v>91603</v>
+        <v>80184</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>2079</v>
+        <v>6463</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>585205</v>
+        <v>585497</v>
       </c>
       <c r="R206" t="n">
-        <v>7212472</v>
+        <v>7212005</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -20602,12 +20602,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -20618,64 +20618,69 @@
       </c>
       <c r="AG206" t="b">
         <v>0</v>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128995984</v>
+        <v>128995934</v>
       </c>
       <c r="B207" t="n">
-        <v>80150</v>
+        <v>80185</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>585176</v>
+        <v>585213</v>
       </c>
       <c r="R207" t="n">
-        <v>7212169</v>
+        <v>7212298</v>
       </c>
       <c r="S207" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -20715,31 +20720,26 @@
       </c>
       <c r="AG207" t="b">
         <v>0</v>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128995914</v>
+        <v>128995867</v>
       </c>
       <c r="B208" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20747,21 +20747,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -20771,10 +20771,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>585318</v>
+        <v>585364</v>
       </c>
       <c r="R208" t="n">
-        <v>7211888</v>
+        <v>7211892</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -20821,44 +20821,44 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128995867</v>
+        <v>128995828</v>
       </c>
       <c r="B209" t="n">
-        <v>79044</v>
+        <v>56917</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -20868,10 +20868,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>585364</v>
+        <v>585296</v>
       </c>
       <c r="R209" t="n">
-        <v>7211892</v>
+        <v>7212121</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -20898,12 +20898,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -20930,48 +20930,48 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128995981</v>
+        <v>128995957</v>
       </c>
       <c r="B210" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>585760</v>
+        <v>585466</v>
       </c>
       <c r="R210" t="n">
-        <v>7212191</v>
+        <v>7211970</v>
       </c>
       <c r="S210" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -20995,12 +20995,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -21011,28 +21011,23 @@
       </c>
       <c r="AG210" t="b">
         <v>0</v>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128995917</v>
+        <v>128995981</v>
       </c>
       <c r="B211" t="n">
         <v>80150</v>
@@ -21063,17 +21058,17 @@
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>585498</v>
+        <v>585760</v>
       </c>
       <c r="R211" t="n">
-        <v>7211889</v>
+        <v>7212191</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -21097,12 +21092,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -21113,23 +21108,28 @@
       </c>
       <c r="AG211" t="b">
         <v>0</v>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128995980</v>
+        <v>128995917</v>
       </c>
       <c r="B212" t="n">
         <v>80150</v>
@@ -21160,17 +21160,17 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>585364</v>
+        <v>585498</v>
       </c>
       <c r="R212" t="n">
-        <v>7212436</v>
+        <v>7211889</v>
       </c>
       <c r="S212" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -21194,12 +21194,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -21210,31 +21210,26 @@
       </c>
       <c r="AG212" t="b">
         <v>0</v>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128995872</v>
+        <v>128995980</v>
       </c>
       <c r="B213" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21242,37 +21237,37 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>585359</v>
+        <v>585364</v>
       </c>
       <c r="R213" t="n">
-        <v>7211883</v>
+        <v>7212436</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -21312,23 +21307,28 @@
       </c>
       <c r="AG213" t="b">
         <v>0</v>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128995871</v>
+        <v>128995872</v>
       </c>
       <c r="B214" t="n">
         <v>79044</v>
@@ -21363,10 +21363,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>585355</v>
+        <v>585359</v>
       </c>
       <c r="R214" t="n">
-        <v>7211878</v>
+        <v>7211883</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21425,27 +21425,27 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128995957</v>
+        <v>128995866</v>
       </c>
       <c r="B215" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -21460,10 +21460,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>585466</v>
+        <v>585353</v>
       </c>
       <c r="R215" t="n">
-        <v>7211970</v>
+        <v>7211885</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21490,12 +21490,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -21510,19 +21510,19 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128995866</v>
+        <v>128995871</v>
       </c>
       <c r="B216" t="n">
         <v>79044</v>
@@ -21557,10 +21557,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>585353</v>
+        <v>585355</v>
       </c>
       <c r="R216" t="n">
-        <v>7211885</v>
+        <v>7211878</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22119,48 +22119,48 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128995932</v>
+        <v>128996026</v>
       </c>
       <c r="B222" t="n">
-        <v>80185</v>
+        <v>79044</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>584973</v>
+        <v>585489</v>
       </c>
       <c r="R222" t="n">
-        <v>7211930</v>
+        <v>7211976</v>
       </c>
       <c r="S222" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -22184,12 +22184,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -22200,26 +22200,31 @@
       </c>
       <c r="AG222" t="b">
         <v>0</v>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128995844</v>
+        <v>128995908</v>
       </c>
       <c r="B223" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22227,21 +22232,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22251,10 +22256,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>585365</v>
+        <v>585324</v>
       </c>
       <c r="R223" t="n">
-        <v>7212081</v>
+        <v>7211986</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22301,22 +22306,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128996001</v>
+        <v>128995932</v>
       </c>
       <c r="B224" t="n">
-        <v>97601</v>
+        <v>80185</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22324,37 +22329,37 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>585205</v>
+        <v>584973</v>
       </c>
       <c r="R224" t="n">
-        <v>7212417</v>
+        <v>7211930</v>
       </c>
       <c r="S224" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -22394,69 +22399,64 @@
       </c>
       <c r="AG224" t="b">
         <v>0</v>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128996026</v>
+        <v>128995844</v>
       </c>
       <c r="B225" t="n">
-        <v>79044</v>
+        <v>80177</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>585489</v>
+        <v>585365</v>
       </c>
       <c r="R225" t="n">
-        <v>7211976</v>
+        <v>7212081</v>
       </c>
       <c r="S225" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -22496,31 +22496,26 @@
       </c>
       <c r="AG225" t="b">
         <v>0</v>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128995908</v>
+        <v>128996001</v>
       </c>
       <c r="B226" t="n">
-        <v>80178</v>
+        <v>97601</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22528,37 +22523,37 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>585324</v>
+        <v>585205</v>
       </c>
       <c r="R226" t="n">
-        <v>7211986</v>
+        <v>7212417</v>
       </c>
       <c r="S226" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -22582,12 +22577,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -22598,16 +22593,21 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
@@ -23647,10 +23647,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128995948</v>
+        <v>128995919</v>
       </c>
       <c r="B237" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23658,21 +23658,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -23682,10 +23682,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>585381</v>
+        <v>585128</v>
       </c>
       <c r="R237" t="n">
-        <v>7212289</v>
+        <v>7212334</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -23712,12 +23712,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -23744,10 +23744,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128995919</v>
+        <v>128995985</v>
       </c>
       <c r="B238" t="n">
-        <v>91848</v>
+        <v>80150</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23755,37 +23755,37 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>585128</v>
+        <v>585343</v>
       </c>
       <c r="R238" t="n">
-        <v>7212334</v>
+        <v>7211931</v>
       </c>
       <c r="S238" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -23809,12 +23809,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -23825,23 +23825,28 @@
       </c>
       <c r="AG238" t="b">
         <v>0</v>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128995985</v>
+        <v>128995916</v>
       </c>
       <c r="B239" t="n">
         <v>80150</v>
@@ -23872,17 +23877,17 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>585343</v>
+        <v>585465</v>
       </c>
       <c r="R239" t="n">
-        <v>7211931</v>
+        <v>7211972</v>
       </c>
       <c r="S239" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -23906,12 +23911,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -23922,69 +23927,64 @@
       </c>
       <c r="AG239" t="b">
         <v>0</v>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128995916</v>
+        <v>128996042</v>
       </c>
       <c r="B240" t="n">
-        <v>80150</v>
+        <v>91923</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>585465</v>
+        <v>585044</v>
       </c>
       <c r="R240" t="n">
-        <v>7211972</v>
+        <v>7212452</v>
       </c>
       <c r="S240" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -24008,12 +24008,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -24024,64 +24024,69 @@
       </c>
       <c r="AG240" t="b">
         <v>0</v>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128996042</v>
+        <v>128995948</v>
       </c>
       <c r="B241" t="n">
-        <v>91923</v>
+        <v>79044</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>585044</v>
+        <v>585381</v>
       </c>
       <c r="R241" t="n">
-        <v>7212452</v>
+        <v>7212289</v>
       </c>
       <c r="S241" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -24121,21 +24126,16 @@
       </c>
       <c r="AG241" t="b">
         <v>0</v>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
@@ -24239,32 +24239,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128995918</v>
+        <v>128995930</v>
       </c>
       <c r="B243" t="n">
-        <v>80053</v>
+        <v>80149</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24274,10 +24274,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>585498</v>
+        <v>585467</v>
       </c>
       <c r="R243" t="n">
-        <v>7211887</v>
+        <v>7211960</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24336,7 +24336,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128995930</v>
+        <v>128995848</v>
       </c>
       <c r="B244" t="n">
         <v>80149</v>
@@ -24371,10 +24371,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>585467</v>
+        <v>584913</v>
       </c>
       <c r="R244" t="n">
-        <v>7211960</v>
+        <v>7211897</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -24421,44 +24421,44 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128995848</v>
+        <v>128995918</v>
       </c>
       <c r="B245" t="n">
-        <v>80149</v>
+        <v>80053</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -24468,10 +24468,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>584913</v>
+        <v>585498</v>
       </c>
       <c r="R245" t="n">
-        <v>7211897</v>
+        <v>7211887</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -24498,12 +24498,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -24518,12 +24518,12 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
@@ -24627,48 +24627,48 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128995975</v>
+        <v>128995873</v>
       </c>
       <c r="B247" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>584970</v>
+        <v>585359</v>
       </c>
       <c r="R247" t="n">
-        <v>7211976</v>
+        <v>7211881</v>
       </c>
       <c r="S247" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -24708,53 +24708,48 @@
       </c>
       <c r="AG247" t="b">
         <v>0</v>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128995933</v>
+        <v>128995859</v>
       </c>
       <c r="B248" t="n">
-        <v>80185</v>
+        <v>79044</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -24764,10 +24759,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>584847</v>
+        <v>585374</v>
       </c>
       <c r="R248" t="n">
-        <v>7212088</v>
+        <v>7212193</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -24794,12 +24789,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -24814,60 +24809,60 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128995873</v>
+        <v>128995975</v>
       </c>
       <c r="B249" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>585359</v>
+        <v>584970</v>
       </c>
       <c r="R249" t="n">
-        <v>7211881</v>
+        <v>7211976</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -24907,48 +24902,53 @@
       </c>
       <c r="AG249" t="b">
         <v>0</v>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128995859</v>
+        <v>128995933</v>
       </c>
       <c r="B250" t="n">
-        <v>79044</v>
+        <v>80185</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -24958,10 +24958,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>585374</v>
+        <v>584847</v>
       </c>
       <c r="R250" t="n">
-        <v>7212193</v>
+        <v>7212088</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -24988,12 +24988,12 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -25008,12 +25008,12 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
@@ -25311,10 +25311,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128995926</v>
+        <v>128995982</v>
       </c>
       <c r="B254" t="n">
-        <v>83007</v>
+        <v>80150</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -25322,37 +25322,37 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>585749</v>
+        <v>585762</v>
       </c>
       <c r="R254" t="n">
-        <v>7212196</v>
+        <v>7212189</v>
       </c>
       <c r="S254" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -25392,26 +25392,31 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128995982</v>
+        <v>128996022</v>
       </c>
       <c r="B255" t="n">
-        <v>80150</v>
+        <v>91570</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -25419,23 +25424,19 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
@@ -25443,10 +25444,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>585762</v>
+        <v>585044</v>
       </c>
       <c r="R255" t="n">
-        <v>7212189</v>
+        <v>7212452</v>
       </c>
       <c r="S255" t="n">
         <v>15</v>
@@ -25510,10 +25511,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128996022</v>
+        <v>128995950</v>
       </c>
       <c r="B256" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -25521,33 +25522,37 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>585044</v>
+        <v>585251</v>
       </c>
       <c r="R256" t="n">
-        <v>7212452</v>
+        <v>7212276</v>
       </c>
       <c r="S256" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -25571,12 +25576,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -25587,31 +25592,26 @@
       </c>
       <c r="AG256" t="b">
         <v>0</v>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128995950</v>
+        <v>128995992</v>
       </c>
       <c r="B257" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -25619,37 +25619,41 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>585251</v>
+        <v>584913</v>
       </c>
       <c r="R257" t="n">
-        <v>7212276</v>
+        <v>7211982</v>
       </c>
       <c r="S257" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -25673,12 +25677,17 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -25689,43 +25698,48 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128995992</v>
+        <v>128995937</v>
       </c>
       <c r="B258" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -25734,23 +25748,19 @@
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>584913</v>
+        <v>584866</v>
       </c>
       <c r="R258" t="n">
-        <v>7211982</v>
+        <v>7212160</v>
       </c>
       <c r="S258" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -25784,7 +25794,7 @@
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -25795,53 +25805,48 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128995937</v>
+        <v>128995926</v>
       </c>
       <c r="B259" t="n">
-        <v>57831</v>
+        <v>83007</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>103031</v>
+        <v>310</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -25851,10 +25856,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>584866</v>
+        <v>585749</v>
       </c>
       <c r="R259" t="n">
-        <v>7212160</v>
+        <v>7212196</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -25887,11 +25892,6 @@
       <c r="AA259" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -25918,48 +25918,48 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128996043</v>
+        <v>128995958</v>
       </c>
       <c r="B260" t="n">
-        <v>88950</v>
+        <v>80184</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>585400</v>
+        <v>585463</v>
       </c>
       <c r="R260" t="n">
-        <v>7212315</v>
+        <v>7211957</v>
       </c>
       <c r="S260" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -25983,12 +25983,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -25999,53 +25999,48 @@
       </c>
       <c r="AG260" t="b">
         <v>0</v>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128995958</v>
+        <v>128995929</v>
       </c>
       <c r="B261" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26055,10 +26050,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>585463</v>
+        <v>584848</v>
       </c>
       <c r="R261" t="n">
-        <v>7211957</v>
+        <v>7212088</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26085,12 +26080,12 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -26117,10 +26112,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128995929</v>
+        <v>128996043</v>
       </c>
       <c r="B262" t="n">
-        <v>80149</v>
+        <v>88950</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26128,37 +26123,37 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>584848</v>
+        <v>585400</v>
       </c>
       <c r="R262" t="n">
-        <v>7212088</v>
+        <v>7212315</v>
       </c>
       <c r="S262" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -26198,16 +26193,21 @@
       </c>
       <c r="AG262" t="b">
         <v>0</v>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
@@ -26719,48 +26719,48 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128995965</v>
+        <v>128995874</v>
       </c>
       <c r="B268" t="n">
-        <v>105775</v>
+        <v>79044</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>585233</v>
+        <v>585370</v>
       </c>
       <c r="R268" t="n">
-        <v>7212183</v>
+        <v>7211866</v>
       </c>
       <c r="S268" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -26784,12 +26784,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -26800,69 +26800,64 @@
       </c>
       <c r="AG268" t="b">
         <v>0</v>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128995874</v>
+        <v>128995965</v>
       </c>
       <c r="B269" t="n">
-        <v>79044</v>
+        <v>105775</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>585370</v>
+        <v>585233</v>
       </c>
       <c r="R269" t="n">
-        <v>7211866</v>
+        <v>7212183</v>
       </c>
       <c r="S269" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -26886,12 +26881,12 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -26902,16 +26897,21 @@
       </c>
       <c r="AG269" t="b">
         <v>0</v>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
@@ -28300,10 +28300,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128995959</v>
+        <v>128995840</v>
       </c>
       <c r="B284" t="n">
-        <v>80184</v>
+        <v>80177</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -28311,21 +28311,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -28335,10 +28335,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>585498</v>
+        <v>585334</v>
       </c>
       <c r="R284" t="n">
-        <v>7211887</v>
+        <v>7212251</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -28385,22 +28385,22 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128995840</v>
+        <v>128995959</v>
       </c>
       <c r="B285" t="n">
-        <v>80177</v>
+        <v>80184</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -28408,21 +28408,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -28432,10 +28432,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>585334</v>
+        <v>585498</v>
       </c>
       <c r="R285" t="n">
-        <v>7212251</v>
+        <v>7211887</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -28482,12 +28482,12 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>

--- a/artfynd/A 45899-2025 artfynd.xlsx
+++ b/artfynd/A 45899-2025 artfynd.xlsx
@@ -19356,7 +19356,7 @@
         <v>128995946</v>
       </c>
       <c r="B194" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>128995941</v>
       </c>
       <c r="B198" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20047,32 +20047,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128995925</v>
+        <v>128995828</v>
       </c>
       <c r="B201" t="n">
-        <v>91603</v>
+        <v>56917</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20082,10 +20082,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>585205</v>
+        <v>585296</v>
       </c>
       <c r="R201" t="n">
-        <v>7212472</v>
+        <v>7212121</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20112,12 +20112,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -20132,22 +20132,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128995984</v>
+        <v>128995867</v>
       </c>
       <c r="B202" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20155,37 +20155,37 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>585176</v>
+        <v>585364</v>
       </c>
       <c r="R202" t="n">
-        <v>7212169</v>
+        <v>7211892</v>
       </c>
       <c r="S202" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -20209,12 +20209,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -20225,31 +20225,26 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128995914</v>
+        <v>128995938</v>
       </c>
       <c r="B203" t="n">
-        <v>80150</v>
+        <v>78801</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20257,21 +20252,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20281,10 +20276,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>585318</v>
+        <v>585313</v>
       </c>
       <c r="R203" t="n">
-        <v>7211888</v>
+        <v>7212215</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20343,32 +20338,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128995938</v>
+        <v>128995955</v>
       </c>
       <c r="B204" t="n">
-        <v>78801</v>
+        <v>80184</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20378,10 +20373,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>585313</v>
+        <v>584836</v>
       </c>
       <c r="R204" t="n">
-        <v>7212215</v>
+        <v>7212031</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20408,12 +20403,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -20440,7 +20435,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128995955</v>
+        <v>128996034</v>
       </c>
       <c r="B205" t="n">
         <v>80184</v>
@@ -20471,17 +20466,17 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>584836</v>
+        <v>585497</v>
       </c>
       <c r="R205" t="n">
-        <v>7212031</v>
+        <v>7212005</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -20505,12 +20500,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -20521,26 +20516,31 @@
       </c>
       <c r="AG205" t="b">
         <v>0</v>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128996034</v>
+        <v>128995934</v>
       </c>
       <c r="B206" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20548,37 +20548,37 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>585497</v>
+        <v>585213</v>
       </c>
       <c r="R206" t="n">
-        <v>7212005</v>
+        <v>7212298</v>
       </c>
       <c r="S206" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -20618,53 +20618,48 @@
       </c>
       <c r="AG206" t="b">
         <v>0</v>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128995934</v>
+        <v>128995925</v>
       </c>
       <c r="B207" t="n">
-        <v>80185</v>
+        <v>91606</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6464</v>
+        <v>2079</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -20674,10 +20669,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>585213</v>
+        <v>585205</v>
       </c>
       <c r="R207" t="n">
-        <v>7212298</v>
+        <v>7212472</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -20704,12 +20699,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -20736,10 +20731,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128995867</v>
+        <v>128995984</v>
       </c>
       <c r="B208" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20747,37 +20742,37 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>585364</v>
+        <v>585176</v>
       </c>
       <c r="R208" t="n">
-        <v>7211892</v>
+        <v>7212169</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -20801,12 +20796,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -20817,48 +20812,53 @@
       </c>
       <c r="AG208" t="b">
         <v>0</v>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128995828</v>
+        <v>128995914</v>
       </c>
       <c r="B209" t="n">
-        <v>56917</v>
+        <v>80150</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -20868,10 +20868,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>585296</v>
+        <v>585318</v>
       </c>
       <c r="R209" t="n">
-        <v>7212121</v>
+        <v>7211888</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -20918,60 +20918,60 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128995957</v>
+        <v>128995997</v>
       </c>
       <c r="B210" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>585466</v>
+        <v>584895</v>
       </c>
       <c r="R210" t="n">
-        <v>7211970</v>
+        <v>7212228</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -20995,12 +20995,17 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -21011,16 +21016,21 @@
       </c>
       <c r="AG210" t="b">
         <v>0</v>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
@@ -21716,48 +21726,48 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128995997</v>
+        <v>128995957</v>
       </c>
       <c r="B218" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>584895</v>
+        <v>585466</v>
       </c>
       <c r="R218" t="n">
-        <v>7212228</v>
+        <v>7211970</v>
       </c>
       <c r="S218" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -21781,17 +21791,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -21802,21 +21807,16 @@
       </c>
       <c r="AG218" t="b">
         <v>0</v>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
@@ -22515,7 +22515,7 @@
         <v>128996001</v>
       </c>
       <c r="B226" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22614,32 +22614,32 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128995976</v>
+        <v>128995990</v>
       </c>
       <c r="B227" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -22649,10 +22649,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>585192</v>
+        <v>584908</v>
       </c>
       <c r="R227" t="n">
-        <v>7212415</v>
+        <v>7212299</v>
       </c>
       <c r="S227" t="n">
         <v>15</v>
@@ -22685,6 +22685,11 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -22716,32 +22721,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128996033</v>
+        <v>128995996</v>
       </c>
       <c r="B228" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -22751,10 +22756,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>585247</v>
+        <v>584898</v>
       </c>
       <c r="R228" t="n">
-        <v>7212446</v>
+        <v>7212225</v>
       </c>
       <c r="S228" t="n">
         <v>15</v>
@@ -22787,6 +22792,11 @@
       <c r="AA228" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -22818,32 +22828,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128995996</v>
+        <v>128995976</v>
       </c>
       <c r="B229" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -22853,10 +22863,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>584898</v>
+        <v>585192</v>
       </c>
       <c r="R229" t="n">
-        <v>7212225</v>
+        <v>7212415</v>
       </c>
       <c r="S229" t="n">
         <v>15</v>
@@ -22889,11 +22899,6 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -22925,32 +22930,32 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128995990</v>
+        <v>128996033</v>
       </c>
       <c r="B230" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -22960,10 +22965,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>584908</v>
+        <v>585247</v>
       </c>
       <c r="R230" t="n">
-        <v>7212299</v>
+        <v>7212446</v>
       </c>
       <c r="S230" t="n">
         <v>15</v>
@@ -22996,11 +23001,6 @@
       <c r="AA230" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -23032,10 +23032,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128995902</v>
+        <v>128995995</v>
       </c>
       <c r="B231" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23043,37 +23043,41 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>584932</v>
+        <v>584838</v>
       </c>
       <c r="R231" t="n">
-        <v>7211934</v>
+        <v>7212145</v>
       </c>
       <c r="S231" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -23105,6 +23109,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD231" t="b">
         <v>0</v>
       </c>
@@ -23113,64 +23122,73 @@
       </c>
       <c r="AG231" t="b">
         <v>0</v>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128995838</v>
+        <v>128995994</v>
       </c>
       <c r="B232" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>584779</v>
+        <v>584839</v>
       </c>
       <c r="R232" t="n">
-        <v>7211856</v>
+        <v>7212144</v>
       </c>
       <c r="S232" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -23202,6 +23220,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD232" t="b">
         <v>0</v>
       </c>
@@ -23210,26 +23233,31 @@
       </c>
       <c r="AG232" t="b">
         <v>0</v>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128995995</v>
+        <v>128995902</v>
       </c>
       <c r="B233" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23237,41 +23265,37 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>584838</v>
+        <v>584932</v>
       </c>
       <c r="R233" t="n">
-        <v>7212145</v>
+        <v>7211934</v>
       </c>
       <c r="S233" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -23303,11 +23327,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD233" t="b">
         <v>0</v>
       </c>
@@ -23316,31 +23335,26 @@
       </c>
       <c r="AG233" t="b">
         <v>0</v>
-      </c>
-      <c r="AH233" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128995994</v>
+        <v>128995947</v>
       </c>
       <c r="B234" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23348,41 +23362,37 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>584839</v>
+        <v>585239</v>
       </c>
       <c r="R234" t="n">
-        <v>7212144</v>
+        <v>7211879</v>
       </c>
       <c r="S234" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -23414,11 +23424,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD234" t="b">
         <v>0</v>
       </c>
@@ -23427,53 +23432,48 @@
       </c>
       <c r="AG234" t="b">
         <v>0</v>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128995947</v>
+        <v>128995838</v>
       </c>
       <c r="B235" t="n">
-        <v>79044</v>
+        <v>80177</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -23483,10 +23483,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>585239</v>
+        <v>584779</v>
       </c>
       <c r="R235" t="n">
-        <v>7211879</v>
+        <v>7211856</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -23533,12 +23533,12 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
@@ -23548,7 +23548,7 @@
         <v>128996000</v>
       </c>
       <c r="B236" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>128995919</v>
       </c>
       <c r="B237" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>128996042</v>
       </c>
       <c r="B240" t="n">
-        <v>91923</v>
+        <v>91926</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>128995922</v>
       </c>
       <c r="B242" t="n">
-        <v>91932</v>
+        <v>91935</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24239,32 +24239,32 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128995930</v>
+        <v>128995918</v>
       </c>
       <c r="B243" t="n">
-        <v>80149</v>
+        <v>80053</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24274,10 +24274,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>585467</v>
+        <v>585498</v>
       </c>
       <c r="R243" t="n">
-        <v>7211960</v>
+        <v>7211887</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24336,7 +24336,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128995848</v>
+        <v>128995930</v>
       </c>
       <c r="B244" t="n">
         <v>80149</v>
@@ -24371,10 +24371,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>584913</v>
+        <v>585467</v>
       </c>
       <c r="R244" t="n">
-        <v>7211897</v>
+        <v>7211960</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -24421,44 +24421,44 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128995918</v>
+        <v>128995848</v>
       </c>
       <c r="B245" t="n">
-        <v>80053</v>
+        <v>80149</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -24468,10 +24468,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>585498</v>
+        <v>584913</v>
       </c>
       <c r="R245" t="n">
-        <v>7211887</v>
+        <v>7211897</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -24498,12 +24498,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -24518,12 +24518,12 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Embla Berg, Magdalena Nilsson, Henny My Lindqvist, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Henny My Lindqvist, Magdalena Nilsson, Embla Berg</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
@@ -25311,10 +25311,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128995982</v>
+        <v>128995950</v>
       </c>
       <c r="B254" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -25322,37 +25322,37 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>585762</v>
+        <v>585251</v>
       </c>
       <c r="R254" t="n">
-        <v>7212189</v>
+        <v>7212276</v>
       </c>
       <c r="S254" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -25376,12 +25376,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -25392,65 +25392,64 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128996022</v>
+        <v>128995937</v>
       </c>
       <c r="B255" t="n">
-        <v>91570</v>
+        <v>57831</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr"/>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>585044</v>
+        <v>584866</v>
       </c>
       <c r="R255" t="n">
-        <v>7212452</v>
+        <v>7212160</v>
       </c>
       <c r="S255" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -25482,6 +25481,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD255" t="b">
         <v>0</v>
       </c>
@@ -25490,31 +25494,26 @@
       </c>
       <c r="AG255" t="b">
         <v>0</v>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128995950</v>
+        <v>128995926</v>
       </c>
       <c r="B256" t="n">
-        <v>79044</v>
+        <v>83007</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -25522,21 +25521,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -25546,10 +25545,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>585251</v>
+        <v>585749</v>
       </c>
       <c r="R256" t="n">
-        <v>7212276</v>
+        <v>7212196</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -25576,12 +25575,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -25608,10 +25607,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128995992</v>
+        <v>128995982</v>
       </c>
       <c r="B257" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -25619,38 +25618,34 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr"/>
-      <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
           <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>584913</v>
+        <v>585762</v>
       </c>
       <c r="R257" t="n">
-        <v>7211982</v>
+        <v>7212189</v>
       </c>
       <c r="S257" t="n">
         <v>15</v>
@@ -25683,11 +25678,6 @@
       <c r="AA257" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -25719,48 +25709,44 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128995937</v>
+        <v>128996022</v>
       </c>
       <c r="B258" t="n">
-        <v>57831</v>
+        <v>91573</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>584866</v>
+        <v>585044</v>
       </c>
       <c r="R258" t="n">
-        <v>7212160</v>
+        <v>7212452</v>
       </c>
       <c r="S258" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -25792,11 +25778,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD258" t="b">
         <v>0</v>
       </c>
@@ -25805,26 +25786,31 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128995926</v>
+        <v>128995992</v>
       </c>
       <c r="B259" t="n">
-        <v>83007</v>
+        <v>57727</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -25832,37 +25818,41 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>585749</v>
+        <v>584913</v>
       </c>
       <c r="R259" t="n">
-        <v>7212196</v>
+        <v>7211982</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -25894,6 +25884,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD259" t="b">
         <v>0</v>
       </c>
@@ -25902,64 +25897,69 @@
       </c>
       <c r="AG259" t="b">
         <v>0</v>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128995958</v>
+        <v>128996043</v>
       </c>
       <c r="B260" t="n">
-        <v>80184</v>
+        <v>88952</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>585463</v>
+        <v>585400</v>
       </c>
       <c r="R260" t="n">
-        <v>7211957</v>
+        <v>7212315</v>
       </c>
       <c r="S260" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -25983,12 +25983,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -25999,48 +25999,53 @@
       </c>
       <c r="AG260" t="b">
         <v>0</v>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128995929</v>
+        <v>128995958</v>
       </c>
       <c r="B261" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -26050,10 +26055,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>584848</v>
+        <v>585463</v>
       </c>
       <c r="R261" t="n">
-        <v>7212088</v>
+        <v>7211957</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -26080,12 +26085,12 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -26112,10 +26117,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128996043</v>
+        <v>128995929</v>
       </c>
       <c r="B262" t="n">
-        <v>88950</v>
+        <v>80149</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -26123,37 +26128,37 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>585400</v>
+        <v>584848</v>
       </c>
       <c r="R262" t="n">
-        <v>7212315</v>
+        <v>7212088</v>
       </c>
       <c r="S262" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -26193,31 +26198,26 @@
       </c>
       <c r="AG262" t="b">
         <v>0</v>
-      </c>
-      <c r="AH262" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128995904</v>
+        <v>128995983</v>
       </c>
       <c r="B263" t="n">
-        <v>57887</v>
+        <v>80150</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -26225,37 +26225,37 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>585576</v>
+        <v>585170</v>
       </c>
       <c r="R263" t="n">
-        <v>7212125</v>
+        <v>7212204</v>
       </c>
       <c r="S263" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -26279,17 +26279,12 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>Varningsläte</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -26300,48 +26295,53 @@
       </c>
       <c r="AG263" t="b">
         <v>0</v>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128995999</v>
+        <v>128995979</v>
       </c>
       <c r="B264" t="n">
-        <v>97595</v>
+        <v>80150</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -26351,10 +26351,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>585573</v>
+        <v>584970</v>
       </c>
       <c r="R264" t="n">
-        <v>7212171</v>
+        <v>7211976</v>
       </c>
       <c r="S264" t="n">
         <v>15</v>
@@ -26515,32 +26515,32 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128995983</v>
+        <v>128995999</v>
       </c>
       <c r="B266" t="n">
-        <v>80150</v>
+        <v>97598</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -26550,10 +26550,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>585170</v>
+        <v>585573</v>
       </c>
       <c r="R266" t="n">
-        <v>7212204</v>
+        <v>7212171</v>
       </c>
       <c r="S266" t="n">
         <v>15</v>
@@ -26580,12 +26580,12 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -26617,10 +26617,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128995979</v>
+        <v>128995904</v>
       </c>
       <c r="B267" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -26628,37 +26628,37 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>584970</v>
+        <v>585576</v>
       </c>
       <c r="R267" t="n">
-        <v>7211976</v>
+        <v>7212125</v>
       </c>
       <c r="S267" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -26690,6 +26690,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>Varningsläte</t>
+        </is>
+      </c>
       <c r="AD267" t="b">
         <v>0</v>
       </c>
@@ -26698,21 +26703,16 @@
       </c>
       <c r="AG267" t="b">
         <v>0</v>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
@@ -26819,7 +26819,7 @@
         <v>128995965</v>
       </c>
       <c r="B269" t="n">
-        <v>105775</v>
+        <v>105778</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -26918,32 +26918,32 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128995856</v>
+        <v>128995864</v>
       </c>
       <c r="B270" t="n">
-        <v>57831</v>
+        <v>79044</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -26953,10 +26953,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>585522</v>
+        <v>585345</v>
       </c>
       <c r="R270" t="n">
-        <v>7211894</v>
+        <v>7211890</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -26983,12 +26983,12 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -27112,32 +27112,32 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128995864</v>
+        <v>128995856</v>
       </c>
       <c r="B272" t="n">
-        <v>79044</v>
+        <v>57831</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -27147,10 +27147,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>585345</v>
+        <v>585522</v>
       </c>
       <c r="R272" t="n">
-        <v>7211890</v>
+        <v>7211894</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27177,12 +27177,12 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -27209,48 +27209,52 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128995906</v>
+        <v>128995993</v>
       </c>
       <c r="B273" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Inre Verkanliden, Ly lm</t>
+          <t>Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>584836</v>
+        <v>584850</v>
       </c>
       <c r="R273" t="n">
-        <v>7212031</v>
+        <v>7212144</v>
       </c>
       <c r="S273" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -27282,6 +27286,11 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD273" t="b">
         <v>0</v>
       </c>
@@ -27290,26 +27299,31 @@
       </c>
       <c r="AG273" t="b">
         <v>0</v>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Embla Berg</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
+          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128995936</v>
+        <v>128995906</v>
       </c>
       <c r="B274" t="n">
-        <v>80185</v>
+        <v>80178</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -27317,21 +27331,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -27341,10 +27355,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>585498</v>
+        <v>584836</v>
       </c>
       <c r="R274" t="n">
-        <v>7211887</v>
+        <v>7212031</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -27371,12 +27385,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -27396,59 +27410,55 @@
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Magdalena Nilsson, Elin Kannerby, Embla Berg, Alva Danielsson, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128995993</v>
+        <v>128995936</v>
       </c>
       <c r="B275" t="n">
-        <v>57727</v>
+        <v>80185</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Verkanliden, Ly lm</t>
+          <t>Inre Verkanliden, Ly lm</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>584850</v>
+        <v>585498</v>
       </c>
       <c r="R275" t="n">
-        <v>7212144</v>
+        <v>7211887</v>
       </c>
       <c r="S275" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -27472,17 +27482,12 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -27493,21 +27498,16 @@
       </c>
       <c r="AG275" t="b">
         <v>0</v>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Embla Berg</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Embla Berg, Henny My Lindqvist, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
@@ -27902,32 +27902,32 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>128996002</v>
+        <v>128995970</v>
       </c>
       <c r="B280" t="n">
-        <v>97601</v>
+        <v>57887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -27937,10 +27937,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>585221</v>
+        <v>585041</v>
       </c>
       <c r="R280" t="n">
-        <v>7212396</v>
+        <v>7212398</v>
       </c>
       <c r="S280" t="n">
         <v>15</v>
@@ -28004,32 +28004,32 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>128995970</v>
+        <v>128996002</v>
       </c>
       <c r="B281" t="n">
-        <v>57887</v>
+        <v>97604</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -28039,10 +28039,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>585041</v>
+        <v>585221</v>
       </c>
       <c r="R281" t="n">
-        <v>7212398</v>
+        <v>7212396</v>
       </c>
       <c r="S281" t="n">
         <v>15</v>
@@ -28300,10 +28300,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>128995840</v>
+        <v>128995959</v>
       </c>
       <c r="B284" t="n">
-        <v>80177</v>
+        <v>80184</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -28311,21 +28311,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -28335,10 +28335,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>585334</v>
+        <v>585498</v>
       </c>
       <c r="R284" t="n">
-        <v>7212251</v>
+        <v>7211887</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -28385,22 +28385,22 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist</t>
+          <t>Magdalena Nilsson</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
+          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>128995959</v>
+        <v>128995840</v>
       </c>
       <c r="B285" t="n">
-        <v>80184</v>
+        <v>80177</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -28408,21 +28408,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -28432,10 +28432,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>585498</v>
+        <v>585334</v>
       </c>
       <c r="R285" t="n">
-        <v>7211887</v>
+        <v>7212251</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -28482,12 +28482,12 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson</t>
+          <t>Henny My Lindqvist</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Magdalena Nilsson, Alva Danielsson, Elin Kannerby, Embla Berg, Henny My Lindqvist</t>
+          <t>Henny My Lindqvist, Embla Berg, Magdalena Nilsson, Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
@@ -28497,7 +28497,7 @@
         <v>129073659</v>
       </c>
       <c r="B286" t="n">
-        <v>91763</v>
+        <v>91766</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>129073658</v>
       </c>
       <c r="B287" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
